--- a/research/traditional_assets/database/data/italy/italy_restaurant_dining.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_restaurant_dining.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bit_agl" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,34 +590,37 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.165</v>
+        <v>-0.0573</v>
+      </c>
+      <c r="E2">
+        <v>-0.0352</v>
       </c>
       <c r="G2">
-        <v>-0.09408876906361917</v>
+        <v>0.05205366644706837</v>
       </c>
       <c r="H2">
-        <v>-0.09408876906361917</v>
+        <v>0.05205366644706837</v>
       </c>
       <c r="I2">
-        <v>-0.1388032674741459</v>
+        <v>0.02357472254598895</v>
       </c>
       <c r="J2">
-        <v>-0.1388032674741459</v>
+        <v>0.01997896661361823</v>
       </c>
       <c r="K2">
-        <v>-424.9299999999999</v>
+        <v>75.468</v>
       </c>
       <c r="L2">
-        <v>-0.1709911069977063</v>
+        <v>0.01912228247098769</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.005193827625141137</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0.1828589600890444</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +629,82 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>13.8</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>1170.51</v>
+        <v>469.67</v>
       </c>
       <c r="V2">
-        <v>0.4290096760005864</v>
+        <v>0.17676703048551</v>
       </c>
       <c r="W2">
-        <v>-0.4395449150671735</v>
+        <v>-0.02433181133971208</v>
       </c>
       <c r="X2">
-        <v>0.1184294946056094</v>
+        <v>0.1594082330350926</v>
       </c>
       <c r="Y2">
-        <v>-0.5579744096727828</v>
+        <v>-0.1837400443748047</v>
       </c>
       <c r="Z2">
-        <v>0.701880936974758</v>
+        <v>1.447521212534669</v>
       </c>
       <c r="AA2">
-        <v>-0.130054859138532</v>
+        <v>-0.06836702817234512</v>
       </c>
       <c r="AB2">
-        <v>0.07936861208580799</v>
+        <v>0.1202982694314547</v>
       </c>
       <c r="AC2">
-        <v>-0.20942347122434</v>
+        <v>-0.1886652976037998</v>
       </c>
       <c r="AD2">
-        <v>3900.01</v>
+        <v>2424.98</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3900.01</v>
+        <v>2424.98</v>
       </c>
       <c r="AG2">
-        <v>2729.5</v>
+        <v>1955.31</v>
       </c>
       <c r="AH2">
-        <v>0.5883779066171223</v>
+        <v>0.4771722832439325</v>
       </c>
       <c r="AI2">
-        <v>0.7977536134054991</v>
+        <v>0.7012605442983433</v>
       </c>
       <c r="AJ2">
-        <v>0.5001007713589476</v>
+        <v>0.4239329099735274</v>
       </c>
       <c r="AK2">
-        <v>0.7340858419194078</v>
+        <v>0.6543087178251616</v>
       </c>
       <c r="AL2">
-        <v>130.481</v>
+        <v>61.872</v>
       </c>
       <c r="AM2">
-        <v>125.881</v>
+        <v>56.672</v>
       </c>
       <c r="AN2">
-        <v>-55.43724235963042</v>
+        <v>7.646498663034155</v>
       </c>
       <c r="AO2">
-        <v>-2.64360328323664</v>
+        <v>1.503749676752004</v>
       </c>
       <c r="AP2">
-        <v>-38.79886282871358</v>
+        <v>6.165525200544876</v>
       </c>
       <c r="AQ2">
-        <v>-2.74020702091658</v>
+        <v>1.641727837380011</v>
       </c>
     </row>
     <row r="3">
@@ -716,34 +724,37 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.165</v>
+        <v>-0.0573</v>
+      </c>
+      <c r="E3">
+        <v>-0.0352</v>
       </c>
       <c r="G3">
-        <v>-0.09436493738819321</v>
+        <v>0.05269479440852521</v>
       </c>
       <c r="H3">
-        <v>-0.09436493738819321</v>
+        <v>0.05269479440852521</v>
       </c>
       <c r="I3">
-        <v>-0.1396975117905351</v>
+        <v>0.02412409598528021</v>
       </c>
       <c r="J3">
-        <v>-0.1396975117905351</v>
+        <v>0.01676499675660989</v>
       </c>
       <c r="K3">
-        <v>-423.4</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="L3">
-        <v>-0.1721418116766954</v>
+        <v>0.01952416242876492</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>13.8</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.005233021121686702</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.1806282722513089</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +763,82 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>13.8</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>1164.2</v>
+        <v>468.1</v>
       </c>
       <c r="V3">
-        <v>0.4311053508609517</v>
+        <v>0.1775055932653294</v>
       </c>
       <c r="W3">
-        <v>-0.6520868627752965</v>
+        <v>0.08316098835310766</v>
       </c>
       <c r="X3">
-        <v>0.1459986200255599</v>
+        <v>0.1758544433770005</v>
       </c>
       <c r="Y3">
-        <v>-0.7980854828008563</v>
+        <v>-0.0926934550238928</v>
       </c>
       <c r="Z3">
-        <v>0.6962971350922885</v>
+        <v>1.439698307579102</v>
       </c>
       <c r="AA3">
-        <v>-0.09727097723927076</v>
+        <v>0.0241365374570604</v>
       </c>
       <c r="AB3">
-        <v>0.08075486855051431</v>
+        <v>0.1215154119837154</v>
       </c>
       <c r="AC3">
-        <v>-0.1780258457897851</v>
+        <v>-0.09737887452665503</v>
       </c>
       <c r="AD3">
-        <v>3892.2</v>
+        <v>2417.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3892.2</v>
+        <v>2417.4</v>
       </c>
       <c r="AG3">
-        <v>2728</v>
+        <v>1949.3</v>
       </c>
       <c r="AH3">
-        <v>0.5903802690855037</v>
+        <v>0.4782668908893066</v>
       </c>
       <c r="AI3">
-        <v>0.7985146585150688</v>
+        <v>0.7015700728444149</v>
       </c>
       <c r="AJ3">
-        <v>0.502532928064843</v>
+        <v>0.4250174428745858</v>
       </c>
       <c r="AK3">
-        <v>0.7352901539042075</v>
+        <v>0.6546547555077915</v>
       </c>
       <c r="AL3">
-        <v>130.4</v>
+        <v>61.8</v>
       </c>
       <c r="AM3">
-        <v>125.8</v>
+        <v>56.59999999999999</v>
       </c>
       <c r="AN3">
-        <v>-56.16450216450217</v>
+        <v>7.599497013517762</v>
       </c>
       <c r="AO3">
-        <v>-2.634969325153374</v>
+        <v>1.527508090614887</v>
       </c>
       <c r="AP3">
-        <v>-39.36507936507937</v>
+        <v>6.127947186419365</v>
       </c>
       <c r="AQ3">
-        <v>-2.731319554848966</v>
+        <v>1.667844522968198</v>
       </c>
     </row>
     <row r="4">
@@ -844,22 +858,22 @@
         </is>
       </c>
       <c r="G4">
-        <v>-0.06745098039215686</v>
+        <v>-0.02283582089552239</v>
       </c>
       <c r="H4">
-        <v>-0.06745098039215686</v>
+        <v>-0.02283582089552239</v>
       </c>
       <c r="I4">
-        <v>-0.05254901960784314</v>
+        <v>-0.04059701492537314</v>
       </c>
       <c r="J4">
-        <v>-0.05254901960784314</v>
+        <v>-0.04059701492537314</v>
       </c>
       <c r="K4">
-        <v>-1.53</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="L4">
-        <v>-0.06</v>
+        <v>-0.02782089552238806</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -883,73 +897,8774 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>6.31</v>
+        <v>1.57</v>
       </c>
       <c r="V4">
-        <v>0.2261648745519713</v>
+        <v>0.07889447236180905</v>
       </c>
       <c r="W4">
-        <v>-0.2270029673590504</v>
+        <v>-0.1318246110325318</v>
       </c>
       <c r="X4">
-        <v>0.0908603691856588</v>
+        <v>0.1429620226931848</v>
       </c>
       <c r="Y4">
-        <v>-0.3178633365447092</v>
+        <v>-0.2747866337257167</v>
       </c>
       <c r="Z4">
-        <v>3.098796937659497</v>
+        <v>3.962621244381358</v>
       </c>
       <c r="AA4">
-        <v>-0.1628387410377932</v>
+        <v>-0.1608705938017506</v>
       </c>
       <c r="AB4">
-        <v>0.07798235562110167</v>
+        <v>0.1190811268791939</v>
       </c>
       <c r="AC4">
-        <v>-0.2408210966588949</v>
+        <v>-0.2799517206809446</v>
       </c>
       <c r="AD4">
-        <v>7.81</v>
+        <v>7.58</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>7.81</v>
+        <v>7.58</v>
       </c>
       <c r="AG4">
+        <v>6.01</v>
+      </c>
+      <c r="AH4">
+        <v>0.2758369723435226</v>
+      </c>
+      <c r="AI4">
+        <v>0.6147607461476075</v>
+      </c>
+      <c r="AJ4">
+        <v>0.2319567734465457</v>
+      </c>
+      <c r="AK4">
+        <v>0.5585501858736059</v>
+      </c>
+      <c r="AL4">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="AM4">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="AN4">
+        <v>-7.863070539419088</v>
+      </c>
+      <c r="AO4">
+        <v>-18.88888888888889</v>
+      </c>
+      <c r="AP4">
+        <v>-6.234439834024896</v>
+      </c>
+      <c r="AQ4">
+        <v>-18.88888888888889</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Autogrill S.p.A. (BIT:AGL)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BIT:AGL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Restaurant/Dining</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.478266890889307</v>
+      </c>
+      <c r="F2">
+        <v>0.01</v>
+      </c>
+      <c r="G2">
+        <v>2637.1</v>
+      </c>
+      <c r="H2">
+        <v>4326.27911556505</v>
+      </c>
+      <c r="I2">
+        <v>4586.4</v>
+      </c>
+      <c r="J2">
+        <v>3908.72411556505</v>
+      </c>
+      <c r="K2">
+        <v>2417.4</v>
+      </c>
+      <c r="L2">
+        <v>50.545</v>
+      </c>
+      <c r="M2">
+        <v>0.121515411983715</v>
+      </c>
+      <c r="N2">
+        <v>0.135856214331277</v>
+      </c>
+      <c r="O2">
+        <v>0.0622378990825688</v>
+      </c>
+      <c r="P2">
+        <v>1.30573045800772</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.175854443377</v>
+      </c>
+      <c r="T2">
+        <v>0.12403930277899</v>
+      </c>
+      <c r="U2">
+        <v>1.4118134200081</v>
+      </c>
+      <c r="V2">
+        <v>0.878059759394173</v>
+      </c>
+      <c r="W2">
+        <v>-18.61617912492524</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>2637.1</v>
+      </c>
+      <c r="AB2">
+        <v>0.09707688100614176</v>
+      </c>
+      <c r="AC2">
+        <v>0.08189197247706423</v>
+      </c>
+      <c r="AD2">
+        <v>0.24</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>318.1</v>
+      </c>
+      <c r="AH2">
+        <v>542.8</v>
+      </c>
+      <c r="AI2">
+        <v>183.9</v>
+      </c>
+      <c r="AJ2">
+        <v>2417.4</v>
+      </c>
+      <c r="AK2">
+        <v>2417.4</v>
+      </c>
+      <c r="AL2">
+        <v>61.8</v>
+      </c>
+      <c r="AM2">
+        <v>2417.4</v>
+      </c>
+      <c r="AN2">
+        <v>468.1</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>-2417.4</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>468.1</v>
+      </c>
+      <c r="H2">
+        <v>2637.1</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>318.1</v>
+      </c>
+      <c r="K2">
+        <v>542.8</v>
+      </c>
+      <c r="L2">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="O2">
+        <v>-53.92799999999998</v>
+      </c>
+      <c r="P2">
+        <v>-170.7719999999999</v>
+      </c>
+      <c r="Q2">
+        <v>372.028</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-Inf</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1358562143312769</v>
+      </c>
+      <c r="C3">
+        <v>4326.279115565053</v>
+      </c>
+      <c r="D3">
+        <v>3908.724115565053</v>
+      </c>
+      <c r="E3">
+        <v>-2366.855</v>
+      </c>
+      <c r="F3">
+        <v>50.545</v>
+      </c>
+      <c r="G3">
+        <v>468.1</v>
+      </c>
+      <c r="H3">
+        <v>2637.1</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>318.1</v>
+      </c>
+      <c r="K3">
+        <v>542.8</v>
+      </c>
+      <c r="L3">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M3">
+        <v>12.070146</v>
+      </c>
+      <c r="N3">
+        <v>-236.7701459999999</v>
+      </c>
+      <c r="O3">
+        <v>-56.82483503999998</v>
+      </c>
+      <c r="P3">
+        <v>-179.9453109599999</v>
+      </c>
+      <c r="Q3">
+        <v>362.85468904</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1240393027789896</v>
+      </c>
+      <c r="T3">
+        <v>0.8780597593941731</v>
+      </c>
+      <c r="U3">
+        <v>0.2388</v>
+      </c>
+      <c r="V3">
+        <v>-4.467882989982058</v>
+      </c>
+      <c r="W3">
+        <v>1.305730458007715</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>-18.61617912492524</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1378562143312769</v>
+      </c>
+      <c r="C4">
+        <v>4196.814804102312</v>
+      </c>
+      <c r="D4">
+        <v>3829.804804102312</v>
+      </c>
+      <c r="E4">
+        <v>-2316.31</v>
+      </c>
+      <c r="F4">
+        <v>101.09</v>
+      </c>
+      <c r="G4">
+        <v>468.1</v>
+      </c>
+      <c r="H4">
+        <v>2637.1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>318.1</v>
+      </c>
+      <c r="K4">
+        <v>542.8</v>
+      </c>
+      <c r="L4">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M4">
+        <v>24.140292</v>
+      </c>
+      <c r="N4">
+        <v>-248.8402919999999</v>
+      </c>
+      <c r="O4">
+        <v>-59.72167007999998</v>
+      </c>
+      <c r="P4">
+        <v>-189.11862192</v>
+      </c>
+      <c r="Q4">
+        <v>353.68137808</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1249090915828568</v>
+      </c>
+      <c r="T4">
+        <v>0.887019552857379</v>
+      </c>
+      <c r="U4">
+        <v>0.2388</v>
+      </c>
+      <c r="V4">
+        <v>-2.233941494991029</v>
+      </c>
+      <c r="W4">
+        <v>0.7722652290038577</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>-9.308089562462621</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1398562143312769</v>
+      </c>
+      <c r="C5">
+        <v>4070.474271300188</v>
+      </c>
+      <c r="D5">
+        <v>3754.009271300188</v>
+      </c>
+      <c r="E5">
+        <v>-2265.765</v>
+      </c>
+      <c r="F5">
+        <v>151.635</v>
+      </c>
+      <c r="G5">
+        <v>468.1</v>
+      </c>
+      <c r="H5">
+        <v>2637.1</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>318.1</v>
+      </c>
+      <c r="K5">
+        <v>542.8</v>
+      </c>
+      <c r="L5">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M5">
+        <v>36.210438</v>
+      </c>
+      <c r="N5">
+        <v>-260.9104379999999</v>
+      </c>
+      <c r="O5">
+        <v>-62.61850511999998</v>
+      </c>
+      <c r="P5">
+        <v>-198.29193288</v>
+      </c>
+      <c r="Q5">
+        <v>344.50806712</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1257968141764946</v>
+      </c>
+      <c r="T5">
+        <v>0.8961640843301356</v>
+      </c>
+      <c r="U5">
+        <v>0.2388</v>
+      </c>
+      <c r="V5">
+        <v>-1.48929432999402</v>
+      </c>
+      <c r="W5">
+        <v>0.5944434860025719</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>-6.205393041641749</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1418562143312769</v>
+      </c>
+      <c r="C6">
+        <v>3947.075648728088</v>
+      </c>
+      <c r="D6">
+        <v>3681.155648728088</v>
+      </c>
+      <c r="E6">
+        <v>-2215.22</v>
+      </c>
+      <c r="F6">
+        <v>202.18</v>
+      </c>
+      <c r="G6">
+        <v>468.1</v>
+      </c>
+      <c r="H6">
+        <v>2637.1</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>318.1</v>
+      </c>
+      <c r="K6">
+        <v>542.8</v>
+      </c>
+      <c r="L6">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M6">
+        <v>48.280584</v>
+      </c>
+      <c r="N6">
+        <v>-272.9805839999999</v>
+      </c>
+      <c r="O6">
+        <v>-65.51534015999998</v>
+      </c>
+      <c r="P6">
+        <v>-207.4652438399999</v>
+      </c>
+      <c r="Q6">
+        <v>335.33475616</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.126703030990833</v>
+      </c>
+      <c r="T6">
+        <v>0.9054991268752411</v>
+      </c>
+      <c r="U6">
+        <v>0.2388</v>
+      </c>
+      <c r="V6">
+        <v>-1.116970747495514</v>
+      </c>
+      <c r="W6">
+        <v>0.5055326145019289</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>-4.65404478123131</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1438562143312769</v>
+      </c>
+      <c r="C7">
+        <v>3826.450917183218</v>
+      </c>
+      <c r="D7">
+        <v>3611.075917183218</v>
+      </c>
+      <c r="E7">
+        <v>-2164.675</v>
+      </c>
+      <c r="F7">
+        <v>252.725</v>
+      </c>
+      <c r="G7">
+        <v>468.1</v>
+      </c>
+      <c r="H7">
+        <v>2637.1</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>318.1</v>
+      </c>
+      <c r="K7">
+        <v>542.8</v>
+      </c>
+      <c r="L7">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M7">
+        <v>60.35073000000001</v>
+      </c>
+      <c r="N7">
+        <v>-285.0507299999999</v>
+      </c>
+      <c r="O7">
+        <v>-68.41217519999998</v>
+      </c>
+      <c r="P7">
+        <v>-216.6385548</v>
+      </c>
+      <c r="Q7">
+        <v>326.1614452</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1276283260538945</v>
+      </c>
+      <c r="T7">
+        <v>0.9150306966318227</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>-0.8935765979964116</v>
+      </c>
+      <c r="W7">
+        <v>0.4521860916015431</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>-3.723235824985048</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1458562143312769</v>
+      </c>
+      <c r="C8">
+        <v>3708.444613049878</v>
+      </c>
+      <c r="D8">
+        <v>3543.614613049878</v>
+      </c>
+      <c r="E8">
+        <v>-2114.13</v>
+      </c>
+      <c r="F8">
+        <v>303.27</v>
+      </c>
+      <c r="G8">
+        <v>468.1</v>
+      </c>
+      <c r="H8">
+        <v>2637.1</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>318.1</v>
+      </c>
+      <c r="K8">
+        <v>542.8</v>
+      </c>
+      <c r="L8">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M8">
+        <v>72.42087599999999</v>
+      </c>
+      <c r="N8">
+        <v>-297.120876</v>
+      </c>
+      <c r="O8">
+        <v>-71.30901023999999</v>
+      </c>
+      <c r="P8">
+        <v>-225.81186576</v>
+      </c>
+      <c r="Q8">
+        <v>316.98813424</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1285733082459571</v>
+      </c>
+      <c r="T8">
+        <v>0.9247650657449271</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>-0.7446471649970098</v>
+      </c>
+      <c r="W8">
+        <v>0.416621743001286</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>-3.102696520820874</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1478562143312769</v>
+      </c>
+      <c r="C9">
+        <v>3592.91267700448</v>
+      </c>
+      <c r="D9">
+        <v>3478.62767700448</v>
+      </c>
+      <c r="E9">
+        <v>-2063.585</v>
+      </c>
+      <c r="F9">
+        <v>353.8150000000001</v>
+      </c>
+      <c r="G9">
+        <v>468.1</v>
+      </c>
+      <c r="H9">
+        <v>2637.1</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>318.1</v>
+      </c>
+      <c r="K9">
+        <v>542.8</v>
+      </c>
+      <c r="L9">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M9">
+        <v>84.49102200000002</v>
+      </c>
+      <c r="N9">
+        <v>-309.191022</v>
+      </c>
+      <c r="O9">
+        <v>-74.20584527999999</v>
+      </c>
+      <c r="P9">
+        <v>-234.98517672</v>
+      </c>
+      <c r="Q9">
+        <v>307.81482328</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1295386126356986</v>
+      </c>
+      <c r="T9">
+        <v>0.9347087761292813</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>-0.6382689985688653</v>
+      </c>
+      <c r="W9">
+        <v>0.3912186368582451</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>-2.659454160703606</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1498562143312769</v>
+      </c>
+      <c r="C10">
+        <v>3479.721427121914</v>
+      </c>
+      <c r="D10">
+        <v>3415.981427121914</v>
+      </c>
+      <c r="E10">
+        <v>-2013.04</v>
+      </c>
+      <c r="F10">
+        <v>404.36</v>
+      </c>
+      <c r="G10">
+        <v>468.1</v>
+      </c>
+      <c r="H10">
+        <v>2637.1</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>318.1</v>
+      </c>
+      <c r="K10">
+        <v>542.8</v>
+      </c>
+      <c r="L10">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M10">
+        <v>96.56116800000001</v>
+      </c>
+      <c r="N10">
+        <v>-321.2611679999999</v>
+      </c>
+      <c r="O10">
+        <v>-77.10268031999998</v>
+      </c>
+      <c r="P10">
+        <v>-244.15848768</v>
+      </c>
+      <c r="Q10">
+        <v>298.64151232</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.130524901903478</v>
+      </c>
+      <c r="T10">
+        <v>0.9448686541306864</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>-0.5584853737477572</v>
+      </c>
+      <c r="W10">
+        <v>0.3721663072509644</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>-2.327022390615655</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1518562143312769</v>
+      </c>
+      <c r="C11">
+        <v>3368.746640978316</v>
+      </c>
+      <c r="D11">
+        <v>3355.551640978317</v>
+      </c>
+      <c r="E11">
+        <v>-1962.495</v>
+      </c>
+      <c r="F11">
+        <v>454.905</v>
+      </c>
+      <c r="G11">
+        <v>468.1</v>
+      </c>
+      <c r="H11">
+        <v>2637.1</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>318.1</v>
+      </c>
+      <c r="K11">
+        <v>542.8</v>
+      </c>
+      <c r="L11">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M11">
+        <v>108.631314</v>
+      </c>
+      <c r="N11">
+        <v>-333.3313139999999</v>
+      </c>
+      <c r="O11">
+        <v>-79.99951535999998</v>
+      </c>
+      <c r="P11">
+        <v>-253.3317986399999</v>
+      </c>
+      <c r="Q11">
+        <v>289.46820136</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1315328678584612</v>
+      </c>
+      <c r="T11">
+        <v>0.9552518261541004</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>-0.4964314433313398</v>
+      </c>
+      <c r="W11">
+        <v>0.357347828667524</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>-2.068464347213915</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1538562143312769</v>
+      </c>
+      <c r="C12">
+        <v>3259.872733487638</v>
+      </c>
+      <c r="D12">
+        <v>3297.222733487639</v>
+      </c>
+      <c r="E12">
+        <v>-1911.95</v>
+      </c>
+      <c r="F12">
+        <v>505.45</v>
+      </c>
+      <c r="G12">
+        <v>468.1</v>
+      </c>
+      <c r="H12">
+        <v>2637.1</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>318.1</v>
+      </c>
+      <c r="K12">
+        <v>542.8</v>
+      </c>
+      <c r="L12">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M12">
+        <v>120.70146</v>
+      </c>
+      <c r="N12">
+        <v>-345.4014599999999</v>
+      </c>
+      <c r="O12">
+        <v>-82.89635039999997</v>
+      </c>
+      <c r="P12">
+        <v>-262.5051096</v>
+      </c>
+      <c r="Q12">
+        <v>280.2948904</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1325632330568886</v>
+      </c>
+      <c r="T12">
+        <v>0.9658657353335905</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>-0.4467882989982058</v>
+      </c>
+      <c r="W12">
+        <v>0.3454930458007716</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>-1.861617912492524</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1558562143312769</v>
+      </c>
+      <c r="C13">
+        <v>3152.992019022172</v>
+      </c>
+      <c r="D13">
+        <v>3240.887019022172</v>
+      </c>
+      <c r="E13">
+        <v>-1861.405</v>
+      </c>
+      <c r="F13">
+        <v>555.995</v>
+      </c>
+      <c r="G13">
+        <v>468.1</v>
+      </c>
+      <c r="H13">
+        <v>2637.1</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>318.1</v>
+      </c>
+      <c r="K13">
+        <v>542.8</v>
+      </c>
+      <c r="L13">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M13">
+        <v>132.771606</v>
+      </c>
+      <c r="N13">
+        <v>-357.471606</v>
+      </c>
+      <c r="O13">
+        <v>-85.79318543999999</v>
+      </c>
+      <c r="P13">
+        <v>-271.6784205599999</v>
+      </c>
+      <c r="Q13">
+        <v>271.12157944</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1336167525294379</v>
+      </c>
+      <c r="T13">
+        <v>0.9767181593261028</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>-0.4061711809074598</v>
+      </c>
+      <c r="W13">
+        <v>0.3357936780007014</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>-1.692379920447749</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1578562143312769</v>
+      </c>
+      <c r="C14">
+        <v>3048.004047905952</v>
+      </c>
+      <c r="D14">
+        <v>3186.444047905952</v>
+      </c>
+      <c r="E14">
+        <v>-1810.86</v>
+      </c>
+      <c r="F14">
+        <v>606.54</v>
+      </c>
+      <c r="G14">
+        <v>468.1</v>
+      </c>
+      <c r="H14">
+        <v>2637.1</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>318.1</v>
+      </c>
+      <c r="K14">
+        <v>542.8</v>
+      </c>
+      <c r="L14">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M14">
+        <v>144.841752</v>
+      </c>
+      <c r="N14">
+        <v>-369.5417519999999</v>
+      </c>
+      <c r="O14">
+        <v>-88.69002047999997</v>
+      </c>
+      <c r="P14">
+        <v>-280.8517315199999</v>
+      </c>
+      <c r="Q14">
+        <v>261.94826848</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1346942156263633</v>
+      </c>
+      <c r="T14">
+        <v>0.9878172293184448</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>-0.3723235824985049</v>
+      </c>
+      <c r="W14">
+        <v>0.327710871500643</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>-1.551348260410437</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1598562143312769</v>
+      </c>
+      <c r="C15">
+        <v>2944.81500867991</v>
+      </c>
+      <c r="D15">
+        <v>3133.80000867991</v>
+      </c>
+      <c r="E15">
+        <v>-1760.315</v>
+      </c>
+      <c r="F15">
+        <v>657.085</v>
+      </c>
+      <c r="G15">
+        <v>468.1</v>
+      </c>
+      <c r="H15">
+        <v>2637.1</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>318.1</v>
+      </c>
+      <c r="K15">
+        <v>542.8</v>
+      </c>
+      <c r="L15">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M15">
+        <v>156.911898</v>
+      </c>
+      <c r="N15">
+        <v>-381.6118979999999</v>
+      </c>
+      <c r="O15">
+        <v>-91.58685551999999</v>
+      </c>
+      <c r="P15">
+        <v>-290.02504248</v>
+      </c>
+      <c r="Q15">
+        <v>252.77495752</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1357964479898847</v>
+      </c>
+      <c r="T15">
+        <v>0.9991714503450936</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>-0.3436833069216968</v>
+      </c>
+      <c r="W15">
+        <v>0.3208715736929013</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>-1.432013778840403</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1618562143312769</v>
+      </c>
+      <c r="C16">
+        <v>2843.337188655989</v>
+      </c>
+      <c r="D16">
+        <v>3082.867188655989</v>
+      </c>
+      <c r="E16">
+        <v>-1709.77</v>
+      </c>
+      <c r="F16">
+        <v>707.6300000000001</v>
+      </c>
+      <c r="G16">
+        <v>468.1</v>
+      </c>
+      <c r="H16">
+        <v>2637.1</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>318.1</v>
+      </c>
+      <c r="K16">
+        <v>542.8</v>
+      </c>
+      <c r="L16">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M16">
+        <v>168.982044</v>
+      </c>
+      <c r="N16">
+        <v>-393.682044</v>
+      </c>
+      <c r="O16">
+        <v>-94.48369055999999</v>
+      </c>
+      <c r="P16">
+        <v>-299.19835344</v>
+      </c>
+      <c r="Q16">
+        <v>243.6016465599999</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1369243136641857</v>
+      </c>
+      <c r="T16">
+        <v>1.010789723023525</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>-0.3191344992844327</v>
+      </c>
+      <c r="W16">
+        <v>0.3150093184291226</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>-1.329727080351803</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1638562143312769</v>
+      </c>
+      <c r="C17">
+        <v>2743.488486234782</v>
+      </c>
+      <c r="D17">
+        <v>3033.563486234782</v>
+      </c>
+      <c r="E17">
+        <v>-1659.225</v>
+      </c>
+      <c r="F17">
+        <v>758.175</v>
+      </c>
+      <c r="G17">
+        <v>468.1</v>
+      </c>
+      <c r="H17">
+        <v>2637.1</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>318.1</v>
+      </c>
+      <c r="K17">
+        <v>542.8</v>
+      </c>
+      <c r="L17">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M17">
+        <v>181.05219</v>
+      </c>
+      <c r="N17">
+        <v>-405.7521899999999</v>
+      </c>
+      <c r="O17">
+        <v>-97.38052559999998</v>
+      </c>
+      <c r="P17">
+        <v>-308.3716643999999</v>
+      </c>
+      <c r="Q17">
+        <v>234.4283356</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1380787173543526</v>
+      </c>
+      <c r="T17">
+        <v>1.022681366823802</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>-0.2978588659988039</v>
+      </c>
+      <c r="W17">
+        <v>0.3099286972005144</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>-1.24107860832835</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1658562143312769</v>
+      </c>
+      <c r="C18">
+        <v>2645.191969282997</v>
+      </c>
+      <c r="D18">
+        <v>2985.811969282997</v>
+      </c>
+      <c r="E18">
+        <v>-1608.68</v>
+      </c>
+      <c r="F18">
+        <v>808.72</v>
+      </c>
+      <c r="G18">
+        <v>468.1</v>
+      </c>
+      <c r="H18">
+        <v>2637.1</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>318.1</v>
+      </c>
+      <c r="K18">
+        <v>542.8</v>
+      </c>
+      <c r="L18">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M18">
+        <v>193.122336</v>
+      </c>
+      <c r="N18">
+        <v>-417.822336</v>
+      </c>
+      <c r="O18">
+        <v>-100.27736064</v>
+      </c>
+      <c r="P18">
+        <v>-317.54497536</v>
+      </c>
+      <c r="Q18">
+        <v>225.25502464</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1392606068466663</v>
+      </c>
+      <c r="T18">
+        <v>1.034856145000276</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>-0.2792426868738786</v>
+      </c>
+      <c r="W18">
+        <v>0.3054831536254822</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>-1.163511195307827</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1678562143312769</v>
+      </c>
+      <c r="C19">
+        <v>2548.375474574208</v>
+      </c>
+      <c r="D19">
+        <v>2939.540474574208</v>
+      </c>
+      <c r="E19">
+        <v>-1558.135</v>
+      </c>
+      <c r="F19">
+        <v>859.2650000000001</v>
+      </c>
+      <c r="G19">
+        <v>468.1</v>
+      </c>
+      <c r="H19">
+        <v>2637.1</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>318.1</v>
+      </c>
+      <c r="K19">
+        <v>542.8</v>
+      </c>
+      <c r="L19">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M19">
+        <v>205.192482</v>
+      </c>
+      <c r="N19">
+        <v>-429.892482</v>
+      </c>
+      <c r="O19">
+        <v>-103.17419568</v>
+      </c>
+      <c r="P19">
+        <v>-326.71828632</v>
+      </c>
+      <c r="Q19">
+        <v>216.08171368</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1404709756038551</v>
+      </c>
+      <c r="T19">
+        <v>1.04732429132558</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>-0.2628166464695328</v>
+      </c>
+      <c r="W19">
+        <v>0.3015606151769245</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>-1.09506936028972</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1698562143312769</v>
+      </c>
+      <c r="C20">
+        <v>2452.971243906309</v>
+      </c>
+      <c r="D20">
+        <v>2894.681243906309</v>
+      </c>
+      <c r="E20">
+        <v>-1507.59</v>
+      </c>
+      <c r="F20">
+        <v>909.8099999999999</v>
+      </c>
+      <c r="G20">
+        <v>468.1</v>
+      </c>
+      <c r="H20">
+        <v>2637.1</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>318.1</v>
+      </c>
+      <c r="K20">
+        <v>542.8</v>
+      </c>
+      <c r="L20">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M20">
+        <v>217.262628</v>
+      </c>
+      <c r="N20">
+        <v>-441.9626279999999</v>
+      </c>
+      <c r="O20">
+        <v>-106.07103072</v>
+      </c>
+      <c r="P20">
+        <v>-335.8915972799999</v>
+      </c>
+      <c r="Q20">
+        <v>206.90840272</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1417108655502436</v>
+      </c>
+      <c r="T20">
+        <v>1.06009653878077</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>-0.2482157216656699</v>
+      </c>
+      <c r="W20">
+        <v>0.298073914333762</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>-1.034232173606958</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1718562143312769</v>
+      </c>
+      <c r="C21">
+        <v>2358.915593036606</v>
+      </c>
+      <c r="D21">
+        <v>2851.170593036606</v>
+      </c>
+      <c r="E21">
+        <v>-1457.045</v>
+      </c>
+      <c r="F21">
+        <v>960.355</v>
+      </c>
+      <c r="G21">
+        <v>468.1</v>
+      </c>
+      <c r="H21">
+        <v>2637.1</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>318.1</v>
+      </c>
+      <c r="K21">
+        <v>542.8</v>
+      </c>
+      <c r="L21">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M21">
+        <v>229.332774</v>
+      </c>
+      <c r="N21">
+        <v>-454.032774</v>
+      </c>
+      <c r="O21">
+        <v>-108.96786576</v>
+      </c>
+      <c r="P21">
+        <v>-345.06490824</v>
+      </c>
+      <c r="Q21">
+        <v>197.73509176</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1429813700632095</v>
+      </c>
+      <c r="T21">
+        <v>1.073184150370656</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>-0.2351517363148451</v>
+      </c>
+      <c r="W21">
+        <v>0.2949542346319851</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>-0.9797989013118549</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1738562143312769</v>
+      </c>
+      <c r="C22">
+        <v>2266.148610032654</v>
+      </c>
+      <c r="D22">
+        <v>2808.948610032654</v>
+      </c>
+      <c r="E22">
+        <v>-1406.5</v>
+      </c>
+      <c r="F22">
+        <v>1010.9</v>
+      </c>
+      <c r="G22">
+        <v>468.1</v>
+      </c>
+      <c r="H22">
+        <v>2637.1</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>318.1</v>
+      </c>
+      <c r="K22">
+        <v>542.8</v>
+      </c>
+      <c r="L22">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M22">
+        <v>241.40292</v>
+      </c>
+      <c r="N22">
+        <v>-466.1029199999999</v>
+      </c>
+      <c r="O22">
+        <v>-111.8647008</v>
+      </c>
+      <c r="P22">
+        <v>-354.2382191999999</v>
+      </c>
+      <c r="Q22">
+        <v>188.5617808</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1442836371889996</v>
+      </c>
+      <c r="T22">
+        <v>1.086598952250289</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>-0.2233941494991029</v>
+      </c>
+      <c r="W22">
+        <v>0.2921465229003858</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>-0.930808956246262</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1758562143312769</v>
+      </c>
+      <c r="C23">
+        <v>2174.613880034083</v>
+      </c>
+      <c r="D23">
+        <v>2767.958880034083</v>
+      </c>
+      <c r="E23">
+        <v>-1355.955</v>
+      </c>
+      <c r="F23">
+        <v>1061.445</v>
+      </c>
+      <c r="G23">
+        <v>468.1</v>
+      </c>
+      <c r="H23">
+        <v>2637.1</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>318.1</v>
+      </c>
+      <c r="K23">
+        <v>542.8</v>
+      </c>
+      <c r="L23">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M23">
+        <v>253.473066</v>
+      </c>
+      <c r="N23">
+        <v>-478.1730659999999</v>
+      </c>
+      <c r="O23">
+        <v>-114.76153584</v>
+      </c>
+      <c r="P23">
+        <v>-363.41153016</v>
+      </c>
+      <c r="Q23">
+        <v>179.38846984</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1456188731027845</v>
+      </c>
+      <c r="T23">
+        <v>1.100353369367382</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>-0.2127563328562885</v>
+      </c>
+      <c r="W23">
+        <v>0.2896062122860817</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>-0.8864847202345356</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1778562143312769</v>
+      </c>
+      <c r="C24">
+        <v>2084.258233766383</v>
+      </c>
+      <c r="D24">
+        <v>2728.148233766382</v>
+      </c>
+      <c r="E24">
+        <v>-1305.41</v>
+      </c>
+      <c r="F24">
+        <v>1111.99</v>
+      </c>
+      <c r="G24">
+        <v>468.1</v>
+      </c>
+      <c r="H24">
+        <v>2637.1</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>318.1</v>
+      </c>
+      <c r="K24">
+        <v>542.8</v>
+      </c>
+      <c r="L24">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M24">
+        <v>265.543212</v>
+      </c>
+      <c r="N24">
+        <v>-490.243212</v>
+      </c>
+      <c r="O24">
+        <v>-117.65837088</v>
+      </c>
+      <c r="P24">
+        <v>-372.58484112</v>
+      </c>
+      <c r="Q24">
+        <v>170.21515888</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1469883458348714</v>
+      </c>
+      <c r="T24">
+        <v>1.114460463846451</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>-0.2030855904537299</v>
+      </c>
+      <c r="W24">
+        <v>0.2872968390003507</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>-0.8461899602238745</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1798562143312769</v>
+      </c>
+      <c r="C25">
+        <v>1995.031517449237</v>
+      </c>
+      <c r="D25">
+        <v>2689.466517449237</v>
+      </c>
+      <c r="E25">
+        <v>-1254.865</v>
+      </c>
+      <c r="F25">
+        <v>1162.535</v>
+      </c>
+      <c r="G25">
+        <v>468.1</v>
+      </c>
+      <c r="H25">
+        <v>2637.1</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>318.1</v>
+      </c>
+      <c r="K25">
+        <v>542.8</v>
+      </c>
+      <c r="L25">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M25">
+        <v>277.6133580000001</v>
+      </c>
+      <c r="N25">
+        <v>-502.313358</v>
+      </c>
+      <c r="O25">
+        <v>-120.55520592</v>
+      </c>
+      <c r="P25">
+        <v>-381.75815208</v>
+      </c>
+      <c r="Q25">
+        <v>161.04184792</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1483933892872724</v>
+      </c>
+      <c r="T25">
+        <v>1.128933976363937</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>-0.1942557821731329</v>
+      </c>
+      <c r="W25">
+        <v>0.2851882807829442</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>-0.8093990923880539</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1818562143312769</v>
+      </c>
+      <c r="C26">
+        <v>1906.886382005681</v>
+      </c>
+      <c r="D26">
+        <v>2651.866382005681</v>
+      </c>
+      <c r="E26">
+        <v>-1204.32</v>
+      </c>
+      <c r="F26">
+        <v>1213.08</v>
+      </c>
+      <c r="G26">
+        <v>468.1</v>
+      </c>
+      <c r="H26">
+        <v>2637.1</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>318.1</v>
+      </c>
+      <c r="K26">
+        <v>542.8</v>
+      </c>
+      <c r="L26">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M26">
+        <v>289.683504</v>
+      </c>
+      <c r="N26">
+        <v>-514.3835039999999</v>
+      </c>
+      <c r="O26">
+        <v>-123.45204096</v>
+      </c>
+      <c r="P26">
+        <v>-390.9314630399999</v>
+      </c>
+      <c r="Q26">
+        <v>151.86853696</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.149835407567368</v>
+      </c>
+      <c r="T26">
+        <v>1.143788370789778</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>-0.1861617912492524</v>
+      </c>
+      <c r="W26">
+        <v>0.2832554357503215</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>-0.7756741302052186</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1838562143312769</v>
+      </c>
+      <c r="C27">
+        <v>1819.778089709228</v>
+      </c>
+      <c r="D27">
+        <v>2615.303089709229</v>
+      </c>
+      <c r="E27">
+        <v>-1153.775</v>
+      </c>
+      <c r="F27">
+        <v>1263.625</v>
+      </c>
+      <c r="G27">
+        <v>468.1</v>
+      </c>
+      <c r="H27">
+        <v>2637.1</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>318.1</v>
+      </c>
+      <c r="K27">
+        <v>542.8</v>
+      </c>
+      <c r="L27">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M27">
+        <v>301.75365</v>
+      </c>
+      <c r="N27">
+        <v>-526.4536499999999</v>
+      </c>
+      <c r="O27">
+        <v>-126.348876</v>
+      </c>
+      <c r="P27">
+        <v>-400.104774</v>
+      </c>
+      <c r="Q27">
+        <v>142.695226</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1513158796682663</v>
+      </c>
+      <c r="T27">
+        <v>1.159038882400309</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>-0.1787153195992823</v>
+      </c>
+      <c r="W27">
+        <v>0.2814772183203086</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>-0.7446471649970097</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1858562143312769</v>
+      </c>
+      <c r="C28">
+        <v>1733.664336608897</v>
+      </c>
+      <c r="D28">
+        <v>2579.734336608897</v>
+      </c>
+      <c r="E28">
+        <v>-1103.23</v>
+      </c>
+      <c r="F28">
+        <v>1314.17</v>
+      </c>
+      <c r="G28">
+        <v>468.1</v>
+      </c>
+      <c r="H28">
+        <v>2637.1</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>318.1</v>
+      </c>
+      <c r="K28">
+        <v>542.8</v>
+      </c>
+      <c r="L28">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M28">
+        <v>313.823796</v>
+      </c>
+      <c r="N28">
+        <v>-538.5237959999999</v>
+      </c>
+      <c r="O28">
+        <v>-129.24571104</v>
+      </c>
+      <c r="P28">
+        <v>-409.27808496</v>
+      </c>
+      <c r="Q28">
+        <v>133.52191504</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1528363645286483</v>
+      </c>
+      <c r="T28">
+        <v>1.174701570000313</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>-0.1718416534608484</v>
+      </c>
+      <c r="W28">
+        <v>0.2798357868464506</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>-0.7160068894202016</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1878562143312769</v>
+      </c>
+      <c r="C29">
+        <v>1648.505089250174</v>
+      </c>
+      <c r="D29">
+        <v>2545.120089250174</v>
+      </c>
+      <c r="E29">
+        <v>-1052.685</v>
+      </c>
+      <c r="F29">
+        <v>1364.715</v>
+      </c>
+      <c r="G29">
+        <v>468.1</v>
+      </c>
+      <c r="H29">
+        <v>2637.1</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>318.1</v>
+      </c>
+      <c r="K29">
+        <v>542.8</v>
+      </c>
+      <c r="L29">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M29">
+        <v>325.893942</v>
+      </c>
+      <c r="N29">
+        <v>-550.593942</v>
+      </c>
+      <c r="O29">
+        <v>-132.14254608</v>
+      </c>
+      <c r="P29">
+        <v>-418.45139592</v>
+      </c>
+      <c r="Q29">
+        <v>124.34860408</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1543985065084928</v>
+      </c>
+      <c r="T29">
+        <v>1.190793372329084</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>-0.1654771477771133</v>
+      </c>
+      <c r="W29">
+        <v>0.2783159428891747</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>-0.689488115737972</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1898562143312769</v>
+      </c>
+      <c r="C30">
+        <v>1564.262434366958</v>
+      </c>
+      <c r="D30">
+        <v>2511.422434366958</v>
+      </c>
+      <c r="E30">
+        <v>-1002.14</v>
+      </c>
+      <c r="F30">
+        <v>1415.26</v>
+      </c>
+      <c r="G30">
+        <v>468.1</v>
+      </c>
+      <c r="H30">
+        <v>2637.1</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>318.1</v>
+      </c>
+      <c r="K30">
+        <v>542.8</v>
+      </c>
+      <c r="L30">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M30">
+        <v>337.9640880000001</v>
+      </c>
+      <c r="N30">
+        <v>-562.664088</v>
+      </c>
+      <c r="O30">
+        <v>-135.03938112</v>
+      </c>
+      <c r="P30">
+        <v>-427.62470688</v>
+      </c>
+      <c r="Q30">
+        <v>115.17529312</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1560040413211107</v>
+      </c>
+      <c r="T30">
+        <v>1.207332169166988</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>-0.1595672496422163</v>
+      </c>
+      <c r="W30">
+        <v>0.2769046592145613</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>-0.6648635401759015</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1918562143312769</v>
+      </c>
+      <c r="C31">
+        <v>1480.900440358062</v>
+      </c>
+      <c r="D31">
+        <v>2478.605440358062</v>
+      </c>
+      <c r="E31">
+        <v>-951.5950000000003</v>
+      </c>
+      <c r="F31">
+        <v>1465.805</v>
+      </c>
+      <c r="G31">
+        <v>468.1</v>
+      </c>
+      <c r="H31">
+        <v>2637.1</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>318.1</v>
+      </c>
+      <c r="K31">
+        <v>542.8</v>
+      </c>
+      <c r="L31">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M31">
+        <v>350.034234</v>
+      </c>
+      <c r="N31">
+        <v>-574.7342339999999</v>
+      </c>
+      <c r="O31">
+        <v>-137.93621616</v>
+      </c>
+      <c r="P31">
+        <v>-436.7980178399999</v>
+      </c>
+      <c r="Q31">
+        <v>106.00198216</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1576548024664785</v>
+      </c>
+      <c r="T31">
+        <v>1.22433684760596</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>-0.1540649306890365</v>
+      </c>
+      <c r="W31">
+        <v>0.2755907054485419</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>-0.6419372112043189</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1938562143312769</v>
+      </c>
+      <c r="C32">
+        <v>1398.385029484203</v>
+      </c>
+      <c r="D32">
+        <v>2446.635029484203</v>
+      </c>
+      <c r="E32">
+        <v>-901.0500000000002</v>
+      </c>
+      <c r="F32">
+        <v>1516.35</v>
+      </c>
+      <c r="G32">
+        <v>468.1</v>
+      </c>
+      <c r="H32">
+        <v>2637.1</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>318.1</v>
+      </c>
+      <c r="K32">
+        <v>542.8</v>
+      </c>
+      <c r="L32">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M32">
+        <v>362.10438</v>
+      </c>
+      <c r="N32">
+        <v>-586.8043799999999</v>
+      </c>
+      <c r="O32">
+        <v>-140.8330512</v>
+      </c>
+      <c r="P32">
+        <v>-445.9713287999999</v>
+      </c>
+      <c r="Q32">
+        <v>96.82867120000003</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1593527282159996</v>
+      </c>
+      <c r="T32">
+        <v>1.241827374000331</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>-0.148929432999402</v>
+      </c>
+      <c r="W32">
+        <v>0.2743643486002572</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>-0.6205393041641749</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1958562143312769</v>
+      </c>
+      <c r="C33">
+        <v>1316.683859829896</v>
+      </c>
+      <c r="D33">
+        <v>2415.478859829896</v>
+      </c>
+      <c r="E33">
+        <v>-850.5050000000001</v>
+      </c>
+      <c r="F33">
+        <v>1566.895</v>
+      </c>
+      <c r="G33">
+        <v>468.1</v>
+      </c>
+      <c r="H33">
+        <v>2637.1</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>318.1</v>
+      </c>
+      <c r="K33">
+        <v>542.8</v>
+      </c>
+      <c r="L33">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M33">
+        <v>374.174526</v>
+      </c>
+      <c r="N33">
+        <v>-598.8745259999999</v>
+      </c>
+      <c r="O33">
+        <v>-143.72988624</v>
+      </c>
+      <c r="P33">
+        <v>-455.14463976</v>
+      </c>
+      <c r="Q33">
+        <v>87.65536023999999</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1610998692046373</v>
+      </c>
+      <c r="T33">
+        <v>1.259824872174249</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>-0.1441252577413567</v>
+      </c>
+      <c r="W33">
+        <v>0.273217111548636</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>-0.6005219072556529</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1978562143312769</v>
+      </c>
+      <c r="C34">
+        <v>1235.76621617073</v>
+      </c>
+      <c r="D34">
+        <v>2385.10621617073</v>
+      </c>
+      <c r="E34">
+        <v>-799.96</v>
+      </c>
+      <c r="F34">
+        <v>1617.44</v>
+      </c>
+      <c r="G34">
+        <v>468.1</v>
+      </c>
+      <c r="H34">
+        <v>2637.1</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>318.1</v>
+      </c>
+      <c r="K34">
+        <v>542.8</v>
+      </c>
+      <c r="L34">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M34">
+        <v>386.244672</v>
+      </c>
+      <c r="N34">
+        <v>-610.944672</v>
+      </c>
+      <c r="O34">
+        <v>-146.62672128</v>
+      </c>
+      <c r="P34">
+        <v>-464.31795072</v>
+      </c>
+      <c r="Q34">
+        <v>78.48204927999996</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1628983966929408</v>
+      </c>
+      <c r="T34">
+        <v>1.278351708529752</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>-0.1396213434369393</v>
+      </c>
+      <c r="W34">
+        <v>0.2721415768127411</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>-0.5817555976539137</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1998562143312769</v>
+      </c>
+      <c r="C35">
+        <v>1155.602908971918</v>
+      </c>
+      <c r="D35">
+        <v>2355.487908971918</v>
+      </c>
+      <c r="E35">
+        <v>-749.415</v>
+      </c>
+      <c r="F35">
+        <v>1667.985</v>
+      </c>
+      <c r="G35">
+        <v>468.1</v>
+      </c>
+      <c r="H35">
+        <v>2637.1</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>318.1</v>
+      </c>
+      <c r="K35">
+        <v>542.8</v>
+      </c>
+      <c r="L35">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M35">
+        <v>398.3148180000001</v>
+      </c>
+      <c r="N35">
+        <v>-623.014818</v>
+      </c>
+      <c r="O35">
+        <v>-149.52355632</v>
+      </c>
+      <c r="P35">
+        <v>-473.49126168</v>
+      </c>
+      <c r="Q35">
+        <v>69.30873831999997</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1647506115689548</v>
+      </c>
+      <c r="T35">
+        <v>1.297431584776465</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>-0.1353903936358199</v>
+      </c>
+      <c r="W35">
+        <v>0.2711312260002338</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>-0.5641266401492497</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.2018562143312769</v>
+      </c>
+      <c r="C36">
+        <v>1076.166180819977</v>
+      </c>
+      <c r="D36">
+        <v>2326.596180819977</v>
+      </c>
+      <c r="E36">
+        <v>-698.8699999999999</v>
+      </c>
+      <c r="F36">
+        <v>1718.53</v>
+      </c>
+      <c r="G36">
+        <v>468.1</v>
+      </c>
+      <c r="H36">
+        <v>2637.1</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>318.1</v>
+      </c>
+      <c r="K36">
+        <v>542.8</v>
+      </c>
+      <c r="L36">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M36">
+        <v>410.3849640000001</v>
+      </c>
+      <c r="N36">
+        <v>-635.084964</v>
+      </c>
+      <c r="O36">
+        <v>-152.42039136</v>
+      </c>
+      <c r="P36">
+        <v>-482.66457264</v>
+      </c>
+      <c r="Q36">
+        <v>60.13542735999994</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1666589541684844</v>
+      </c>
+      <c r="T36">
+        <v>1.31708963909126</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>-0.1314083232347664</v>
+      </c>
+      <c r="W36">
+        <v>0.2701803075884622</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>-0.54753468014486</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2038562143312769</v>
+      </c>
+      <c r="C37">
+        <v>997.429619657059</v>
+      </c>
+      <c r="D37">
+        <v>2298.404619657059</v>
+      </c>
+      <c r="E37">
+        <v>-648.3249999999998</v>
+      </c>
+      <c r="F37">
+        <v>1769.075</v>
+      </c>
+      <c r="G37">
+        <v>468.1</v>
+      </c>
+      <c r="H37">
+        <v>2637.1</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>318.1</v>
+      </c>
+      <c r="K37">
+        <v>542.8</v>
+      </c>
+      <c r="L37">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M37">
+        <v>422.4551100000001</v>
+      </c>
+      <c r="N37">
+        <v>-647.15511</v>
+      </c>
+      <c r="O37">
+        <v>-155.3172264</v>
+      </c>
+      <c r="P37">
+        <v>-491.8378836000001</v>
+      </c>
+      <c r="Q37">
+        <v>50.9621163999999</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1686260150018457</v>
+      </c>
+      <c r="T37">
+        <v>1.337352556615741</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>-0.1276537997137731</v>
+      </c>
+      <c r="W37">
+        <v>0.269283727371649</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>-0.5318908321407212</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2058562143312769</v>
+      </c>
+      <c r="C38">
+        <v>919.3680782478386</v>
+      </c>
+      <c r="D38">
+        <v>2270.888078247839</v>
+      </c>
+      <c r="E38">
+        <v>-597.7800000000002</v>
+      </c>
+      <c r="F38">
+        <v>1819.62</v>
+      </c>
+      <c r="G38">
+        <v>468.1</v>
+      </c>
+      <c r="H38">
+        <v>2637.1</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>318.1</v>
+      </c>
+      <c r="K38">
+        <v>542.8</v>
+      </c>
+      <c r="L38">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M38">
+        <v>434.525256</v>
+      </c>
+      <c r="N38">
+        <v>-659.2252559999999</v>
+      </c>
+      <c r="O38">
+        <v>-158.21406144</v>
+      </c>
+      <c r="P38">
+        <v>-501.0111945599999</v>
+      </c>
+      <c r="Q38">
+        <v>41.78880544000003</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1706545464862496</v>
+      </c>
+      <c r="T38">
+        <v>1.358248690312862</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>-0.124107860832835</v>
+      </c>
+      <c r="W38">
+        <v>0.268436957166881</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>-0.517116086803479</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2078562143312769</v>
+      </c>
+      <c r="C39">
+        <v>841.957599362835</v>
+      </c>
+      <c r="D39">
+        <v>2244.022599362835</v>
+      </c>
+      <c r="E39">
+        <v>-547.2350000000001</v>
+      </c>
+      <c r="F39">
+        <v>1870.165</v>
+      </c>
+      <c r="G39">
+        <v>468.1</v>
+      </c>
+      <c r="H39">
+        <v>2637.1</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>318.1</v>
+      </c>
+      <c r="K39">
+        <v>542.8</v>
+      </c>
+      <c r="L39">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M39">
+        <v>446.595402</v>
+      </c>
+      <c r="N39">
+        <v>-671.295402</v>
+      </c>
+      <c r="O39">
+        <v>-161.11089648</v>
+      </c>
+      <c r="P39">
+        <v>-510.18450552</v>
+      </c>
+      <c r="Q39">
+        <v>32.61549447999994</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1727474757955551</v>
+      </c>
+      <c r="T39">
+        <v>1.379808193333701</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>-0.1207535943238394</v>
+      </c>
+      <c r="W39">
+        <v>0.2676359583245329</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>-0.5031399763493309</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2098562143312769</v>
+      </c>
+      <c r="C40">
+        <v>765.1753462102897</v>
+      </c>
+      <c r="D40">
+        <v>2217.78534621029</v>
+      </c>
+      <c r="E40">
+        <v>-496.6900000000001</v>
+      </c>
+      <c r="F40">
+        <v>1920.71</v>
+      </c>
+      <c r="G40">
+        <v>468.1</v>
+      </c>
+      <c r="H40">
+        <v>2637.1</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>318.1</v>
+      </c>
+      <c r="K40">
+        <v>542.8</v>
+      </c>
+      <c r="L40">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M40">
+        <v>458.6655480000001</v>
+      </c>
+      <c r="N40">
+        <v>-683.365548</v>
+      </c>
+      <c r="O40">
+        <v>-164.00773152</v>
+      </c>
+      <c r="P40">
+        <v>-519.35781648</v>
+      </c>
+      <c r="Q40">
+        <v>23.44218351999996</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.174907918953548</v>
+      </c>
+      <c r="T40">
+        <v>1.402063164193922</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>-0.1175758681574226</v>
+      </c>
+      <c r="W40">
+        <v>0.2668771173159925</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>-0.4898994506559273</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2118562143312769</v>
+      </c>
+      <c r="C41">
+        <v>688.999537692026</v>
+      </c>
+      <c r="D41">
+        <v>2192.154537692026</v>
+      </c>
+      <c r="E41">
+        <v>-446.145</v>
+      </c>
+      <c r="F41">
+        <v>1971.255</v>
+      </c>
+      <c r="G41">
+        <v>468.1</v>
+      </c>
+      <c r="H41">
+        <v>2637.1</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>318.1</v>
+      </c>
+      <c r="K41">
+        <v>542.8</v>
+      </c>
+      <c r="L41">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M41">
+        <v>470.735694</v>
+      </c>
+      <c r="N41">
+        <v>-695.435694</v>
+      </c>
+      <c r="O41">
+        <v>-166.90456656</v>
+      </c>
+      <c r="P41">
+        <v>-528.53112744</v>
+      </c>
+      <c r="Q41">
+        <v>14.26887255999998</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1771391963134421</v>
+      </c>
+      <c r="T41">
+        <v>1.425047806229887</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>-0.1145611023072323</v>
+      </c>
+      <c r="W41">
+        <v>0.266157191230967</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>-0.4773379262801345</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2138562143312769</v>
+      </c>
+      <c r="C42">
+        <v>613.4093880974665</v>
+      </c>
+      <c r="D42">
+        <v>2167.109388097467</v>
+      </c>
+      <c r="E42">
+        <v>-395.5999999999999</v>
+      </c>
+      <c r="F42">
+        <v>2021.8</v>
+      </c>
+      <c r="G42">
+        <v>468.1</v>
+      </c>
+      <c r="H42">
+        <v>2637.1</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>318.1</v>
+      </c>
+      <c r="K42">
+        <v>542.8</v>
+      </c>
+      <c r="L42">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M42">
+        <v>482.80584</v>
+      </c>
+      <c r="N42">
+        <v>-707.50584</v>
+      </c>
+      <c r="O42">
+        <v>-169.8014016</v>
+      </c>
+      <c r="P42">
+        <v>-537.7044384000001</v>
+      </c>
+      <c r="Q42">
+        <v>5.095561599999883</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1794448495853329</v>
+      </c>
+      <c r="T42">
+        <v>1.448798603000386</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>-0.1116970747495515</v>
+      </c>
+      <c r="W42">
+        <v>0.2654732614501929</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>-0.4654044781231312</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2158562143312769</v>
+      </c>
+      <c r="C43">
+        <v>538.3850508849046</v>
+      </c>
+      <c r="D43">
+        <v>2142.630050884905</v>
+      </c>
+      <c r="E43">
+        <v>-345.0549999999998</v>
+      </c>
+      <c r="F43">
+        <v>2072.345</v>
+      </c>
+      <c r="G43">
+        <v>468.1</v>
+      </c>
+      <c r="H43">
+        <v>2637.1</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>318.1</v>
+      </c>
+      <c r="K43">
+        <v>542.8</v>
+      </c>
+      <c r="L43">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M43">
+        <v>494.8759860000001</v>
+      </c>
+      <c r="N43">
+        <v>-719.5759860000001</v>
+      </c>
+      <c r="O43">
+        <v>-172.69823664</v>
+      </c>
+      <c r="P43">
+        <v>-546.8777493600001</v>
+      </c>
+      <c r="Q43">
+        <v>-4.077749360000098</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1818286605952538</v>
+      </c>
+      <c r="T43">
+        <v>1.473354511525816</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>-0.1089727558532209</v>
+      </c>
+      <c r="W43">
+        <v>0.2648226940977492</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>-0.4540531493884206</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2178562143312769</v>
+      </c>
+      <c r="C44">
+        <v>463.9075662304404</v>
+      </c>
+      <c r="D44">
+        <v>2118.69756623044</v>
+      </c>
+      <c r="E44">
+        <v>-294.5100000000002</v>
+      </c>
+      <c r="F44">
+        <v>2122.89</v>
+      </c>
+      <c r="G44">
+        <v>468.1</v>
+      </c>
+      <c r="H44">
+        <v>2637.1</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>318.1</v>
+      </c>
+      <c r="K44">
+        <v>542.8</v>
+      </c>
+      <c r="L44">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M44">
+        <v>506.946132</v>
+      </c>
+      <c r="N44">
+        <v>-731.6461319999999</v>
+      </c>
+      <c r="O44">
+        <v>-175.59507168</v>
+      </c>
+      <c r="P44">
+        <v>-556.0510603199999</v>
+      </c>
+      <c r="Q44">
+        <v>-13.25106031999997</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1842946719848271</v>
+      </c>
+      <c r="T44">
+        <v>1.49875717551764</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>-0.1063781664281443</v>
+      </c>
+      <c r="W44">
+        <v>0.2642031061430409</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>-0.4432423601172677</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2198562143312769</v>
+      </c>
+      <c r="C45">
+        <v>389.9588120532553</v>
+      </c>
+      <c r="D45">
+        <v>2095.293812053255</v>
+      </c>
+      <c r="E45">
+        <v>-243.9650000000001</v>
+      </c>
+      <c r="F45">
+        <v>2173.435</v>
+      </c>
+      <c r="G45">
+        <v>468.1</v>
+      </c>
+      <c r="H45">
+        <v>2637.1</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>318.1</v>
+      </c>
+      <c r="K45">
+        <v>542.8</v>
+      </c>
+      <c r="L45">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M45">
+        <v>519.0162780000001</v>
+      </c>
+      <c r="N45">
+        <v>-743.716278</v>
+      </c>
+      <c r="O45">
+        <v>-178.49190672</v>
+      </c>
+      <c r="P45">
+        <v>-565.22437128</v>
+      </c>
+      <c r="Q45">
+        <v>-22.42437128000006</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1868472100898241</v>
+      </c>
+      <c r="T45">
+        <v>1.525051161053038</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>-0.1039042555809781</v>
+      </c>
+      <c r="W45">
+        <v>0.2636123362327376</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>-0.4329343982540754</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2218562143312769</v>
+      </c>
+      <c r="C46">
+        <v>316.5214582513636</v>
+      </c>
+      <c r="D46">
+        <v>2072.401458251364</v>
+      </c>
+      <c r="E46">
+        <v>-193.4200000000001</v>
+      </c>
+      <c r="F46">
+        <v>2223.98</v>
+      </c>
+      <c r="G46">
+        <v>468.1</v>
+      </c>
+      <c r="H46">
+        <v>2637.1</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>318.1</v>
+      </c>
+      <c r="K46">
+        <v>542.8</v>
+      </c>
+      <c r="L46">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M46">
+        <v>531.0864240000001</v>
+      </c>
+      <c r="N46">
+        <v>-755.786424</v>
+      </c>
+      <c r="O46">
+        <v>-181.38874176</v>
+      </c>
+      <c r="P46">
+        <v>-574.39768224</v>
+      </c>
+      <c r="Q46">
+        <v>-31.59768224000004</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1894909102699995</v>
+      </c>
+      <c r="T46">
+        <v>1.552284217500413</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>-0.1015427952268649</v>
+      </c>
+      <c r="W46">
+        <v>0.2630484195001754</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>-0.4230949801119372</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2238562143312769</v>
+      </c>
+      <c r="C47">
+        <v>243.5789239049464</v>
+      </c>
+      <c r="D47">
+        <v>2050.003923904947</v>
+      </c>
+      <c r="E47">
+        <v>-142.875</v>
+      </c>
+      <c r="F47">
+        <v>2274.525</v>
+      </c>
+      <c r="G47">
+        <v>468.1</v>
+      </c>
+      <c r="H47">
+        <v>2637.1</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>318.1</v>
+      </c>
+      <c r="K47">
+        <v>542.8</v>
+      </c>
+      <c r="L47">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M47">
+        <v>543.1565700000001</v>
+      </c>
+      <c r="N47">
+        <v>-767.85657</v>
+      </c>
+      <c r="O47">
+        <v>-184.2855768</v>
+      </c>
+      <c r="P47">
+        <v>-583.5709932</v>
+      </c>
+      <c r="Q47">
+        <v>-40.77099320000002</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1922307450021813</v>
+      </c>
+      <c r="T47">
+        <v>1.580507566909512</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>-0.09928628866626794</v>
+      </c>
+      <c r="W47">
+        <v>0.2625095657335048</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>-0.4136928694427831</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2258562143312769</v>
+      </c>
+      <c r="C48">
+        <v>171.1153372251756</v>
+      </c>
+      <c r="D48">
+        <v>2028.085337225176</v>
+      </c>
+      <c r="E48">
+        <v>-92.32999999999993</v>
+      </c>
+      <c r="F48">
+        <v>2325.07</v>
+      </c>
+      <c r="G48">
+        <v>468.1</v>
+      </c>
+      <c r="H48">
+        <v>2637.1</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>318.1</v>
+      </c>
+      <c r="K48">
+        <v>542.8</v>
+      </c>
+      <c r="L48">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M48">
+        <v>555.2267160000001</v>
+      </c>
+      <c r="N48">
+        <v>-779.9267160000001</v>
+      </c>
+      <c r="O48">
+        <v>-187.18241184</v>
+      </c>
+      <c r="P48">
+        <v>-592.7443041600001</v>
+      </c>
+      <c r="Q48">
+        <v>-49.94430416000012</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1950720550948143</v>
+      </c>
+      <c r="T48">
+        <v>1.609776225555984</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>-0.09712789108656646</v>
+      </c>
+      <c r="W48">
+        <v>0.2619941403914721</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>-0.404699546194027</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2278562143312769</v>
+      </c>
+      <c r="C49">
+        <v>99.11549804521155</v>
+      </c>
+      <c r="D49">
+        <v>2006.630498045212</v>
+      </c>
+      <c r="E49">
+        <v>-41.78499999999985</v>
+      </c>
+      <c r="F49">
+        <v>2375.615</v>
+      </c>
+      <c r="G49">
+        <v>468.1</v>
+      </c>
+      <c r="H49">
+        <v>2637.1</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>318.1</v>
+      </c>
+      <c r="K49">
+        <v>542.8</v>
+      </c>
+      <c r="L49">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M49">
+        <v>567.296862</v>
+      </c>
+      <c r="N49">
+        <v>-791.996862</v>
+      </c>
+      <c r="O49">
+        <v>-190.07924688</v>
+      </c>
+      <c r="P49">
+        <v>-601.9176151199999</v>
+      </c>
+      <c r="Q49">
+        <v>-59.11761511999998</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1980205844362259</v>
+      </c>
+      <c r="T49">
+        <v>1.640149361887229</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>-0.09506134021238422</v>
+      </c>
+      <c r="W49">
+        <v>0.2615006480427174</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>-0.3960889175516009</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2298562143312769</v>
+      </c>
+      <c r="C50">
+        <v>27.56484266709504</v>
+      </c>
+      <c r="D50">
+        <v>1985.624842667095</v>
+      </c>
+      <c r="E50">
+        <v>8.759999999999764</v>
+      </c>
+      <c r="F50">
+        <v>2426.16</v>
+      </c>
+      <c r="G50">
+        <v>468.1</v>
+      </c>
+      <c r="H50">
+        <v>2637.1</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>318.1</v>
+      </c>
+      <c r="K50">
+        <v>542.8</v>
+      </c>
+      <c r="L50">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M50">
+        <v>579.3670079999999</v>
+      </c>
+      <c r="N50">
+        <v>-804.0670079999999</v>
+      </c>
+      <c r="O50">
+        <v>-192.97608192</v>
+      </c>
+      <c r="P50">
+        <v>-611.0909260799999</v>
+      </c>
+      <c r="Q50">
+        <v>-68.29092607999996</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2010825187523071</v>
+      </c>
+      <c r="T50">
+        <v>1.671690695769676</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>-0.09308089562462622</v>
+      </c>
+      <c r="W50">
+        <v>0.2610277178751608</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>-0.3878370651026093</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2318562143312769</v>
+      </c>
+      <c r="C51">
+        <v>-43.55058910631442</v>
+      </c>
+      <c r="D51">
+        <v>1965.054410893685</v>
+      </c>
+      <c r="E51">
+        <v>59.30499999999984</v>
+      </c>
+      <c r="F51">
+        <v>2476.705</v>
+      </c>
+      <c r="G51">
+        <v>468.1</v>
+      </c>
+      <c r="H51">
+        <v>2637.1</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>318.1</v>
+      </c>
+      <c r="K51">
+        <v>542.8</v>
+      </c>
+      <c r="L51">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M51">
+        <v>591.437154</v>
+      </c>
+      <c r="N51">
+        <v>-816.1371539999999</v>
+      </c>
+      <c r="O51">
+        <v>-195.87291696</v>
+      </c>
+      <c r="P51">
+        <v>-620.2642370399999</v>
+      </c>
+      <c r="Q51">
+        <v>-77.46423703999994</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.204264528923921</v>
+      </c>
+      <c r="T51">
+        <v>1.704468944706336</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>-0.09118128550983792</v>
+      </c>
+      <c r="W51">
+        <v>0.2605740909797493</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>-0.3799220229576581</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2338562143312769</v>
+      </c>
+      <c r="C52">
+        <v>-114.2441849111765</v>
+      </c>
+      <c r="D52">
+        <v>1944.905815088824</v>
+      </c>
+      <c r="E52">
+        <v>109.8499999999999</v>
+      </c>
+      <c r="F52">
+        <v>2527.25</v>
+      </c>
+      <c r="G52">
+        <v>468.1</v>
+      </c>
+      <c r="H52">
+        <v>2637.1</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>318.1</v>
+      </c>
+      <c r="K52">
+        <v>542.8</v>
+      </c>
+      <c r="L52">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M52">
+        <v>603.5073</v>
+      </c>
+      <c r="N52">
+        <v>-828.2072999999999</v>
+      </c>
+      <c r="O52">
+        <v>-198.769752</v>
+      </c>
+      <c r="P52">
+        <v>-629.4375479999999</v>
+      </c>
+      <c r="Q52">
+        <v>-86.63754799999992</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2075738195023994</v>
+      </c>
+      <c r="T52">
+        <v>1.738558323600463</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>-0.08935765979964116</v>
+      </c>
+      <c r="W52">
+        <v>0.2601386091601544</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>-0.3723235824985049</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2358562143312768</v>
+      </c>
+      <c r="C53">
+        <v>-184.5287888783887</v>
+      </c>
+      <c r="D53">
+        <v>1925.166211121611</v>
+      </c>
+      <c r="E53">
+        <v>160.395</v>
+      </c>
+      <c r="F53">
+        <v>2577.795</v>
+      </c>
+      <c r="G53">
+        <v>468.1</v>
+      </c>
+      <c r="H53">
+        <v>2637.1</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>318.1</v>
+      </c>
+      <c r="K53">
+        <v>542.8</v>
+      </c>
+      <c r="L53">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M53">
+        <v>615.577446</v>
+      </c>
+      <c r="N53">
+        <v>-840.2774459999999</v>
+      </c>
+      <c r="O53">
+        <v>-201.66658704</v>
+      </c>
+      <c r="P53">
+        <v>-638.61085896</v>
+      </c>
+      <c r="Q53">
+        <v>-95.81085896000002</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2110181831657137</v>
+      </c>
+      <c r="T53">
+        <v>1.774039105714758</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>-0.08760554882317761</v>
+      </c>
+      <c r="W53">
+        <v>0.2597202050589748</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>-0.3650231200965735</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2378562143312769</v>
+      </c>
+      <c r="C54">
+        <v>-254.4167289376996</v>
+      </c>
+      <c r="D54">
+        <v>1905.8232710623</v>
+      </c>
+      <c r="E54">
+        <v>210.9400000000001</v>
+      </c>
+      <c r="F54">
+        <v>2628.34</v>
+      </c>
+      <c r="G54">
+        <v>468.1</v>
+      </c>
+      <c r="H54">
+        <v>2637.1</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>318.1</v>
+      </c>
+      <c r="K54">
+        <v>542.8</v>
+      </c>
+      <c r="L54">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M54">
+        <v>627.647592</v>
+      </c>
+      <c r="N54">
+        <v>-852.347592</v>
+      </c>
+      <c r="O54">
+        <v>-204.56342208</v>
+      </c>
+      <c r="P54">
+        <v>-647.78416992</v>
+      </c>
+      <c r="Q54">
+        <v>-104.98416992</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2146060619816661</v>
+      </c>
+      <c r="T54">
+        <v>1.810998253750482</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>-0.0859208267304242</v>
+      </c>
+      <c r="W54">
+        <v>0.2593178934232253</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>-0.3580034447101008</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2398562143312769</v>
+      </c>
+      <c r="C55">
+        <v>-323.9198424921719</v>
+      </c>
+      <c r="D55">
+        <v>1886.865157507828</v>
+      </c>
+      <c r="E55">
+        <v>261.4850000000001</v>
+      </c>
+      <c r="F55">
+        <v>2678.885</v>
+      </c>
+      <c r="G55">
+        <v>468.1</v>
+      </c>
+      <c r="H55">
+        <v>2637.1</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>318.1</v>
+      </c>
+      <c r="K55">
+        <v>542.8</v>
+      </c>
+      <c r="L55">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M55">
+        <v>639.7177380000001</v>
+      </c>
+      <c r="N55">
+        <v>-864.417738</v>
+      </c>
+      <c r="O55">
+        <v>-207.46025712</v>
+      </c>
+      <c r="P55">
+        <v>-656.95748088</v>
+      </c>
+      <c r="Q55">
+        <v>-114.1574808800001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2183466164919143</v>
+      </c>
+      <c r="T55">
+        <v>1.849530131489855</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>-0.08429967905626524</v>
+      </c>
+      <c r="W55">
+        <v>0.2589307633586362</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>-0.3512486627344384</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2418562143312769</v>
+      </c>
+      <c r="C56">
+        <v>-393.0495005753719</v>
+      </c>
+      <c r="D56">
+        <v>1868.280499424628</v>
+      </c>
+      <c r="E56">
+        <v>312.0300000000002</v>
+      </c>
+      <c r="F56">
+        <v>2729.43</v>
+      </c>
+      <c r="G56">
+        <v>468.1</v>
+      </c>
+      <c r="H56">
+        <v>2637.1</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>318.1</v>
+      </c>
+      <c r="K56">
+        <v>542.8</v>
+      </c>
+      <c r="L56">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M56">
+        <v>651.7878840000001</v>
+      </c>
+      <c r="N56">
+        <v>-876.487884</v>
+      </c>
+      <c r="O56">
+        <v>-210.35709216</v>
+      </c>
+      <c r="P56">
+        <v>-666.13079184</v>
+      </c>
+      <c r="Q56">
+        <v>-123.3307918400001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2222498038069559</v>
+      </c>
+      <c r="T56">
+        <v>1.889737308261373</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>-0.08273857388855663</v>
+      </c>
+      <c r="W56">
+        <v>0.2585579714445874</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>-0.344744057868986</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2438562143312769</v>
+      </c>
+      <c r="C57">
+        <v>-461.816630594863</v>
+      </c>
+      <c r="D57">
+        <v>1850.058369405137</v>
+      </c>
+      <c r="E57">
+        <v>362.5750000000003</v>
+      </c>
+      <c r="F57">
+        <v>2779.975</v>
+      </c>
+      <c r="G57">
+        <v>468.1</v>
+      </c>
+      <c r="H57">
+        <v>2637.1</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>318.1</v>
+      </c>
+      <c r="K57">
+        <v>542.8</v>
+      </c>
+      <c r="L57">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M57">
+        <v>663.8580300000001</v>
+      </c>
+      <c r="N57">
+        <v>-888.55803</v>
+      </c>
+      <c r="O57">
+        <v>-213.2539272</v>
+      </c>
+      <c r="P57">
+        <v>-675.3041028</v>
+      </c>
+      <c r="Q57">
+        <v>-132.5041028000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2263264661137772</v>
+      </c>
+      <c r="T57">
+        <v>1.931731470667181</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>-0.08123423618149195</v>
+      </c>
+      <c r="W57">
+        <v>0.2581987356001403</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>-0.3384759840895499</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2458562143312769</v>
+      </c>
+      <c r="C58">
+        <v>-530.2317377575987</v>
+      </c>
+      <c r="D58">
+        <v>1832.188262242402</v>
+      </c>
+      <c r="E58">
+        <v>413.1200000000003</v>
+      </c>
+      <c r="F58">
+        <v>2830.52</v>
+      </c>
+      <c r="G58">
+        <v>468.1</v>
+      </c>
+      <c r="H58">
+        <v>2637.1</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>318.1</v>
+      </c>
+      <c r="K58">
+        <v>542.8</v>
+      </c>
+      <c r="L58">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M58">
+        <v>675.9281760000001</v>
+      </c>
+      <c r="N58">
+        <v>-900.6281760000001</v>
+      </c>
+      <c r="O58">
+        <v>-216.15076224</v>
+      </c>
+      <c r="P58">
+        <v>-684.47741376</v>
+      </c>
+      <c r="Q58">
+        <v>-141.67741376</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2305884312527266</v>
+      </c>
+      <c r="T58">
+        <v>1.97563445863689</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>-0.07978362482110817</v>
+      </c>
+      <c r="W58">
+        <v>0.2578523296072806</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>-0.3324317700879507</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2478562143312769</v>
+      </c>
+      <c r="C59">
+        <v>-598.3049252654728</v>
+      </c>
+      <c r="D59">
+        <v>1814.660074734528</v>
+      </c>
+      <c r="E59">
+        <v>463.6650000000004</v>
+      </c>
+      <c r="F59">
+        <v>2881.065000000001</v>
+      </c>
+      <c r="G59">
+        <v>468.1</v>
+      </c>
+      <c r="H59">
+        <v>2637.1</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>318.1</v>
+      </c>
+      <c r="K59">
+        <v>542.8</v>
+      </c>
+      <c r="L59">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M59">
+        <v>687.9983220000001</v>
+      </c>
+      <c r="N59">
+        <v>-912.6983220000001</v>
+      </c>
+      <c r="O59">
+        <v>-219.04759728</v>
+      </c>
+      <c r="P59">
+        <v>-693.6507247200001</v>
+      </c>
+      <c r="Q59">
+        <v>-150.8507247200001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2350486273283715</v>
+      </c>
+      <c r="T59">
+        <v>2.02157944604705</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>-0.07838391210494837</v>
+      </c>
+      <c r="W59">
+        <v>0.2575180782106617</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>-0.3265996337706183</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2498562143312769</v>
+      </c>
+      <c r="C60">
+        <v>-666.0459133626164</v>
+      </c>
+      <c r="D60">
+        <v>1797.464086637383</v>
+      </c>
+      <c r="E60">
+        <v>514.2099999999996</v>
+      </c>
+      <c r="F60">
+        <v>2931.61</v>
+      </c>
+      <c r="G60">
+        <v>468.1</v>
+      </c>
+      <c r="H60">
+        <v>2637.1</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>318.1</v>
+      </c>
+      <c r="K60">
+        <v>542.8</v>
+      </c>
+      <c r="L60">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M60">
+        <v>700.0684679999999</v>
+      </c>
+      <c r="N60">
+        <v>-924.7684679999999</v>
+      </c>
+      <c r="O60">
+        <v>-221.9444323199999</v>
+      </c>
+      <c r="P60">
+        <v>-702.82403568</v>
+      </c>
+      <c r="Q60">
+        <v>-160.02403568</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2397212136933327</v>
+      </c>
+      <c r="T60">
+        <v>2.069712290000551</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>-0.07703246534451826</v>
+      </c>
+      <c r="W60">
+        <v>0.257195352724271</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>-0.3209686056021595</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2518562143312769</v>
+      </c>
+      <c r="C61">
+        <v>-733.4640573098991</v>
+      </c>
+      <c r="D61">
+        <v>1780.590942690101</v>
+      </c>
+      <c r="E61">
+        <v>564.7549999999997</v>
+      </c>
+      <c r="F61">
+        <v>2982.155</v>
+      </c>
+      <c r="G61">
+        <v>468.1</v>
+      </c>
+      <c r="H61">
+        <v>2637.1</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>318.1</v>
+      </c>
+      <c r="K61">
+        <v>542.8</v>
+      </c>
+      <c r="L61">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M61">
+        <v>712.138614</v>
+      </c>
+      <c r="N61">
+        <v>-936.8386139999999</v>
+      </c>
+      <c r="O61">
+        <v>-224.84126736</v>
+      </c>
+      <c r="P61">
+        <v>-711.9973466399999</v>
+      </c>
+      <c r="Q61">
+        <v>-169.19734664</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2446217311004871</v>
+      </c>
+      <c r="T61">
+        <v>2.12019307756154</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>-0.07572683033867895</v>
+      </c>
+      <c r="W61">
+        <v>0.2568835670848765</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>-0.3155284597444956</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2538562143312768</v>
+      </c>
+      <c r="C62">
+        <v>-800.568364356448</v>
+      </c>
+      <c r="D62">
+        <v>1764.031635643552</v>
+      </c>
+      <c r="E62">
+        <v>615.2999999999997</v>
+      </c>
+      <c r="F62">
+        <v>3032.7</v>
+      </c>
+      <c r="G62">
+        <v>468.1</v>
+      </c>
+      <c r="H62">
+        <v>2637.1</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>318.1</v>
+      </c>
+      <c r="K62">
+        <v>542.8</v>
+      </c>
+      <c r="L62">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M62">
+        <v>724.20876</v>
+      </c>
+      <c r="N62">
+        <v>-948.9087599999999</v>
+      </c>
+      <c r="O62">
+        <v>-227.7381024</v>
+      </c>
+      <c r="P62">
+        <v>-721.1706575999999</v>
+      </c>
+      <c r="Q62">
+        <v>-178.3706576</v>
+      </c>
+      <c r="R62">
         <v>1.5</v>
       </c>
-      <c r="AH4">
-        <v>0.2187062447493699</v>
-      </c>
-      <c r="AI4">
-        <v>0.5408587257617729</v>
-      </c>
-      <c r="AJ4">
-        <v>0.05102040816326531</v>
-      </c>
-      <c r="AK4">
-        <v>0.1845018450184502</v>
-      </c>
-      <c r="AL4">
-        <v>0.081</v>
-      </c>
-      <c r="AM4">
-        <v>0.081</v>
-      </c>
-      <c r="AN4">
-        <v>-7.438095238095237</v>
-      </c>
-      <c r="AO4">
-        <v>-16.54320987654321</v>
-      </c>
-      <c r="AP4">
-        <v>-1.428571428571429</v>
-      </c>
-      <c r="AQ4">
-        <v>-16.54320987654321</v>
+      <c r="S62">
+        <v>0.2497672743779992</v>
+      </c>
+      <c r="T62">
+        <v>2.173197904500578</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>-0.07446471649970098</v>
+      </c>
+      <c r="W62">
+        <v>0.2565821743001286</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>-0.3102696520820873</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2558562143312769</v>
+      </c>
+      <c r="C63">
+        <v>-867.3675097729097</v>
+      </c>
+      <c r="D63">
+        <v>1747.77749022709</v>
+      </c>
+      <c r="E63">
+        <v>665.8449999999998</v>
+      </c>
+      <c r="F63">
+        <v>3083.245</v>
+      </c>
+      <c r="G63">
+        <v>468.1</v>
+      </c>
+      <c r="H63">
+        <v>2637.1</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>318.1</v>
+      </c>
+      <c r="K63">
+        <v>542.8</v>
+      </c>
+      <c r="L63">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M63">
+        <v>736.278906</v>
+      </c>
+      <c r="N63">
+        <v>-960.9789059999999</v>
+      </c>
+      <c r="O63">
+        <v>-230.63493744</v>
+      </c>
+      <c r="P63">
+        <v>-730.3439685599999</v>
+      </c>
+      <c r="Q63">
+        <v>-187.5439685599999</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2551766916697429</v>
+      </c>
+      <c r="T63">
+        <v>2.228920927692901</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>-0.07324398344232882</v>
+      </c>
+      <c r="W63">
+        <v>0.2562906632460281</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>-0.3051832643430368</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2578562143312769</v>
+      </c>
+      <c r="C64">
+        <v>-933.8698520063876</v>
+      </c>
+      <c r="D64">
+        <v>1731.820147993612</v>
+      </c>
+      <c r="E64">
+        <v>716.3899999999999</v>
+      </c>
+      <c r="F64">
+        <v>3133.79</v>
+      </c>
+      <c r="G64">
+        <v>468.1</v>
+      </c>
+      <c r="H64">
+        <v>2637.1</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>318.1</v>
+      </c>
+      <c r="K64">
+        <v>542.8</v>
+      </c>
+      <c r="L64">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M64">
+        <v>748.349052</v>
+      </c>
+      <c r="N64">
+        <v>-973.049052</v>
+      </c>
+      <c r="O64">
+        <v>-233.53177248</v>
+      </c>
+      <c r="P64">
+        <v>-739.51727952</v>
+      </c>
+      <c r="Q64">
+        <v>-196.71727952</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2608708151347361</v>
+      </c>
+      <c r="T64">
+        <v>2.287576741579556</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>-0.07206262887067837</v>
+      </c>
+      <c r="W64">
+        <v>0.256008555774318</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>-0.3002609536278265</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2598562143312769</v>
+      </c>
+      <c r="C65">
+        <v>-1000.083447012708</v>
+      </c>
+      <c r="D65">
+        <v>1716.151552987292</v>
+      </c>
+      <c r="E65">
+        <v>766.9349999999999</v>
+      </c>
+      <c r="F65">
+        <v>3184.335</v>
+      </c>
+      <c r="G65">
+        <v>468.1</v>
+      </c>
+      <c r="H65">
+        <v>2637.1</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>318.1</v>
+      </c>
+      <c r="K65">
+        <v>542.8</v>
+      </c>
+      <c r="L65">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M65">
+        <v>760.4191980000001</v>
+      </c>
+      <c r="N65">
+        <v>-985.119198</v>
+      </c>
+      <c r="O65">
+        <v>-236.42860752</v>
+      </c>
+      <c r="P65">
+        <v>-748.69059048</v>
+      </c>
+      <c r="Q65">
+        <v>-205.89059048</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2668727290572965</v>
+      </c>
+      <c r="T65">
+        <v>2.349403140000626</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>-0.07091877761876283</v>
+      </c>
+      <c r="W65">
+        <v>0.2557354040953606</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>-0.2954949067448451</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2618562143312769</v>
+      </c>
+      <c r="C66">
+        <v>-1066.016061817634</v>
+      </c>
+      <c r="D66">
+        <v>1700.763938182366</v>
+      </c>
+      <c r="E66">
+        <v>817.48</v>
+      </c>
+      <c r="F66">
+        <v>3234.88</v>
+      </c>
+      <c r="G66">
+        <v>468.1</v>
+      </c>
+      <c r="H66">
+        <v>2637.1</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>318.1</v>
+      </c>
+      <c r="K66">
+        <v>542.8</v>
+      </c>
+      <c r="L66">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M66">
+        <v>772.4893440000001</v>
+      </c>
+      <c r="N66">
+        <v>-997.189344</v>
+      </c>
+      <c r="O66">
+        <v>-239.32544256</v>
+      </c>
+      <c r="P66">
+        <v>-757.8639014400001</v>
+      </c>
+      <c r="Q66">
+        <v>-215.0639014400001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2732080826422215</v>
+      </c>
+      <c r="T66">
+        <v>2.414664338333977</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>-0.06981067171846965</v>
+      </c>
+      <c r="W66">
+        <v>0.2554707884063706</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>-0.2908777988269569</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2638562143312769</v>
+      </c>
+      <c r="C67">
+        <v>-1131.675187354989</v>
+      </c>
+      <c r="D67">
+        <v>1685.649812645011</v>
+      </c>
+      <c r="E67">
+        <v>868.0250000000001</v>
+      </c>
+      <c r="F67">
+        <v>3285.425</v>
+      </c>
+      <c r="G67">
+        <v>468.1</v>
+      </c>
+      <c r="H67">
+        <v>2637.1</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>318.1</v>
+      </c>
+      <c r="K67">
+        <v>542.8</v>
+      </c>
+      <c r="L67">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M67">
+        <v>784.5594900000001</v>
+      </c>
+      <c r="N67">
+        <v>-1009.25949</v>
+      </c>
+      <c r="O67">
+        <v>-242.2222776</v>
+      </c>
+      <c r="P67">
+        <v>-767.0372124</v>
+      </c>
+      <c r="Q67">
+        <v>-224.2372124000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2799054564319993</v>
+      </c>
+      <c r="T67">
+        <v>2.483654748000662</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>-0.06873666138433936</v>
+      </c>
+      <c r="W67">
+        <v>0.2552143147385803</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>-0.2864027557680806</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2658562143312769</v>
+      </c>
+      <c r="C68">
+        <v>-1197.06805062629</v>
+      </c>
+      <c r="D68">
+        <v>1670.80194937371</v>
+      </c>
+      <c r="E68">
+        <v>918.5700000000002</v>
+      </c>
+      <c r="F68">
+        <v>3335.97</v>
+      </c>
+      <c r="G68">
+        <v>468.1</v>
+      </c>
+      <c r="H68">
+        <v>2637.1</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>318.1</v>
+      </c>
+      <c r="K68">
+        <v>542.8</v>
+      </c>
+      <c r="L68">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M68">
+        <v>796.6296360000001</v>
+      </c>
+      <c r="N68">
+        <v>-1021.329636</v>
+      </c>
+      <c r="O68">
+        <v>-245.11911264</v>
+      </c>
+      <c r="P68">
+        <v>-776.21052336</v>
+      </c>
+      <c r="Q68">
+        <v>-233.4105233600001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2869967933858816</v>
+      </c>
+      <c r="T68">
+        <v>2.556703417059504</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>-0.06769519681790996</v>
+      </c>
+      <c r="W68">
+        <v>0.2549656130001169</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>-0.2820633200746248</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2678562143312769</v>
+      </c>
+      <c r="C69">
+        <v>-1262.201626223346</v>
+      </c>
+      <c r="D69">
+        <v>1656.213373776654</v>
+      </c>
+      <c r="E69">
+        <v>969.1150000000002</v>
+      </c>
+      <c r="F69">
+        <v>3386.515</v>
+      </c>
+      <c r="G69">
+        <v>468.1</v>
+      </c>
+      <c r="H69">
+        <v>2637.1</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>318.1</v>
+      </c>
+      <c r="K69">
+        <v>542.8</v>
+      </c>
+      <c r="L69">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M69">
+        <v>808.6997820000001</v>
+      </c>
+      <c r="N69">
+        <v>-1033.399782</v>
+      </c>
+      <c r="O69">
+        <v>-248.01594768</v>
+      </c>
+      <c r="P69">
+        <v>-785.38383432</v>
+      </c>
+      <c r="Q69">
+        <v>-242.5838343200001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2945179083369689</v>
+      </c>
+      <c r="T69">
+        <v>2.63417927818252</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>-0.06668482074600086</v>
+      </c>
+      <c r="W69">
+        <v>0.254724335194145</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>-0.2778534197750036</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2698562143312769</v>
+      </c>
+      <c r="C70">
+        <v>-1327.082647252429</v>
+      </c>
+      <c r="D70">
+        <v>1641.877352747571</v>
+      </c>
+      <c r="E70">
+        <v>1019.66</v>
+      </c>
+      <c r="F70">
+        <v>3437.06</v>
+      </c>
+      <c r="G70">
+        <v>468.1</v>
+      </c>
+      <c r="H70">
+        <v>2637.1</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>318.1</v>
+      </c>
+      <c r="K70">
+        <v>542.8</v>
+      </c>
+      <c r="L70">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M70">
+        <v>820.7699280000002</v>
+      </c>
+      <c r="N70">
+        <v>-1045.469928</v>
+      </c>
+      <c r="O70">
+        <v>-250.91278272</v>
+      </c>
+      <c r="P70">
+        <v>-794.55714528</v>
+      </c>
+      <c r="Q70">
+        <v>-251.75714528</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3025090929724992</v>
+      </c>
+      <c r="T70">
+        <v>2.716497380625724</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>-0.0657041616173832</v>
+      </c>
+      <c r="W70">
+        <v>0.2544901537942311</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>-0.2737673400724299</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2718562143312769</v>
+      </c>
+      <c r="C71">
+        <v>-1391.717615695954</v>
+      </c>
+      <c r="D71">
+        <v>1627.787384304046</v>
+      </c>
+      <c r="E71">
+        <v>1070.205</v>
+      </c>
+      <c r="F71">
+        <v>3487.605</v>
+      </c>
+      <c r="G71">
+        <v>468.1</v>
+      </c>
+      <c r="H71">
+        <v>2637.1</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>318.1</v>
+      </c>
+      <c r="K71">
+        <v>542.8</v>
+      </c>
+      <c r="L71">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M71">
+        <v>832.8400740000002</v>
+      </c>
+      <c r="N71">
+        <v>-1057.540074</v>
+      </c>
+      <c r="O71">
+        <v>-253.80961776</v>
+      </c>
+      <c r="P71">
+        <v>-803.73045624</v>
+      </c>
+      <c r="Q71">
+        <v>-260.93045624</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3110158379070959</v>
+      </c>
+      <c r="T71">
+        <v>2.804126328387844</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>-0.06475192739104431</v>
+      </c>
+      <c r="W71">
+        <v>0.2542627602609814</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>-0.2697996974626844</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2738562143312768</v>
+      </c>
+      <c r="C72">
+        <v>-1456.112812245192</v>
+      </c>
+      <c r="D72">
+        <v>1613.937187754809</v>
+      </c>
+      <c r="E72">
+        <v>1120.75</v>
+      </c>
+      <c r="F72">
+        <v>3538.150000000001</v>
+      </c>
+      <c r="G72">
+        <v>468.1</v>
+      </c>
+      <c r="H72">
+        <v>2637.1</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>318.1</v>
+      </c>
+      <c r="K72">
+        <v>542.8</v>
+      </c>
+      <c r="L72">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M72">
+        <v>844.9102200000002</v>
+      </c>
+      <c r="N72">
+        <v>-1069.61022</v>
+      </c>
+      <c r="O72">
+        <v>-256.7064528</v>
+      </c>
+      <c r="P72">
+        <v>-812.9037671999999</v>
+      </c>
+      <c r="Q72">
+        <v>-270.1037672</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3200896991706658</v>
+      </c>
+      <c r="T72">
+        <v>2.897597206000772</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>-0.06382689985688653</v>
+      </c>
+      <c r="W72">
+        <v>0.2540418636858245</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>-0.2659454160703605</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2758562143312768</v>
+      </c>
+      <c r="C73">
+        <v>-1520.274305635231</v>
+      </c>
+      <c r="D73">
+        <v>1600.320694364769</v>
+      </c>
+      <c r="E73">
+        <v>1171.295</v>
+      </c>
+      <c r="F73">
+        <v>3588.695</v>
+      </c>
+      <c r="G73">
+        <v>468.1</v>
+      </c>
+      <c r="H73">
+        <v>2637.1</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>318.1</v>
+      </c>
+      <c r="K73">
+        <v>542.8</v>
+      </c>
+      <c r="L73">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M73">
+        <v>856.980366</v>
+      </c>
+      <c r="N73">
+        <v>-1081.680366</v>
+      </c>
+      <c r="O73">
+        <v>-259.60328784</v>
+      </c>
+      <c r="P73">
+        <v>-822.07707816</v>
+      </c>
+      <c r="Q73">
+        <v>-279.2770781600001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3297893439696541</v>
+      </c>
+      <c r="T73">
+        <v>2.997514351035281</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>-0.06292792943636702</v>
+      </c>
+      <c r="W73">
+        <v>0.2538271895494044</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>-0.2621997059848626</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2778562143312769</v>
+      </c>
+      <c r="C74">
+        <v>-1584.207961511352</v>
+      </c>
+      <c r="D74">
+        <v>1586.932038488648</v>
+      </c>
+      <c r="E74">
+        <v>1221.84</v>
+      </c>
+      <c r="F74">
+        <v>3639.24</v>
+      </c>
+      <c r="G74">
+        <v>468.1</v>
+      </c>
+      <c r="H74">
+        <v>2637.1</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>318.1</v>
+      </c>
+      <c r="K74">
+        <v>542.8</v>
+      </c>
+      <c r="L74">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M74">
+        <v>869.050512</v>
+      </c>
+      <c r="N74">
+        <v>-1093.750512</v>
+      </c>
+      <c r="O74">
+        <v>-262.50012288</v>
+      </c>
+      <c r="P74">
+        <v>-831.2503891200001</v>
+      </c>
+      <c r="Q74">
+        <v>-288.4503891200002</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.340181820539999</v>
+      </c>
+      <c r="T74">
+        <v>3.104568435000826</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>-0.06205393041641748</v>
+      </c>
+      <c r="W74">
+        <v>0.2536184785834405</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>-0.2585580434017396</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2798562143312768</v>
+      </c>
+      <c r="C75">
+        <v>-1647.919450854022</v>
+      </c>
+      <c r="D75">
+        <v>1573.765549145978</v>
+      </c>
+      <c r="E75">
+        <v>1272.385</v>
+      </c>
+      <c r="F75">
+        <v>3689.785</v>
+      </c>
+      <c r="G75">
+        <v>468.1</v>
+      </c>
+      <c r="H75">
+        <v>2637.1</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>318.1</v>
+      </c>
+      <c r="K75">
+        <v>542.8</v>
+      </c>
+      <c r="L75">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M75">
+        <v>881.120658</v>
+      </c>
+      <c r="N75">
+        <v>-1105.820658</v>
+      </c>
+      <c r="O75">
+        <v>-265.39695792</v>
+      </c>
+      <c r="P75">
+        <v>-840.4237000800001</v>
+      </c>
+      <c r="Q75">
+        <v>-297.6237000800002</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3513441101896285</v>
+      </c>
+      <c r="T75">
+        <v>3.219552451111968</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>-0.06120387657509669</v>
+      </c>
+      <c r="W75">
+        <v>0.2534154857261331</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>-0.2550161523962364</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2818562143312769</v>
+      </c>
+      <c r="C76">
+        <v>-1711.414257987947</v>
+      </c>
+      <c r="D76">
+        <v>1560.815742012053</v>
+      </c>
+      <c r="E76">
+        <v>1322.93</v>
+      </c>
+      <c r="F76">
+        <v>3740.33</v>
+      </c>
+      <c r="G76">
+        <v>468.1</v>
+      </c>
+      <c r="H76">
+        <v>2637.1</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>318.1</v>
+      </c>
+      <c r="K76">
+        <v>542.8</v>
+      </c>
+      <c r="L76">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M76">
+        <v>893.1908040000001</v>
+      </c>
+      <c r="N76">
+        <v>-1117.890804</v>
+      </c>
+      <c r="O76">
+        <v>-268.29379296</v>
+      </c>
+      <c r="P76">
+        <v>-849.5970110400001</v>
+      </c>
+      <c r="Q76">
+        <v>-306.7970110400001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3633650375046143</v>
+      </c>
+      <c r="T76">
+        <v>3.343381391539352</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>-0.0603767971619197</v>
+      </c>
+      <c r="W76">
+        <v>0.2532179791622665</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>-0.2515699881746656</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2838562143312769</v>
+      </c>
+      <c r="C77">
+        <v>-1774.69768819892</v>
+      </c>
+      <c r="D77">
+        <v>1548.07731180108</v>
+      </c>
+      <c r="E77">
+        <v>1373.475</v>
+      </c>
+      <c r="F77">
+        <v>3790.875</v>
+      </c>
+      <c r="G77">
+        <v>468.1</v>
+      </c>
+      <c r="H77">
+        <v>2637.1</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>318.1</v>
+      </c>
+      <c r="K77">
+        <v>542.8</v>
+      </c>
+      <c r="L77">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M77">
+        <v>905.2609500000001</v>
+      </c>
+      <c r="N77">
+        <v>-1129.96095</v>
+      </c>
+      <c r="O77">
+        <v>-271.190628</v>
+      </c>
+      <c r="P77">
+        <v>-858.7703220000001</v>
+      </c>
+      <c r="Q77">
+        <v>-315.9703220000001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3763476390047989</v>
+      </c>
+      <c r="T77">
+        <v>3.477116647200926</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>-0.05957177319976077</v>
+      </c>
+      <c r="W77">
+        <v>0.2530257394401029</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>-0.24821572166567</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2858562143312769</v>
+      </c>
+      <c r="C78">
+        <v>-1837.774874980713</v>
+      </c>
+      <c r="D78">
+        <v>1535.545125019287</v>
+      </c>
+      <c r="E78">
+        <v>1424.02</v>
+      </c>
+      <c r="F78">
+        <v>3841.42</v>
+      </c>
+      <c r="G78">
+        <v>468.1</v>
+      </c>
+      <c r="H78">
+        <v>2637.1</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>318.1</v>
+      </c>
+      <c r="K78">
+        <v>542.8</v>
+      </c>
+      <c r="L78">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M78">
+        <v>917.3310960000001</v>
+      </c>
+      <c r="N78">
+        <v>-1142.031096</v>
+      </c>
+      <c r="O78">
+        <v>-274.08746304</v>
+      </c>
+      <c r="P78">
+        <v>-867.9436329600001</v>
+      </c>
+      <c r="Q78">
+        <v>-325.1436329600001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3904121239633322</v>
+      </c>
+      <c r="T78">
+        <v>3.621996507500965</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>-0.05878793407871128</v>
+      </c>
+      <c r="W78">
+        <v>0.2528385586579963</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>-0.2449497253279638</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2878562143312769</v>
+      </c>
+      <c r="C79">
+        <v>-1900.650786932798</v>
+      </c>
+      <c r="D79">
+        <v>1523.214213067202</v>
+      </c>
+      <c r="E79">
+        <v>1474.565</v>
+      </c>
+      <c r="F79">
+        <v>3891.965</v>
+      </c>
+      <c r="G79">
+        <v>468.1</v>
+      </c>
+      <c r="H79">
+        <v>2637.1</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>318.1</v>
+      </c>
+      <c r="K79">
+        <v>542.8</v>
+      </c>
+      <c r="L79">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M79">
+        <v>929.4012420000001</v>
+      </c>
+      <c r="N79">
+        <v>-1154.101242</v>
+      </c>
+      <c r="O79">
+        <v>-276.98429808</v>
+      </c>
+      <c r="P79">
+        <v>-877.1169439200002</v>
+      </c>
+      <c r="Q79">
+        <v>-334.3169439200002</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4056996076139118</v>
+      </c>
+      <c r="T79">
+        <v>3.779474616522746</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>-0.0580244544153514</v>
+      </c>
+      <c r="W79">
+        <v>0.2526562397143859</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>-0.2417685600639643</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2898562143312768</v>
+      </c>
+      <c r="C80">
+        <v>-1963.33023432837</v>
+      </c>
+      <c r="D80">
+        <v>1511.07976567163</v>
+      </c>
+      <c r="E80">
+        <v>1525.11</v>
+      </c>
+      <c r="F80">
+        <v>3942.51</v>
+      </c>
+      <c r="G80">
+        <v>468.1</v>
+      </c>
+      <c r="H80">
+        <v>2637.1</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>318.1</v>
+      </c>
+      <c r="K80">
+        <v>542.8</v>
+      </c>
+      <c r="L80">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M80">
+        <v>941.471388</v>
+      </c>
+      <c r="N80">
+        <v>-1166.171388</v>
+      </c>
+      <c r="O80">
+        <v>-279.88113312</v>
+      </c>
+      <c r="P80">
+        <v>-886.29025488</v>
+      </c>
+      <c r="Q80">
+        <v>-343.4902548800001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.4223768625054533</v>
+      </c>
+      <c r="T80">
+        <v>3.951268917273779</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>-0.05728055115361613</v>
+      </c>
+      <c r="W80">
+        <v>0.2524785956154835</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>-0.2386689631400671</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2918562143312769</v>
+      </c>
+      <c r="C81">
+        <v>-2025.817875370913</v>
+      </c>
+      <c r="D81">
+        <v>1499.137124629087</v>
+      </c>
+      <c r="E81">
+        <v>1575.655</v>
+      </c>
+      <c r="F81">
+        <v>3993.055</v>
+      </c>
+      <c r="G81">
+        <v>468.1</v>
+      </c>
+      <c r="H81">
+        <v>2637.1</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>318.1</v>
+      </c>
+      <c r="K81">
+        <v>542.8</v>
+      </c>
+      <c r="L81">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M81">
+        <v>953.5415340000001</v>
+      </c>
+      <c r="N81">
+        <v>-1178.241534</v>
+      </c>
+      <c r="O81">
+        <v>-282.77796816</v>
+      </c>
+      <c r="P81">
+        <v>-895.46356584</v>
+      </c>
+      <c r="Q81">
+        <v>-352.66356584</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4406424273866654</v>
+      </c>
+      <c r="T81">
+        <v>4.139424580001103</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>-0.05655548088584883</v>
+      </c>
+      <c r="W81">
+        <v>0.2523054488355407</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>-0.2356478370243702</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2938562143312769</v>
+      </c>
+      <c r="C82">
+        <v>-2088.118222156402</v>
+      </c>
+      <c r="D82">
+        <v>1487.381777843598</v>
+      </c>
+      <c r="E82">
+        <v>1626.2</v>
+      </c>
+      <c r="F82">
+        <v>4043.6</v>
+      </c>
+      <c r="G82">
+        <v>468.1</v>
+      </c>
+      <c r="H82">
+        <v>2637.1</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>318.1</v>
+      </c>
+      <c r="K82">
+        <v>542.8</v>
+      </c>
+      <c r="L82">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M82">
+        <v>965.6116800000001</v>
+      </c>
+      <c r="N82">
+        <v>-1190.31168</v>
+      </c>
+      <c r="O82">
+        <v>-285.6748032</v>
+      </c>
+      <c r="P82">
+        <v>-904.6368768</v>
+      </c>
+      <c r="Q82">
+        <v>-361.8368768</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4607345487559986</v>
+      </c>
+      <c r="T82">
+        <v>4.346395809001158</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>-0.05584853737477573</v>
+      </c>
+      <c r="W82">
+        <v>0.2521366307250965</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>-0.2327022390615656</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2958562143312769</v>
+      </c>
+      <c r="C83">
+        <v>-2150.235646357179</v>
+      </c>
+      <c r="D83">
+        <v>1475.809353642822</v>
+      </c>
+      <c r="E83">
+        <v>1676.745</v>
+      </c>
+      <c r="F83">
+        <v>4094.145</v>
+      </c>
+      <c r="G83">
+        <v>468.1</v>
+      </c>
+      <c r="H83">
+        <v>2637.1</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>318.1</v>
+      </c>
+      <c r="K83">
+        <v>542.8</v>
+      </c>
+      <c r="L83">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M83">
+        <v>977.6818260000001</v>
+      </c>
+      <c r="N83">
+        <v>-1202.381826</v>
+      </c>
+      <c r="O83">
+        <v>-288.57163824</v>
+      </c>
+      <c r="P83">
+        <v>-913.81018776</v>
+      </c>
+      <c r="Q83">
+        <v>-371.01018776</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4829416302694723</v>
+      </c>
+      <c r="T83">
+        <v>4.575153483159114</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>-0.05515904925903775</v>
+      </c>
+      <c r="W83">
+        <v>0.2519719809630582</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>-0.2298293719126574</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2978562143312769</v>
+      </c>
+      <c r="C84">
+        <v>-2212.174384642535</v>
+      </c>
+      <c r="D84">
+        <v>1464.415615357466</v>
+      </c>
+      <c r="E84">
+        <v>1727.29</v>
+      </c>
+      <c r="F84">
+        <v>4144.690000000001</v>
+      </c>
+      <c r="G84">
+        <v>468.1</v>
+      </c>
+      <c r="H84">
+        <v>2637.1</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>318.1</v>
+      </c>
+      <c r="K84">
+        <v>542.8</v>
+      </c>
+      <c r="L84">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M84">
+        <v>989.7519720000001</v>
+      </c>
+      <c r="N84">
+        <v>-1214.451972</v>
+      </c>
+      <c r="O84">
+        <v>-291.46847328</v>
+      </c>
+      <c r="P84">
+        <v>-922.9834987200001</v>
+      </c>
+      <c r="Q84">
+        <v>-380.1834987200001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.5076161652844431</v>
+      </c>
+      <c r="T84">
+        <v>4.829328676667954</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>-0.05448637792661046</v>
+      </c>
+      <c r="W84">
+        <v>0.2518113470488746</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>-0.2270265746942102</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.299856214331277</v>
+      </c>
+      <c r="C85">
+        <v>-2273.938543850131</v>
+      </c>
+      <c r="D85">
+        <v>1453.196456149869</v>
+      </c>
+      <c r="E85">
+        <v>1777.835</v>
+      </c>
+      <c r="F85">
+        <v>4195.235000000001</v>
+      </c>
+      <c r="G85">
+        <v>468.1</v>
+      </c>
+      <c r="H85">
+        <v>2637.1</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>318.1</v>
+      </c>
+      <c r="K85">
+        <v>542.8</v>
+      </c>
+      <c r="L85">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M85">
+        <v>1001.822118</v>
+      </c>
+      <c r="N85">
+        <v>-1226.522118</v>
+      </c>
+      <c r="O85">
+        <v>-294.36530832</v>
+      </c>
+      <c r="P85">
+        <v>-932.1568096800002</v>
+      </c>
+      <c r="Q85">
+        <v>-389.3568096800002</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.5351935867717633</v>
+      </c>
+      <c r="T85">
+        <v>5.113406834119012</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>-0.0538299155419525</v>
+      </c>
+      <c r="W85">
+        <v>0.2516545838314183</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>-0.2242913147581354</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.3018562143312769</v>
+      </c>
+      <c r="C86">
+        <v>-2335.532105921504</v>
+      </c>
+      <c r="D86">
+        <v>1442.147894078496</v>
+      </c>
+      <c r="E86">
+        <v>1828.38</v>
+      </c>
+      <c r="F86">
+        <v>4245.78</v>
+      </c>
+      <c r="G86">
+        <v>468.1</v>
+      </c>
+      <c r="H86">
+        <v>2637.1</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>318.1</v>
+      </c>
+      <c r="K86">
+        <v>542.8</v>
+      </c>
+      <c r="L86">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M86">
+        <v>1013.892264</v>
+      </c>
+      <c r="N86">
+        <v>-1238.592264</v>
+      </c>
+      <c r="O86">
+        <v>-297.26214336</v>
+      </c>
+      <c r="P86">
+        <v>-941.3301206399999</v>
+      </c>
+      <c r="Q86">
+        <v>-398.53012064</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5662181859449982</v>
+      </c>
+      <c r="T86">
+        <v>5.432994761251447</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>-0.05318908321407213</v>
+      </c>
+      <c r="W86">
+        <v>0.2515015530715204</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>-0.2216211800586338</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3038562143312769</v>
+      </c>
+      <c r="C87">
+        <v>-2396.958932614132</v>
+      </c>
+      <c r="D87">
+        <v>1431.266067385868</v>
+      </c>
+      <c r="E87">
+        <v>1878.925</v>
+      </c>
+      <c r="F87">
+        <v>4296.325</v>
+      </c>
+      <c r="G87">
+        <v>468.1</v>
+      </c>
+      <c r="H87">
+        <v>2637.1</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>318.1</v>
+      </c>
+      <c r="K87">
+        <v>542.8</v>
+      </c>
+      <c r="L87">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M87">
+        <v>1025.96241</v>
+      </c>
+      <c r="N87">
+        <v>-1250.66241</v>
+      </c>
+      <c r="O87">
+        <v>-300.1589784</v>
+      </c>
+      <c r="P87">
+        <v>-950.5034315999999</v>
+      </c>
+      <c r="Q87">
+        <v>-407.7034315999999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.6013793983413314</v>
+      </c>
+      <c r="T87">
+        <v>5.795194412001542</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>-0.05256332929390656</v>
+      </c>
+      <c r="W87">
+        <v>0.2513521230353849</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>-0.219013872057944</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3058562143312769</v>
+      </c>
+      <c r="C88">
+        <v>-2458.222770001757</v>
+      </c>
+      <c r="D88">
+        <v>1420.547229998243</v>
+      </c>
+      <c r="E88">
+        <v>1929.47</v>
+      </c>
+      <c r="F88">
+        <v>4346.87</v>
+      </c>
+      <c r="G88">
+        <v>468.1</v>
+      </c>
+      <c r="H88">
+        <v>2637.1</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>318.1</v>
+      </c>
+      <c r="K88">
+        <v>542.8</v>
+      </c>
+      <c r="L88">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M88">
+        <v>1038.032556</v>
+      </c>
+      <c r="N88">
+        <v>-1262.732556</v>
+      </c>
+      <c r="O88">
+        <v>-303.05581344</v>
+      </c>
+      <c r="P88">
+        <v>-959.67674256</v>
+      </c>
+      <c r="Q88">
+        <v>-416.87674256</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.6415636410799979</v>
+      </c>
+      <c r="T88">
+        <v>6.209136870001653</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>-0.05195212779048904</v>
+      </c>
+      <c r="W88">
+        <v>0.2512061681163688</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>-0.2164671991270375</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3078562143312769</v>
+      </c>
+      <c r="C89">
+        <v>-2519.327252774002</v>
+      </c>
+      <c r="D89">
+        <v>1409.987747225998</v>
+      </c>
+      <c r="E89">
+        <v>1980.015</v>
+      </c>
+      <c r="F89">
+        <v>4397.415</v>
+      </c>
+      <c r="G89">
+        <v>468.1</v>
+      </c>
+      <c r="H89">
+        <v>2637.1</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>318.1</v>
+      </c>
+      <c r="K89">
+        <v>542.8</v>
+      </c>
+      <c r="L89">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M89">
+        <v>1050.102702</v>
+      </c>
+      <c r="N89">
+        <v>-1274.802702</v>
+      </c>
+      <c r="O89">
+        <v>-305.95264848</v>
+      </c>
+      <c r="P89">
+        <v>-968.85005352</v>
+      </c>
+      <c r="Q89">
+        <v>-426.05005352</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6879300750092285</v>
+      </c>
+      <c r="T89">
+        <v>6.686762783078702</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>-0.05135497689634549</v>
+      </c>
+      <c r="W89">
+        <v>0.2510635684828473</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>-0.2139790704014395</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3098562143312769</v>
+      </c>
+      <c r="C90">
+        <v>-2580.27590834563</v>
+      </c>
+      <c r="D90">
+        <v>1399.58409165437</v>
+      </c>
+      <c r="E90">
+        <v>2030.56</v>
+      </c>
+      <c r="F90">
+        <v>4447.96</v>
+      </c>
+      <c r="G90">
+        <v>468.1</v>
+      </c>
+      <c r="H90">
+        <v>2637.1</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>318.1</v>
+      </c>
+      <c r="K90">
+        <v>542.8</v>
+      </c>
+      <c r="L90">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M90">
+        <v>1062.172848</v>
+      </c>
+      <c r="N90">
+        <v>-1286.872848</v>
+      </c>
+      <c r="O90">
+        <v>-308.84948352</v>
+      </c>
+      <c r="P90">
+        <v>-978.0233644800001</v>
+      </c>
+      <c r="Q90">
+        <v>-435.2233644800001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.7420242479266643</v>
+      </c>
+      <c r="T90">
+        <v>7.243993015001929</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>-0.05077139761343247</v>
+      </c>
+      <c r="W90">
+        <v>0.2509242097500877</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>-0.2115474900559686</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3118562143312769</v>
+      </c>
+      <c r="C91">
+        <v>-2641.07216078522</v>
+      </c>
+      <c r="D91">
+        <v>1389.33283921478</v>
+      </c>
+      <c r="E91">
+        <v>2081.105</v>
+      </c>
+      <c r="F91">
+        <v>4498.505</v>
+      </c>
+      <c r="G91">
+        <v>468.1</v>
+      </c>
+      <c r="H91">
+        <v>2637.1</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>318.1</v>
+      </c>
+      <c r="K91">
+        <v>542.8</v>
+      </c>
+      <c r="L91">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M91">
+        <v>1074.242994</v>
+      </c>
+      <c r="N91">
+        <v>-1298.942994</v>
+      </c>
+      <c r="O91">
+        <v>-311.74631856</v>
+      </c>
+      <c r="P91">
+        <v>-987.19667544</v>
+      </c>
+      <c r="Q91">
+        <v>-444.3966754400001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.8059537250109066</v>
+      </c>
+      <c r="T91">
+        <v>7.90253783454756</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>-0.05020093247170852</v>
+      </c>
+      <c r="W91">
+        <v>0.250787982674244</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>-0.2091705519654521</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3138562143312769</v>
+      </c>
+      <c r="C92">
+        <v>-2701.719334572441</v>
+      </c>
+      <c r="D92">
+        <v>1379.230665427559</v>
+      </c>
+      <c r="E92">
+        <v>2131.65</v>
+      </c>
+      <c r="F92">
+        <v>4549.05</v>
+      </c>
+      <c r="G92">
+        <v>468.1</v>
+      </c>
+      <c r="H92">
+        <v>2637.1</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>318.1</v>
+      </c>
+      <c r="K92">
+        <v>542.8</v>
+      </c>
+      <c r="L92">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M92">
+        <v>1086.31314</v>
+      </c>
+      <c r="N92">
+        <v>-1311.01314</v>
+      </c>
+      <c r="O92">
+        <v>-314.6431536</v>
+      </c>
+      <c r="P92">
+        <v>-996.3699864</v>
+      </c>
+      <c r="Q92">
+        <v>-453.5699864000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.8826690975119973</v>
+      </c>
+      <c r="T92">
+        <v>8.692791618002316</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>-0.04964314433313397</v>
+      </c>
+      <c r="W92">
+        <v>0.2506547828667524</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>-0.2068464347213914</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3158562143312769</v>
+      </c>
+      <c r="C93">
+        <v>-2762.220658192588</v>
+      </c>
+      <c r="D93">
+        <v>1369.274341807412</v>
+      </c>
+      <c r="E93">
+        <v>2182.195</v>
+      </c>
+      <c r="F93">
+        <v>4599.595</v>
+      </c>
+      <c r="G93">
+        <v>468.1</v>
+      </c>
+      <c r="H93">
+        <v>2637.1</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>318.1</v>
+      </c>
+      <c r="K93">
+        <v>542.8</v>
+      </c>
+      <c r="L93">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M93">
+        <v>1098.383286</v>
+      </c>
+      <c r="N93">
+        <v>-1323.083286</v>
+      </c>
+      <c r="O93">
+        <v>-317.53998864</v>
+      </c>
+      <c r="P93">
+        <v>-1005.54329736</v>
+      </c>
+      <c r="Q93">
+        <v>-462.74329736</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.976432330568886</v>
+      </c>
+      <c r="T93">
+        <v>9.658657353335908</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>-0.04909761527452811</v>
+      </c>
+      <c r="W93">
+        <v>0.2505245105275574</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>-0.2045733969772003</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3178562143312769</v>
+      </c>
+      <c r="C94">
+        <v>-2822.579267576552</v>
+      </c>
+      <c r="D94">
+        <v>1359.460732423448</v>
+      </c>
+      <c r="E94">
+        <v>2232.74</v>
+      </c>
+      <c r="F94">
+        <v>4650.14</v>
+      </c>
+      <c r="G94">
+        <v>468.1</v>
+      </c>
+      <c r="H94">
+        <v>2637.1</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>318.1</v>
+      </c>
+      <c r="K94">
+        <v>542.8</v>
+      </c>
+      <c r="L94">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M94">
+        <v>1110.453432</v>
+      </c>
+      <c r="N94">
+        <v>-1335.153432</v>
+      </c>
+      <c r="O94">
+        <v>-320.43682368</v>
+      </c>
+      <c r="P94">
+        <v>-1014.71660832</v>
+      </c>
+      <c r="Q94">
+        <v>-471.91660832</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.093636371889997</v>
+      </c>
+      <c r="T94">
+        <v>10.8659895225029</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>-0.04856394554328323</v>
+      </c>
+      <c r="W94">
+        <v>0.250397070195736</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>-0.2023497730970134</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3198562143312769</v>
+      </c>
+      <c r="C95">
+        <v>-2882.798209393907</v>
+      </c>
+      <c r="D95">
+        <v>1349.786790606093</v>
+      </c>
+      <c r="E95">
+        <v>2283.285</v>
+      </c>
+      <c r="F95">
+        <v>4700.685</v>
+      </c>
+      <c r="G95">
+        <v>468.1</v>
+      </c>
+      <c r="H95">
+        <v>2637.1</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>318.1</v>
+      </c>
+      <c r="K95">
+        <v>542.8</v>
+      </c>
+      <c r="L95">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M95">
+        <v>1122.523578</v>
+      </c>
+      <c r="N95">
+        <v>-1347.223578</v>
+      </c>
+      <c r="O95">
+        <v>-323.33365872</v>
+      </c>
+      <c r="P95">
+        <v>-1023.88991928</v>
+      </c>
+      <c r="Q95">
+        <v>-481.0899192800001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.244327282159997</v>
+      </c>
+      <c r="T95">
+        <v>12.41827374000331</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>-0.04804175258045224</v>
+      </c>
+      <c r="W95">
+        <v>0.250272370516212</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>-0.2001739690852178</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.321856214331277</v>
+      </c>
+      <c r="C96">
+        <v>-2942.880444206399</v>
+      </c>
+      <c r="D96">
+        <v>1340.249555793602</v>
+      </c>
+      <c r="E96">
+        <v>2333.83</v>
+      </c>
+      <c r="F96">
+        <v>4751.23</v>
+      </c>
+      <c r="G96">
+        <v>468.1</v>
+      </c>
+      <c r="H96">
+        <v>2637.1</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>318.1</v>
+      </c>
+      <c r="K96">
+        <v>542.8</v>
+      </c>
+      <c r="L96">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M96">
+        <v>1134.593724</v>
+      </c>
+      <c r="N96">
+        <v>-1359.293724</v>
+      </c>
+      <c r="O96">
+        <v>-326.23049376</v>
+      </c>
+      <c r="P96">
+        <v>-1033.06323024</v>
+      </c>
+      <c r="Q96">
+        <v>-490.2632302400002</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.44524849585333</v>
+      </c>
+      <c r="T96">
+        <v>14.48798603000387</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>-0.04753067010619211</v>
+      </c>
+      <c r="W96">
+        <v>0.2501503240213587</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>-0.1980444587758006</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3238562143312769</v>
+      </c>
+      <c r="C97">
+        <v>-3002.828849488671</v>
+      </c>
+      <c r="D97">
+        <v>1330.84615051133</v>
+      </c>
+      <c r="E97">
+        <v>2384.375</v>
+      </c>
+      <c r="F97">
+        <v>4801.775000000001</v>
+      </c>
+      <c r="G97">
+        <v>468.1</v>
+      </c>
+      <c r="H97">
+        <v>2637.1</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>318.1</v>
+      </c>
+      <c r="K97">
+        <v>542.8</v>
+      </c>
+      <c r="L97">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M97">
+        <v>1146.66387</v>
+      </c>
+      <c r="N97">
+        <v>-1371.36387</v>
+      </c>
+      <c r="O97">
+        <v>-329.1273288</v>
+      </c>
+      <c r="P97">
+        <v>-1042.2365412</v>
+      </c>
+      <c r="Q97">
+        <v>-499.4365412000002</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.726538195023997</v>
+      </c>
+      <c r="T97">
+        <v>17.38558323600465</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>-0.04703034726296904</v>
+      </c>
+      <c r="W97">
+        <v>0.250030846926397</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>-0.1959597802623712</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3258562143312769</v>
+      </c>
+      <c r="C98">
+        <v>-3062.646222522723</v>
+      </c>
+      <c r="D98">
+        <v>1321.573777477277</v>
+      </c>
+      <c r="E98">
+        <v>2434.92</v>
+      </c>
+      <c r="F98">
+        <v>4852.32</v>
+      </c>
+      <c r="G98">
+        <v>468.1</v>
+      </c>
+      <c r="H98">
+        <v>2637.1</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>318.1</v>
+      </c>
+      <c r="K98">
+        <v>542.8</v>
+      </c>
+      <c r="L98">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M98">
+        <v>1158.734016</v>
+      </c>
+      <c r="N98">
+        <v>-1383.434016</v>
+      </c>
+      <c r="O98">
+        <v>-332.0241638399999</v>
+      </c>
+      <c r="P98">
+        <v>-1051.40985216</v>
+      </c>
+      <c r="Q98">
+        <v>-508.6098521599999</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.148472743779991</v>
+      </c>
+      <c r="T98">
+        <v>21.73197904500577</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>-0.04654044781231311</v>
+      </c>
+      <c r="W98">
+        <v>0.2499138589375804</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>-0.1939185325513046</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3278562143312769</v>
+      </c>
+      <c r="C99">
+        <v>-3122.335283172204</v>
+      </c>
+      <c r="D99">
+        <v>1312.429716827796</v>
+      </c>
+      <c r="E99">
+        <v>2485.465</v>
+      </c>
+      <c r="F99">
+        <v>4902.865</v>
+      </c>
+      <c r="G99">
+        <v>468.1</v>
+      </c>
+      <c r="H99">
+        <v>2637.1</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>318.1</v>
+      </c>
+      <c r="K99">
+        <v>542.8</v>
+      </c>
+      <c r="L99">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M99">
+        <v>1170.804162</v>
+      </c>
+      <c r="N99">
+        <v>-1395.504162</v>
+      </c>
+      <c r="O99">
+        <v>-334.9209988799999</v>
+      </c>
+      <c r="P99">
+        <v>-1060.58316312</v>
+      </c>
+      <c r="Q99">
+        <v>-517.7831631199999</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.851696991706655</v>
+      </c>
+      <c r="T99">
+        <v>28.97597206000769</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>-0.04606064938125833</v>
+      </c>
+      <c r="W99">
+        <v>0.2497992830722445</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>-0.1919193724219097</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3298562143312769</v>
+      </c>
+      <c r="C100">
+        <v>-3181.898676542317</v>
+      </c>
+      <c r="D100">
+        <v>1303.411323457682</v>
+      </c>
+      <c r="E100">
+        <v>2536.01</v>
+      </c>
+      <c r="F100">
+        <v>4953.41</v>
+      </c>
+      <c r="G100">
+        <v>468.1</v>
+      </c>
+      <c r="H100">
+        <v>2637.1</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>318.1</v>
+      </c>
+      <c r="K100">
+        <v>542.8</v>
+      </c>
+      <c r="L100">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M100">
+        <v>1182.874308</v>
+      </c>
+      <c r="N100">
+        <v>-1407.574308</v>
+      </c>
+      <c r="O100">
+        <v>-337.8178339199999</v>
+      </c>
+      <c r="P100">
+        <v>-1069.75647408</v>
+      </c>
+      <c r="Q100">
+        <v>-526.9564740799999</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.258145487559982</v>
+      </c>
+      <c r="T100">
+        <v>43.46395809001153</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>-0.04559064275491896</v>
+      </c>
+      <c r="W100">
+        <v>0.2496870454898746</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>-0.1899610114788288</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3318562143312768</v>
+      </c>
+      <c r="C101">
+        <v>-3241.338975530819</v>
+      </c>
+      <c r="D101">
+        <v>1294.51602446918</v>
+      </c>
+      <c r="E101">
+        <v>2586.555</v>
+      </c>
+      <c r="F101">
+        <v>5003.955</v>
+      </c>
+      <c r="G101">
+        <v>468.1</v>
+      </c>
+      <c r="H101">
+        <v>2637.1</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>318.1</v>
+      </c>
+      <c r="K101">
+        <v>542.8</v>
+      </c>
+      <c r="L101">
+        <v>-224.6999999999999</v>
+      </c>
+      <c r="M101">
+        <v>1194.944454</v>
+      </c>
+      <c r="N101">
+        <v>-1419.644454</v>
+      </c>
+      <c r="O101">
+        <v>-340.7146689599999</v>
+      </c>
+      <c r="P101">
+        <v>-1078.92978504</v>
+      </c>
+      <c r="Q101">
+        <v>-536.1297850399999</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>8.477490975119963</v>
+      </c>
+      <c r="T101">
+        <v>86.92791618002306</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>-0.04513013121193998</v>
+      </c>
+      <c r="W101">
+        <v>0.2495770753334113</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>-0.1880422133830832</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/italy/italy_restaurant_dining.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_restaurant_dining.xlsx
@@ -1391,7 +1391,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1528,22 +1528,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1071509003594644</v>
+        <v>0.1069279381986017</v>
       </c>
       <c r="C2">
-        <v>19.28299791981287</v>
+        <v>19.15326326754907</v>
       </c>
       <c r="D2">
-        <v>18.00299791981287</v>
+        <v>18.06866326754907</v>
       </c>
       <c r="E2">
-        <v>-8.640000000000001</v>
+        <v>-8.444600000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1954</v>
       </c>
       <c r="G2">
         <v>1.28</v>
@@ -1564,28 +1564,28 @@
         <v>1.115</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.00982862</v>
       </c>
       <c r="N2">
-        <v>1.115</v>
+        <v>1.10517138</v>
       </c>
       <c r="O2">
-        <v>0.2676000000000001</v>
+        <v>0.2652411312</v>
       </c>
       <c r="P2">
-        <v>0.8474000000000002</v>
+        <v>0.8399302488000002</v>
       </c>
       <c r="Q2">
-        <v>1.5324</v>
+        <v>1.5249302488</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1071509003594644</v>
+        <v>0.1076218769682845</v>
       </c>
       <c r="T2">
-        <v>0.8445182362326223</v>
+        <v>0.8510014065309738</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>113.4442068164198</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1610,22 +1610,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1069279381986017</v>
+        <v>0.106704976037739</v>
       </c>
       <c r="C3">
-        <v>19.15326326754907</v>
+        <v>19.02400939333586</v>
       </c>
       <c r="D3">
-        <v>18.06866326754907</v>
+        <v>18.13480939333586</v>
       </c>
       <c r="E3">
-        <v>-8.444600000000001</v>
+        <v>-8.2492</v>
       </c>
       <c r="F3">
-        <v>0.1954</v>
+        <v>0.3908</v>
       </c>
       <c r="G3">
         <v>1.28</v>
@@ -1646,28 +1646,28 @@
         <v>1.115</v>
       </c>
       <c r="M3">
-        <v>0.00982862</v>
+        <v>0.01965724</v>
       </c>
       <c r="N3">
-        <v>1.10517138</v>
+        <v>1.09534276</v>
       </c>
       <c r="O3">
-        <v>0.2652411312</v>
+        <v>0.2628822624000001</v>
       </c>
       <c r="P3">
-        <v>0.8399302488000002</v>
+        <v>0.8324604976000003</v>
       </c>
       <c r="Q3">
-        <v>1.5249302488</v>
+        <v>1.5174604976</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1076218769682845</v>
+        <v>0.1081024653446316</v>
       </c>
       <c r="T3">
-        <v>0.8510014065309738</v>
+        <v>0.8576168864272508</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>113.4442068164198</v>
+        <v>56.72210340820992</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1692,22 +1692,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.106704976037739</v>
+        <v>0.1064820138768762</v>
       </c>
       <c r="C4">
-        <v>19.02400939333586</v>
+        <v>18.89524159669971</v>
       </c>
       <c r="D4">
-        <v>18.13480939333586</v>
+        <v>18.20144159669971</v>
       </c>
       <c r="E4">
-        <v>-8.2492</v>
+        <v>-8.053800000000001</v>
       </c>
       <c r="F4">
-        <v>0.3908</v>
+        <v>0.5861999999999999</v>
       </c>
       <c r="G4">
         <v>1.28</v>
@@ -1728,28 +1728,28 @@
         <v>1.115</v>
       </c>
       <c r="M4">
-        <v>0.01965724</v>
+        <v>0.02948586</v>
       </c>
       <c r="N4">
-        <v>1.09534276</v>
+        <v>1.08551414</v>
       </c>
       <c r="O4">
-        <v>0.2628822624000001</v>
+        <v>0.2605233936</v>
       </c>
       <c r="P4">
-        <v>0.8324604976000003</v>
+        <v>0.8249907464000001</v>
       </c>
       <c r="Q4">
-        <v>1.5174604976</v>
+        <v>1.5099907464</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1081024653446316</v>
+        <v>0.1085929627596662</v>
       </c>
       <c r="T4">
-        <v>0.8576168864272508</v>
+        <v>0.8643687679708737</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>56.72210340820992</v>
+        <v>37.81473560547327</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1774,22 +1774,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1064820138768762</v>
+        <v>0.1062590517160135</v>
       </c>
       <c r="C5">
-        <v>18.89524159669971</v>
+        <v>18.76696525534189</v>
       </c>
       <c r="D5">
-        <v>18.20144159669971</v>
+        <v>18.26856525534189</v>
       </c>
       <c r="E5">
-        <v>-8.053800000000001</v>
+        <v>-7.8584</v>
       </c>
       <c r="F5">
-        <v>0.5861999999999999</v>
+        <v>0.7816</v>
       </c>
       <c r="G5">
         <v>1.28</v>
@@ -1810,28 +1810,28 @@
         <v>1.115</v>
       </c>
       <c r="M5">
-        <v>0.02948586</v>
+        <v>0.03931448</v>
       </c>
       <c r="N5">
-        <v>1.08551414</v>
+        <v>1.07568552</v>
       </c>
       <c r="O5">
-        <v>0.2605233936</v>
+        <v>0.2581645248</v>
       </c>
       <c r="P5">
-        <v>0.8249907464000001</v>
+        <v>0.8175209952000002</v>
       </c>
       <c r="Q5">
-        <v>1.5099907464</v>
+        <v>1.5025209952</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1085929627596662</v>
+        <v>0.1090936788708474</v>
       </c>
       <c r="T5">
-        <v>0.8643687679708737</v>
+        <v>0.8712613137133222</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>37.81473560547327</v>
+        <v>28.36105170410496</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1856,22 +1856,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1062590517160135</v>
+        <v>0.1060360895551508</v>
       </c>
       <c r="C6">
-        <v>18.76696525534189</v>
+        <v>18.63918582658538</v>
       </c>
       <c r="D6">
-        <v>18.26856525534189</v>
+        <v>18.33618582658537</v>
       </c>
       <c r="E6">
-        <v>-7.8584</v>
+        <v>-7.663</v>
       </c>
       <c r="F6">
-        <v>0.7816</v>
+        <v>0.977</v>
       </c>
       <c r="G6">
         <v>1.28</v>
@@ -1892,28 +1892,28 @@
         <v>1.115</v>
       </c>
       <c r="M6">
-        <v>0.03931448</v>
+        <v>0.0491431</v>
       </c>
       <c r="N6">
-        <v>1.07568552</v>
+        <v>1.0658569</v>
       </c>
       <c r="O6">
-        <v>0.2581645248</v>
+        <v>0.255805656</v>
       </c>
       <c r="P6">
-        <v>0.8175209952000002</v>
+        <v>0.8100512440000002</v>
       </c>
       <c r="Q6">
-        <v>1.5025209952</v>
+        <v>1.495051244</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1090936788708474</v>
+        <v>0.109604936373843</v>
       </c>
       <c r="T6">
-        <v>0.8712613137133222</v>
+        <v>0.8782989656819272</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>28.36105170410496</v>
+        <v>22.68884136328397</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1938,22 +1938,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1060360895551508</v>
+        <v>0.1058131273942881</v>
       </c>
       <c r="C7">
-        <v>18.63918582658538</v>
+        <v>18.51190884885375</v>
       </c>
       <c r="D7">
-        <v>18.33618582658537</v>
+        <v>18.40430884885374</v>
       </c>
       <c r="E7">
-        <v>-7.663</v>
+        <v>-7.467600000000001</v>
       </c>
       <c r="F7">
-        <v>0.977</v>
+        <v>1.1724</v>
       </c>
       <c r="G7">
         <v>1.28</v>
@@ -1974,28 +1974,28 @@
         <v>1.115</v>
       </c>
       <c r="M7">
-        <v>0.0491431</v>
+        <v>0.05897172000000001</v>
       </c>
       <c r="N7">
-        <v>1.0658569</v>
+        <v>1.05602828</v>
       </c>
       <c r="O7">
-        <v>0.255805656</v>
+        <v>0.2534467872000001</v>
       </c>
       <c r="P7">
-        <v>0.8100512440000002</v>
+        <v>0.8025814928000001</v>
       </c>
       <c r="Q7">
-        <v>1.495051244</v>
+        <v>1.4875814928</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.109604936373843</v>
+        <v>0.1101270716960512</v>
       </c>
       <c r="T7">
-        <v>0.8782989656819272</v>
+        <v>0.8854863549264602</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>22.68884136328397</v>
+        <v>18.90736780273664</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2020,22 +2020,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1058131273942881</v>
+        <v>0.1055901652334254</v>
       </c>
       <c r="C8">
-        <v>18.51190884885375</v>
+        <v>18.38513994318348</v>
       </c>
       <c r="D8">
-        <v>18.40430884885374</v>
+        <v>18.47293994318348</v>
       </c>
       <c r="E8">
-        <v>-7.467600000000001</v>
+        <v>-7.272200000000001</v>
       </c>
       <c r="F8">
-        <v>1.1724</v>
+        <v>1.3678</v>
       </c>
       <c r="G8">
         <v>1.28</v>
@@ -2056,28 +2056,28 @@
         <v>1.115</v>
       </c>
       <c r="M8">
-        <v>0.05897171999999999</v>
+        <v>0.06880033999999999</v>
       </c>
       <c r="N8">
-        <v>1.05602828</v>
+        <v>1.04619966</v>
       </c>
       <c r="O8">
-        <v>0.2534467872000001</v>
+        <v>0.2510879184000001</v>
       </c>
       <c r="P8">
-        <v>0.8025814928000001</v>
+        <v>0.7951117416000002</v>
       </c>
       <c r="Q8">
-        <v>1.4875814928</v>
+        <v>1.4801117416</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1101270716960512</v>
+        <v>0.110660435734866</v>
       </c>
       <c r="T8">
-        <v>0.8854863549264602</v>
+        <v>0.8928283116816282</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.90736780273664</v>
+        <v>16.20631525948855</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2102,22 +2102,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1055901652334254</v>
+        <v>0.1053672030725627</v>
       </c>
       <c r="C9">
-        <v>18.38513994318349</v>
+        <v>18.25888481476998</v>
       </c>
       <c r="D9">
-        <v>18.47293994318348</v>
+        <v>18.54208481476998</v>
       </c>
       <c r="E9">
-        <v>-7.272200000000001</v>
+        <v>-7.0768</v>
       </c>
       <c r="F9">
-        <v>1.3678</v>
+        <v>1.5632</v>
       </c>
       <c r="G9">
         <v>1.28</v>
@@ -2138,28 +2138,28 @@
         <v>1.115</v>
       </c>
       <c r="M9">
-        <v>0.06880034</v>
+        <v>0.07862896</v>
       </c>
       <c r="N9">
-        <v>1.04619966</v>
+        <v>1.03637104</v>
       </c>
       <c r="O9">
-        <v>0.2510879184000001</v>
+        <v>0.2487290496</v>
       </c>
       <c r="P9">
-        <v>0.7951117416000002</v>
+        <v>0.7876419904</v>
       </c>
       <c r="Q9">
-        <v>1.4801117416</v>
+        <v>1.4726419904</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.110660435734866</v>
+        <v>0.1112053946440898</v>
       </c>
       <c r="T9">
-        <v>0.8928283116816282</v>
+        <v>0.9003298761923434</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.20631525948855</v>
+        <v>14.18052585205248</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2184,22 +2184,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1053672030725627</v>
+        <v>0.1052468409117</v>
       </c>
       <c r="C10">
-        <v>18.25888481476998</v>
+        <v>18.10102701820717</v>
       </c>
       <c r="D10">
-        <v>18.54208481476998</v>
+        <v>18.57962701820717</v>
       </c>
       <c r="E10">
-        <v>-7.0768</v>
+        <v>-6.881400000000001</v>
       </c>
       <c r="F10">
-        <v>1.5632</v>
+        <v>1.7586</v>
       </c>
       <c r="G10">
         <v>1.28</v>
@@ -2220,45 +2220,45 @@
         <v>1.115</v>
       </c>
       <c r="M10">
-        <v>0.07862896</v>
+        <v>0.09109547999999999</v>
       </c>
       <c r="N10">
-        <v>1.03637104</v>
+        <v>1.02390452</v>
       </c>
       <c r="O10">
-        <v>0.2487290496</v>
+        <v>0.2457370848000001</v>
       </c>
       <c r="P10">
-        <v>0.7876419904</v>
+        <v>0.7781674352000003</v>
       </c>
       <c r="Q10">
-        <v>1.4726419904</v>
+        <v>1.4631674352</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1112053946440898</v>
+        <v>0.1117623306721978</v>
       </c>
       <c r="T10">
-        <v>0.9003298761923434</v>
+        <v>0.9079963102527446</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.24</v>
       </c>
       <c r="W10">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>14.18052585205248</v>
+        <v>12.23990476805216</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2266,22 +2266,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1052468409117</v>
+        <v>0.1050352787508372</v>
       </c>
       <c r="C11">
-        <v>18.10102701820717</v>
+        <v>17.97198521087356</v>
       </c>
       <c r="D11">
-        <v>18.57962701820717</v>
+        <v>18.64598521087355</v>
       </c>
       <c r="E11">
-        <v>-6.881400000000001</v>
+        <v>-6.686000000000001</v>
       </c>
       <c r="F11">
-        <v>1.7586</v>
+        <v>1.954</v>
       </c>
       <c r="G11">
         <v>1.28</v>
@@ -2302,28 +2302,28 @@
         <v>1.115</v>
       </c>
       <c r="M11">
-        <v>0.09109547999999999</v>
+        <v>0.1012172</v>
       </c>
       <c r="N11">
-        <v>1.02390452</v>
+        <v>1.0137828</v>
       </c>
       <c r="O11">
-        <v>0.2457370848000001</v>
+        <v>0.243307872</v>
       </c>
       <c r="P11">
-        <v>0.7781674352000003</v>
+        <v>0.7704749280000002</v>
       </c>
       <c r="Q11">
-        <v>1.4631674352</v>
+        <v>1.455474928</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1117623306721978</v>
+        <v>0.1123316430564858</v>
       </c>
       <c r="T11">
-        <v>0.9079963102527446</v>
+        <v>0.9158331095144883</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>12.23990476805216</v>
+        <v>11.01591429124695</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2348,22 +2348,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1050352787508372</v>
+        <v>0.1048237165899745</v>
       </c>
       <c r="C12">
-        <v>17.97198521087356</v>
+        <v>17.84341910664515</v>
       </c>
       <c r="D12">
-        <v>18.64598521087355</v>
+        <v>18.71281910664515</v>
       </c>
       <c r="E12">
-        <v>-6.686000000000001</v>
+        <v>-6.490600000000001</v>
       </c>
       <c r="F12">
-        <v>1.954</v>
+        <v>2.1494</v>
       </c>
       <c r="G12">
         <v>1.28</v>
@@ -2384,28 +2384,28 @@
         <v>1.115</v>
       </c>
       <c r="M12">
-        <v>0.1012172</v>
+        <v>0.11133892</v>
       </c>
       <c r="N12">
-        <v>1.0137828</v>
+        <v>1.00366108</v>
       </c>
       <c r="O12">
-        <v>0.243307872</v>
+        <v>0.2408786592000001</v>
       </c>
       <c r="P12">
-        <v>0.7704749280000002</v>
+        <v>0.7627824208000002</v>
       </c>
       <c r="Q12">
-        <v>1.455474928</v>
+        <v>1.4477824208</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1123316430564858</v>
+        <v>0.1129137489774995</v>
       </c>
       <c r="T12">
-        <v>0.9158331095144883</v>
+        <v>0.9238460166248103</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.01591429124695</v>
+        <v>10.01446753749722</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2430,22 +2430,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1048237165899745</v>
+        <v>0.1047671944291118</v>
       </c>
       <c r="C13">
-        <v>17.84341910664515</v>
+        <v>17.6659560117664</v>
       </c>
       <c r="D13">
-        <v>18.71281910664515</v>
+        <v>18.7307560117664</v>
       </c>
       <c r="E13">
-        <v>-6.490600000000001</v>
+        <v>-6.295200000000001</v>
       </c>
       <c r="F13">
-        <v>2.1494</v>
+        <v>2.3448</v>
       </c>
       <c r="G13">
         <v>1.28</v>
@@ -2466,45 +2466,45 @@
         <v>1.115</v>
       </c>
       <c r="M13">
-        <v>0.11133892</v>
+        <v>0.1254468</v>
       </c>
       <c r="N13">
-        <v>1.00366108</v>
+        <v>0.9895532000000002</v>
       </c>
       <c r="O13">
-        <v>0.2408786592000001</v>
+        <v>0.237492768</v>
       </c>
       <c r="P13">
-        <v>0.7627824208000002</v>
+        <v>0.7520604320000002</v>
       </c>
       <c r="Q13">
-        <v>1.4477824208</v>
+        <v>1.437060432</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1129137489774995</v>
+        <v>0.1135090845785361</v>
       </c>
       <c r="T13">
-        <v>0.9238460166248103</v>
+        <v>0.9320410352603667</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.24</v>
       </c>
       <c r="W13">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>10.01446753749722</v>
+        <v>8.888229911006102</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2512,22 +2512,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1047671944291118</v>
+        <v>0.1045685522682491</v>
       </c>
       <c r="C14">
-        <v>17.6659560117664</v>
+        <v>17.53386738673079</v>
       </c>
       <c r="D14">
-        <v>18.7307560117664</v>
+        <v>18.79406738673078</v>
       </c>
       <c r="E14">
-        <v>-6.295200000000001</v>
+        <v>-6.0998</v>
       </c>
       <c r="F14">
-        <v>2.3448</v>
+        <v>2.5402</v>
       </c>
       <c r="G14">
         <v>1.28</v>
@@ -2548,28 +2548,28 @@
         <v>1.115</v>
       </c>
       <c r="M14">
-        <v>0.1254468</v>
+        <v>0.1359007</v>
       </c>
       <c r="N14">
-        <v>0.9895532000000002</v>
+        <v>0.9790993000000002</v>
       </c>
       <c r="O14">
-        <v>0.237492768</v>
+        <v>0.2349838320000001</v>
       </c>
       <c r="P14">
-        <v>0.7520604320000002</v>
+        <v>0.7441154680000002</v>
       </c>
       <c r="Q14">
-        <v>1.437060432</v>
+        <v>1.429115468</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1135090845785361</v>
+        <v>0.1141181060554587</v>
       </c>
       <c r="T14">
-        <v>0.9320410352603667</v>
+        <v>0.9404244451289248</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.888229911006102</v>
+        <v>8.204519917851787</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2594,22 +2594,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1045685522682491</v>
+        <v>0.1043699101073864</v>
       </c>
       <c r="C15">
-        <v>17.53386738673079</v>
+        <v>17.40220820774715</v>
       </c>
       <c r="D15">
-        <v>18.79406738673078</v>
+        <v>18.85780820774715</v>
       </c>
       <c r="E15">
-        <v>-6.0998</v>
+        <v>-5.904400000000001</v>
       </c>
       <c r="F15">
-        <v>2.5402</v>
+        <v>2.7356</v>
       </c>
       <c r="G15">
         <v>1.28</v>
@@ -2630,28 +2630,28 @@
         <v>1.115</v>
       </c>
       <c r="M15">
-        <v>0.1359007</v>
+        <v>0.1463546</v>
       </c>
       <c r="N15">
-        <v>0.9790993000000002</v>
+        <v>0.9686454000000002</v>
       </c>
       <c r="O15">
-        <v>0.2349838320000001</v>
+        <v>0.232474896</v>
       </c>
       <c r="P15">
-        <v>0.7441154680000002</v>
+        <v>0.7361705040000002</v>
       </c>
       <c r="Q15">
-        <v>1.429115468</v>
+        <v>1.421170504</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1141181060554587</v>
+        <v>0.1147412908225423</v>
       </c>
       <c r="T15">
-        <v>0.9404244451289248</v>
+        <v>0.9490028180176817</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.204519917851787</v>
+        <v>7.618482780862372</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2676,22 +2676,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1043699101073864</v>
+        <v>0.1042624679465237</v>
       </c>
       <c r="C16">
-        <v>17.40220820774715</v>
+        <v>17.24146503518092</v>
       </c>
       <c r="D16">
-        <v>18.85780820774715</v>
+        <v>18.89246503518092</v>
       </c>
       <c r="E16">
-        <v>-5.904400000000001</v>
+        <v>-5.709</v>
       </c>
       <c r="F16">
-        <v>2.7356</v>
+        <v>2.931</v>
       </c>
       <c r="G16">
         <v>1.28</v>
@@ -2712,45 +2712,45 @@
         <v>1.115</v>
       </c>
       <c r="M16">
-        <v>0.1463546</v>
+        <v>0.1591533</v>
       </c>
       <c r="N16">
-        <v>0.9686454000000002</v>
+        <v>0.9558467000000002</v>
       </c>
       <c r="O16">
-        <v>0.232474896</v>
+        <v>0.229403208</v>
       </c>
       <c r="P16">
-        <v>0.7361705040000002</v>
+        <v>0.7264434920000001</v>
       </c>
       <c r="Q16">
-        <v>1.421170504</v>
+        <v>1.411443492</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1147412908225423</v>
+        <v>0.1153791387606161</v>
       </c>
       <c r="T16">
-        <v>0.9490028180176817</v>
+        <v>0.9577830349744094</v>
       </c>
       <c r="U16">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.24</v>
       </c>
       <c r="W16">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>7.618482780862372</v>
+        <v>7.00582394458676</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2758,22 +2758,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1042624679465237</v>
+        <v>0.104069905785661</v>
       </c>
       <c r="C17">
-        <v>17.24146503518093</v>
+        <v>17.10849818728828</v>
       </c>
       <c r="D17">
-        <v>18.89246503518093</v>
+        <v>18.95489818728828</v>
       </c>
       <c r="E17">
-        <v>-5.709000000000001</v>
+        <v>-5.5136</v>
       </c>
       <c r="F17">
-        <v>2.931</v>
+        <v>3.1264</v>
       </c>
       <c r="G17">
         <v>1.28</v>
@@ -2794,28 +2794,28 @@
         <v>1.115</v>
       </c>
       <c r="M17">
-        <v>0.1591533</v>
+        <v>0.16976352</v>
       </c>
       <c r="N17">
-        <v>0.9558467000000003</v>
+        <v>0.9452364800000002</v>
       </c>
       <c r="O17">
-        <v>0.2294032080000001</v>
+        <v>0.2268567552</v>
       </c>
       <c r="P17">
-        <v>0.7264434920000002</v>
+        <v>0.7183797248000001</v>
       </c>
       <c r="Q17">
-        <v>1.411443492</v>
+        <v>1.4033797248</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1153791387606161</v>
+        <v>0.1160321735543583</v>
       </c>
       <c r="T17">
-        <v>0.9577830349744093</v>
+        <v>0.9667723047158211</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.005823944586763</v>
+        <v>6.567959948050088</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2840,22 +2840,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.104069905785661</v>
+        <v>0.1038773436247982</v>
       </c>
       <c r="C18">
-        <v>17.10849818728828</v>
+        <v>16.97594534809263</v>
       </c>
       <c r="D18">
-        <v>18.95489818728828</v>
+        <v>19.01774534809263</v>
       </c>
       <c r="E18">
-        <v>-5.5136</v>
+        <v>-5.318200000000001</v>
       </c>
       <c r="F18">
-        <v>3.1264</v>
+        <v>3.3218</v>
       </c>
       <c r="G18">
         <v>1.28</v>
@@ -2876,28 +2876,28 @@
         <v>1.115</v>
       </c>
       <c r="M18">
-        <v>0.16976352</v>
+        <v>0.18037374</v>
       </c>
       <c r="N18">
-        <v>0.9452364800000002</v>
+        <v>0.9346262600000002</v>
       </c>
       <c r="O18">
-        <v>0.2268567552</v>
+        <v>0.2243103024</v>
       </c>
       <c r="P18">
-        <v>0.7183797248000001</v>
+        <v>0.7103159576000001</v>
       </c>
       <c r="Q18">
-        <v>1.4033797248</v>
+        <v>1.3953159576</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1160321735543583</v>
+        <v>0.1167009441262629</v>
       </c>
       <c r="T18">
-        <v>0.9667723047158211</v>
+        <v>0.9759781833666643</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.567959948050088</v>
+        <v>6.181609362870671</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2922,22 +2922,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1038773436247982</v>
+        <v>0.1038215814639355</v>
       </c>
       <c r="C19">
-        <v>16.97594534809263</v>
+        <v>16.79882252269887</v>
       </c>
       <c r="D19">
-        <v>19.01774534809263</v>
+        <v>19.03602252269886</v>
       </c>
       <c r="E19">
-        <v>-5.318200000000001</v>
+        <v>-5.1228</v>
       </c>
       <c r="F19">
-        <v>3.3218</v>
+        <v>3.5172</v>
       </c>
       <c r="G19">
         <v>1.28</v>
@@ -2958,45 +2958,45 @@
         <v>1.115</v>
       </c>
       <c r="M19">
-        <v>0.18037374</v>
+        <v>0.19450116</v>
       </c>
       <c r="N19">
-        <v>0.9346262600000002</v>
+        <v>0.9204988400000002</v>
       </c>
       <c r="O19">
-        <v>0.2243103024</v>
+        <v>0.2209197216</v>
       </c>
       <c r="P19">
-        <v>0.7103159576000001</v>
+        <v>0.6995791184000001</v>
       </c>
       <c r="Q19">
-        <v>1.3953159576</v>
+        <v>1.3845791184</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1167009441262629</v>
+        <v>0.1173860261755311</v>
       </c>
       <c r="T19">
-        <v>0.9759781833666643</v>
+        <v>0.985408595643138</v>
       </c>
       <c r="U19">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V19">
         <v>0.24</v>
       </c>
       <c r="W19">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.181609362870671</v>
+        <v>5.732613625543416</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3004,22 +3004,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1038215814639355</v>
+        <v>0.1036366193030728</v>
       </c>
       <c r="C20">
-        <v>16.79882252269887</v>
+        <v>16.66429993743121</v>
       </c>
       <c r="D20">
-        <v>19.03602252269887</v>
+        <v>19.0968999374312</v>
       </c>
       <c r="E20">
-        <v>-5.122800000000001</v>
+        <v>-4.9274</v>
       </c>
       <c r="F20">
-        <v>3.5172</v>
+        <v>3.7126</v>
       </c>
       <c r="G20">
         <v>1.28</v>
@@ -3040,28 +3040,28 @@
         <v>1.115</v>
       </c>
       <c r="M20">
-        <v>0.19450116</v>
+        <v>0.20530678</v>
       </c>
       <c r="N20">
-        <v>0.9204988400000003</v>
+        <v>0.9096932200000002</v>
       </c>
       <c r="O20">
-        <v>0.2209197216000001</v>
+        <v>0.2183263728</v>
       </c>
       <c r="P20">
-        <v>0.6995791184000002</v>
+        <v>0.6913668472000002</v>
       </c>
       <c r="Q20">
-        <v>1.3845791184</v>
+        <v>1.3763668472</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1173860261755311</v>
+        <v>0.1180880238309541</v>
       </c>
       <c r="T20">
-        <v>0.9854085956431378</v>
+        <v>0.9950718576054502</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.732613625543417</v>
+        <v>5.430897118935869</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3086,22 +3086,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1036366193030728</v>
+        <v>0.1034516571422101</v>
       </c>
       <c r="C21">
-        <v>16.66429993743121</v>
+        <v>16.5301679746967</v>
       </c>
       <c r="D21">
-        <v>19.0968999374312</v>
+        <v>19.1581679746967</v>
       </c>
       <c r="E21">
-        <v>-4.9274</v>
+        <v>-4.732000000000001</v>
       </c>
       <c r="F21">
-        <v>3.7126</v>
+        <v>3.908</v>
       </c>
       <c r="G21">
         <v>1.28</v>
@@ -3122,28 +3122,28 @@
         <v>1.115</v>
       </c>
       <c r="M21">
-        <v>0.20530678</v>
+        <v>0.2161124</v>
       </c>
       <c r="N21">
-        <v>0.9096932200000002</v>
+        <v>0.8988876000000002</v>
       </c>
       <c r="O21">
-        <v>0.2183263728</v>
+        <v>0.2157330240000001</v>
       </c>
       <c r="P21">
-        <v>0.6913668472000002</v>
+        <v>0.6831545760000002</v>
       </c>
       <c r="Q21">
-        <v>1.3763668472</v>
+        <v>1.368154576</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1180880238309541</v>
+        <v>0.1188075714277626</v>
       </c>
       <c r="T21">
-        <v>0.9950718576054502</v>
+        <v>1.00497670111682</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.430897118935869</v>
+        <v>5.159352262989075</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3168,22 +3168,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1034516571422101</v>
+        <v>0.1032666949813474</v>
       </c>
       <c r="C22">
-        <v>16.5301679746967</v>
+        <v>16.39643040626547</v>
       </c>
       <c r="D22">
-        <v>19.1581679746967</v>
+        <v>19.21983040626547</v>
       </c>
       <c r="E22">
-        <v>-4.732000000000001</v>
+        <v>-4.5366</v>
       </c>
       <c r="F22">
-        <v>3.908</v>
+        <v>4.103400000000001</v>
       </c>
       <c r="G22">
         <v>1.28</v>
@@ -3204,28 +3204,28 @@
         <v>1.115</v>
       </c>
       <c r="M22">
-        <v>0.2161124</v>
+        <v>0.2269180200000001</v>
       </c>
       <c r="N22">
-        <v>0.8988876000000002</v>
+        <v>0.8880819800000002</v>
       </c>
       <c r="O22">
-        <v>0.2157330240000001</v>
+        <v>0.2131396752</v>
       </c>
       <c r="P22">
-        <v>0.6831545760000002</v>
+        <v>0.6749423048000002</v>
       </c>
       <c r="Q22">
-        <v>1.368154576</v>
+        <v>1.3599423048</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1188075714277626</v>
+        <v>0.1195453354194271</v>
       </c>
       <c r="T22">
-        <v>1.00497670111682</v>
+        <v>1.015132300160124</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.159352262989075</v>
+        <v>4.913668821894356</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3250,22 +3250,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1032666949813474</v>
+        <v>0.1030817328204847</v>
       </c>
       <c r="C23">
-        <v>16.39643040626547</v>
+        <v>16.26309105262369</v>
       </c>
       <c r="D23">
-        <v>19.21983040626547</v>
+        <v>19.28189105262368</v>
       </c>
       <c r="E23">
-        <v>-4.536600000000001</v>
+        <v>-4.341200000000001</v>
       </c>
       <c r="F23">
-        <v>4.1034</v>
+        <v>4.2988</v>
       </c>
       <c r="G23">
         <v>1.28</v>
@@ -3286,28 +3286,28 @@
         <v>1.115</v>
       </c>
       <c r="M23">
-        <v>0.22691802</v>
+        <v>0.23772364</v>
       </c>
       <c r="N23">
-        <v>0.8880819800000002</v>
+        <v>0.8772763600000002</v>
       </c>
       <c r="O23">
-        <v>0.2131396752</v>
+        <v>0.2105463264</v>
       </c>
       <c r="P23">
-        <v>0.6749423048000002</v>
+        <v>0.6667300336000002</v>
       </c>
       <c r="Q23">
-        <v>1.3599423048</v>
+        <v>1.3517300336</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1195453354194271</v>
+        <v>0.1203020164365188</v>
       </c>
       <c r="T23">
-        <v>1.015132300160124</v>
+        <v>1.025548299178897</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.913668821894356</v>
+        <v>4.690320239080977</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3332,22 +3332,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1030817328204847</v>
+        <v>0.103333770659622</v>
       </c>
       <c r="C24">
-        <v>16.26309105262369</v>
+        <v>15.98322298978568</v>
       </c>
       <c r="D24">
-        <v>19.28189105262368</v>
+        <v>19.19742298978568</v>
       </c>
       <c r="E24">
-        <v>-4.341200000000001</v>
+        <v>-4.1458</v>
       </c>
       <c r="F24">
-        <v>4.2988</v>
+        <v>4.4942</v>
       </c>
       <c r="G24">
         <v>1.28</v>
@@ -3368,45 +3368,45 @@
         <v>1.115</v>
       </c>
       <c r="M24">
-        <v>0.23772364</v>
+        <v>0.25976476</v>
       </c>
       <c r="N24">
-        <v>0.8772763600000002</v>
+        <v>0.8552352400000002</v>
       </c>
       <c r="O24">
-        <v>0.2105463264</v>
+        <v>0.2052564576</v>
       </c>
       <c r="P24">
-        <v>0.6667300336000002</v>
+        <v>0.6499787824000002</v>
       </c>
       <c r="Q24">
-        <v>1.3517300336</v>
+        <v>1.3349787824</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1203020164365188</v>
+        <v>0.1210783515060025</v>
       </c>
       <c r="T24">
-        <v>1.025548299178897</v>
+        <v>1.036234843626729</v>
       </c>
       <c r="U24">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V24">
         <v>0.24</v>
       </c>
       <c r="W24">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.690320239080977</v>
+        <v>4.292345120254187</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3414,22 +3414,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.103333770659622</v>
+        <v>0.1031678084987592</v>
       </c>
       <c r="C25">
-        <v>15.98322298978568</v>
+        <v>15.84336016099294</v>
       </c>
       <c r="D25">
-        <v>19.19742298978568</v>
+        <v>19.25296016099294</v>
       </c>
       <c r="E25">
-        <v>-4.1458</v>
+        <v>-3.9504</v>
       </c>
       <c r="F25">
-        <v>4.4942</v>
+        <v>4.6896</v>
       </c>
       <c r="G25">
         <v>1.28</v>
@@ -3450,28 +3450,28 @@
         <v>1.115</v>
       </c>
       <c r="M25">
-        <v>0.25976476</v>
+        <v>0.2710588800000001</v>
       </c>
       <c r="N25">
-        <v>0.8552352400000002</v>
+        <v>0.8439411200000002</v>
       </c>
       <c r="O25">
-        <v>0.2052564576</v>
+        <v>0.2025458688000001</v>
       </c>
       <c r="P25">
-        <v>0.6499787824000002</v>
+        <v>0.6413952512000002</v>
       </c>
       <c r="Q25">
-        <v>1.3349787824</v>
+        <v>1.3263952512</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1210783515060025</v>
+        <v>0.1218751164457358</v>
       </c>
       <c r="T25">
-        <v>1.036234843626729</v>
+        <v>1.047202612928452</v>
       </c>
       <c r="U25">
         <v>0.0578</v>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.292345120254187</v>
+        <v>4.113497406910263</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3496,22 +3496,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1031678084987592</v>
+        <v>0.1036668463378965</v>
       </c>
       <c r="C26">
-        <v>15.84336016099294</v>
+        <v>15.4819245768238</v>
       </c>
       <c r="D26">
-        <v>19.25296016099294</v>
+        <v>19.0869245768238</v>
       </c>
       <c r="E26">
-        <v>-3.950400000000001</v>
+        <v>-3.755000000000001</v>
       </c>
       <c r="F26">
-        <v>4.6896</v>
+        <v>4.885</v>
       </c>
       <c r="G26">
         <v>1.28</v>
@@ -3532,45 +3532,45 @@
         <v>1.115</v>
       </c>
       <c r="M26">
-        <v>0.27105888</v>
+        <v>0.2994505</v>
       </c>
       <c r="N26">
-        <v>0.8439411200000002</v>
+        <v>0.8155495000000001</v>
       </c>
       <c r="O26">
-        <v>0.2025458688000001</v>
+        <v>0.19573188</v>
       </c>
       <c r="P26">
-        <v>0.6413952512000002</v>
+        <v>0.6198176200000001</v>
       </c>
       <c r="Q26">
-        <v>1.3263952512</v>
+        <v>1.30481762</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1218751164457358</v>
+        <v>0.1226931284505287</v>
       </c>
       <c r="T26">
-        <v>1.047202612928452</v>
+        <v>1.05846285607822</v>
       </c>
       <c r="U26">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V26">
         <v>0.24</v>
       </c>
       <c r="W26">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.113497406910263</v>
+        <v>3.723486853419848</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3578,22 +3578,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1036668463378965</v>
+        <v>0.1035274841770338</v>
       </c>
       <c r="C27">
-        <v>15.4819245768238</v>
+        <v>15.33260306250824</v>
       </c>
       <c r="D27">
-        <v>19.0869245768238</v>
+        <v>19.13300306250824</v>
       </c>
       <c r="E27">
-        <v>-3.755000000000001</v>
+        <v>-3.559600000000001</v>
       </c>
       <c r="F27">
-        <v>4.885</v>
+        <v>5.0804</v>
       </c>
       <c r="G27">
         <v>1.28</v>
@@ -3614,28 +3614,28 @@
         <v>1.115</v>
       </c>
       <c r="M27">
-        <v>0.2994505</v>
+        <v>0.31142852</v>
       </c>
       <c r="N27">
-        <v>0.8155495000000001</v>
+        <v>0.8035714800000002</v>
       </c>
       <c r="O27">
-        <v>0.19573188</v>
+        <v>0.1928571552</v>
       </c>
       <c r="P27">
-        <v>0.6198176200000001</v>
+        <v>0.6107143248000002</v>
       </c>
       <c r="Q27">
-        <v>1.30481762</v>
+        <v>1.2957143248</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1226931284505287</v>
+        <v>0.1235332488878835</v>
       </c>
       <c r="T27">
-        <v>1.05846285607822</v>
+        <v>1.070027430123928</v>
       </c>
       <c r="U27">
         <v>0.0613</v>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.723486853419848</v>
+        <v>3.580275820596008</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3660,22 +3660,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1035274841770338</v>
+        <v>0.1039626820161711</v>
       </c>
       <c r="C28">
-        <v>15.33260306250824</v>
+        <v>14.99404182405821</v>
       </c>
       <c r="D28">
-        <v>19.13300306250824</v>
+        <v>18.98984182405821</v>
       </c>
       <c r="E28">
-        <v>-3.559600000000001</v>
+        <v>-3.3642</v>
       </c>
       <c r="F28">
-        <v>5.0804</v>
+        <v>5.2758</v>
       </c>
       <c r="G28">
         <v>1.28</v>
@@ -3696,45 +3696,45 @@
         <v>1.115</v>
       </c>
       <c r="M28">
-        <v>0.31142852</v>
+        <v>0.33817878</v>
       </c>
       <c r="N28">
-        <v>0.8035714800000002</v>
+        <v>0.7768212200000002</v>
       </c>
       <c r="O28">
-        <v>0.1928571552</v>
+        <v>0.1864370928</v>
       </c>
       <c r="P28">
-        <v>0.6107143248000002</v>
+        <v>0.5903841272000001</v>
       </c>
       <c r="Q28">
-        <v>1.2957143248</v>
+        <v>1.2753841272</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1235332488878835</v>
+        <v>0.124396386323522</v>
       </c>
       <c r="T28">
-        <v>1.070027430123928</v>
+        <v>1.081908841814724</v>
       </c>
       <c r="U28">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V28">
         <v>0.24</v>
       </c>
       <c r="W28">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>3.580275820596008</v>
+        <v>3.297072631227779</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3742,22 +3742,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1039626820161711</v>
+        <v>0.1038445998553084</v>
       </c>
       <c r="C29">
-        <v>14.99404182405821</v>
+        <v>14.83727352386518</v>
       </c>
       <c r="D29">
-        <v>18.98984182405821</v>
+        <v>19.02847352386518</v>
       </c>
       <c r="E29">
-        <v>-3.3642</v>
+        <v>-3.1688</v>
       </c>
       <c r="F29">
-        <v>5.2758</v>
+        <v>5.471200000000001</v>
       </c>
       <c r="G29">
         <v>1.28</v>
@@ -3778,28 +3778,28 @@
         <v>1.115</v>
       </c>
       <c r="M29">
-        <v>0.33817878</v>
+        <v>0.3507039200000001</v>
       </c>
       <c r="N29">
-        <v>0.7768212200000002</v>
+        <v>0.7642960800000002</v>
       </c>
       <c r="O29">
-        <v>0.1864370928</v>
+        <v>0.1834310592</v>
       </c>
       <c r="P29">
-        <v>0.5903841272000001</v>
+        <v>0.5808650208000001</v>
       </c>
       <c r="Q29">
-        <v>1.2753841272</v>
+        <v>1.2658650208</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.124396386323522</v>
+        <v>0.1252834997990394</v>
       </c>
       <c r="T29">
-        <v>1.081908841814724</v>
+        <v>1.094120292719153</v>
       </c>
       <c r="U29">
         <v>0.0641</v>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.297072631227779</v>
+        <v>3.179320037255358</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3824,22 +3824,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1038445998553084</v>
+        <v>0.1037265176944457</v>
       </c>
       <c r="C30">
-        <v>14.83727352386518</v>
+        <v>14.68066272371781</v>
       </c>
       <c r="D30">
-        <v>19.02847352386518</v>
+        <v>19.06726272371781</v>
       </c>
       <c r="E30">
-        <v>-3.1688</v>
+        <v>-2.9734</v>
       </c>
       <c r="F30">
-        <v>5.471200000000001</v>
+        <v>5.666600000000001</v>
       </c>
       <c r="G30">
         <v>1.28</v>
@@ -3860,28 +3860,28 @@
         <v>1.115</v>
       </c>
       <c r="M30">
-        <v>0.3507039200000001</v>
+        <v>0.36322906</v>
       </c>
       <c r="N30">
-        <v>0.7642960800000002</v>
+        <v>0.7517709400000001</v>
       </c>
       <c r="O30">
-        <v>0.1834310592</v>
+        <v>0.1804250256</v>
       </c>
       <c r="P30">
-        <v>0.5808650208000001</v>
+        <v>0.5713459144000002</v>
       </c>
       <c r="Q30">
-        <v>1.2658650208</v>
+        <v>1.2563459144</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1252834997990394</v>
+        <v>0.1261956023865432</v>
       </c>
       <c r="T30">
-        <v>1.094120292719153</v>
+        <v>1.106675728156101</v>
       </c>
       <c r="U30">
         <v>0.0641</v>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.179320037255358</v>
+        <v>3.069688311832759</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3906,22 +3906,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1037265176944457</v>
+        <v>0.1053868355335829</v>
       </c>
       <c r="C31">
-        <v>14.68066272371781</v>
+        <v>13.95397563387288</v>
       </c>
       <c r="D31">
-        <v>19.06726272371781</v>
+        <v>18.53597563387288</v>
       </c>
       <c r="E31">
-        <v>-2.973400000000002</v>
+        <v>-2.778000000000001</v>
       </c>
       <c r="F31">
-        <v>5.666599999999999</v>
+        <v>5.861999999999999</v>
       </c>
       <c r="G31">
         <v>1.28</v>
@@ -3942,45 +3942,45 @@
         <v>1.115</v>
       </c>
       <c r="M31">
-        <v>0.3632290599999999</v>
+        <v>0.4214778</v>
       </c>
       <c r="N31">
-        <v>0.7517709400000003</v>
+        <v>0.6935222000000003</v>
       </c>
       <c r="O31">
-        <v>0.1804250256000001</v>
+        <v>0.1664453280000001</v>
       </c>
       <c r="P31">
-        <v>0.5713459144000003</v>
+        <v>0.5270768720000003</v>
       </c>
       <c r="Q31">
-        <v>1.2563459144</v>
+        <v>1.212076872</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1261956023865432</v>
+        <v>0.1271337650479756</v>
       </c>
       <c r="T31">
-        <v>1.106675728156101</v>
+        <v>1.119589890319819</v>
       </c>
       <c r="U31">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V31">
         <v>0.24</v>
       </c>
       <c r="W31">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>3.06968831183276</v>
+        <v>2.645453687003207</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3988,22 +3988,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1053868355335829</v>
+        <v>0.1053280333727202</v>
       </c>
       <c r="C32">
-        <v>13.95397563387288</v>
+        <v>13.77688558565888</v>
       </c>
       <c r="D32">
-        <v>18.53597563387288</v>
+        <v>18.55428558565888</v>
       </c>
       <c r="E32">
-        <v>-2.778000000000001</v>
+        <v>-2.582600000000001</v>
       </c>
       <c r="F32">
-        <v>5.861999999999999</v>
+        <v>6.057399999999999</v>
       </c>
       <c r="G32">
         <v>1.28</v>
@@ -4024,28 +4024,28 @@
         <v>1.115</v>
       </c>
       <c r="M32">
-        <v>0.4214778</v>
+        <v>0.43552706</v>
       </c>
       <c r="N32">
-        <v>0.6935222000000003</v>
+        <v>0.6794729400000001</v>
       </c>
       <c r="O32">
-        <v>0.1664453280000001</v>
+        <v>0.1630735056</v>
       </c>
       <c r="P32">
-        <v>0.5270768720000003</v>
+        <v>0.5163994344000001</v>
       </c>
       <c r="Q32">
-        <v>1.212076872</v>
+        <v>1.2013994344</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1271337650479756</v>
+        <v>0.1280991208300293</v>
       </c>
       <c r="T32">
-        <v>1.119589890319819</v>
+        <v>1.132878376024515</v>
       </c>
       <c r="U32">
         <v>0.07190000000000001</v>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.645453687003207</v>
+        <v>2.560116471293425</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4070,22 +4070,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1053280333727202</v>
+        <v>0.1062177112118575</v>
       </c>
       <c r="C33">
-        <v>13.77688558565888</v>
+        <v>13.3082654259494</v>
       </c>
       <c r="D33">
-        <v>18.55428558565888</v>
+        <v>18.2810654259494</v>
       </c>
       <c r="E33">
-        <v>-2.582600000000001</v>
+        <v>-2.387200000000001</v>
       </c>
       <c r="F33">
-        <v>6.057399999999999</v>
+        <v>6.2528</v>
       </c>
       <c r="G33">
         <v>1.28</v>
@@ -4106,45 +4106,45 @@
         <v>1.115</v>
       </c>
       <c r="M33">
-        <v>0.43552706</v>
+        <v>0.47396224</v>
       </c>
       <c r="N33">
-        <v>0.6794729400000001</v>
+        <v>0.6410377600000001</v>
       </c>
       <c r="O33">
-        <v>0.1630735056</v>
+        <v>0.1538490624</v>
       </c>
       <c r="P33">
-        <v>0.5163994344000001</v>
+        <v>0.4871886976000001</v>
       </c>
       <c r="Q33">
-        <v>1.2013994344</v>
+        <v>1.1721886976</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1280991208300293</v>
+        <v>0.1290928694292023</v>
       </c>
       <c r="T33">
-        <v>1.132878376024515</v>
+        <v>1.146557699544054</v>
       </c>
       <c r="U33">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V33">
         <v>0.24</v>
       </c>
       <c r="W33">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y33">
-        <v>2.560116471293425</v>
+        <v>2.352508081656463</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4152,22 +4152,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1062177112118575</v>
+        <v>0.1061885490509948</v>
       </c>
       <c r="C34">
-        <v>13.3082654259494</v>
+        <v>13.12169351304656</v>
       </c>
       <c r="D34">
-        <v>18.2810654259494</v>
+        <v>18.28989351304656</v>
       </c>
       <c r="E34">
-        <v>-2.387200000000001</v>
+        <v>-2.191800000000001</v>
       </c>
       <c r="F34">
-        <v>6.2528</v>
+        <v>6.4482</v>
       </c>
       <c r="G34">
         <v>1.28</v>
@@ -4188,28 +4188,28 @@
         <v>1.115</v>
       </c>
       <c r="M34">
-        <v>0.47396224</v>
+        <v>0.4887735600000001</v>
       </c>
       <c r="N34">
-        <v>0.6410377600000001</v>
+        <v>0.6262264400000002</v>
       </c>
       <c r="O34">
-        <v>0.1538490624</v>
+        <v>0.1502943456</v>
       </c>
       <c r="P34">
-        <v>0.4871886976000001</v>
+        <v>0.4759320944000001</v>
       </c>
       <c r="Q34">
-        <v>1.1721886976</v>
+        <v>1.1609320944</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1290928694292023</v>
+        <v>0.1301162821656639</v>
       </c>
       <c r="T34">
-        <v>1.146557699544054</v>
+        <v>1.160645361079102</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.352508081656463</v>
+        <v>2.281219957969904</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4234,22 +4234,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1061885490509948</v>
+        <v>0.1061593868901321</v>
       </c>
       <c r="C35">
-        <v>13.12169351304656</v>
+        <v>12.93513013058477</v>
       </c>
       <c r="D35">
-        <v>18.28989351304656</v>
+        <v>18.29873013058477</v>
       </c>
       <c r="E35">
-        <v>-2.191800000000001</v>
+        <v>-1.9964</v>
       </c>
       <c r="F35">
-        <v>6.4482</v>
+        <v>6.6436</v>
       </c>
       <c r="G35">
         <v>1.28</v>
@@ -4270,28 +4270,28 @@
         <v>1.115</v>
       </c>
       <c r="M35">
-        <v>0.4887735600000001</v>
+        <v>0.50358488</v>
       </c>
       <c r="N35">
-        <v>0.6262264400000002</v>
+        <v>0.6114151200000002</v>
       </c>
       <c r="O35">
-        <v>0.1502943456</v>
+        <v>0.1467396288</v>
       </c>
       <c r="P35">
-        <v>0.4759320944000001</v>
+        <v>0.4646754912000002</v>
       </c>
       <c r="Q35">
-        <v>1.1609320944</v>
+        <v>1.1496754912</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1301162821656639</v>
+        <v>0.1311707074092911</v>
       </c>
       <c r="T35">
-        <v>1.160645361079102</v>
+        <v>1.175159921448546</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.281219957969904</v>
+        <v>2.21412525332373</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4316,22 +4316,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1061593868901321</v>
+        <v>0.1061302247292694</v>
       </c>
       <c r="C36">
-        <v>12.93513013058477</v>
+        <v>12.74857529093427</v>
       </c>
       <c r="D36">
-        <v>18.29873013058477</v>
+        <v>18.30757529093427</v>
       </c>
       <c r="E36">
-        <v>-1.9964</v>
+        <v>-1.801</v>
       </c>
       <c r="F36">
-        <v>6.6436</v>
+        <v>6.839</v>
       </c>
       <c r="G36">
         <v>1.28</v>
@@ -4352,28 +4352,28 @@
         <v>1.115</v>
       </c>
       <c r="M36">
-        <v>0.50358488</v>
+        <v>0.5183962000000001</v>
       </c>
       <c r="N36">
-        <v>0.6114151200000002</v>
+        <v>0.5966038000000001</v>
       </c>
       <c r="O36">
-        <v>0.1467396288</v>
+        <v>0.143184912</v>
       </c>
       <c r="P36">
-        <v>0.4646754912000002</v>
+        <v>0.4534188880000001</v>
       </c>
       <c r="Q36">
-        <v>1.1496754912</v>
+        <v>1.138418888</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1311707074092911</v>
+        <v>0.1322575765065683</v>
       </c>
       <c r="T36">
-        <v>1.175159921448546</v>
+        <v>1.190121083675511</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.21412525332373</v>
+        <v>2.150864531800194</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4398,22 +4398,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1061302247292694</v>
+        <v>0.1061010625684067</v>
       </c>
       <c r="C37">
-        <v>12.74857529093427</v>
+        <v>12.5620290064892</v>
       </c>
       <c r="D37">
-        <v>18.30757529093427</v>
+        <v>18.3164290064892</v>
       </c>
       <c r="E37">
-        <v>-1.801</v>
+        <v>-1.6056</v>
       </c>
       <c r="F37">
-        <v>6.839</v>
+        <v>7.034400000000001</v>
       </c>
       <c r="G37">
         <v>1.28</v>
@@ -4434,28 +4434,28 @@
         <v>1.115</v>
       </c>
       <c r="M37">
-        <v>0.5183962000000001</v>
+        <v>0.53320752</v>
       </c>
       <c r="N37">
-        <v>0.5966038000000001</v>
+        <v>0.5817924800000002</v>
       </c>
       <c r="O37">
-        <v>0.143184912</v>
+        <v>0.1396301952</v>
       </c>
       <c r="P37">
-        <v>0.4534188880000001</v>
+        <v>0.4421622848000001</v>
       </c>
       <c r="Q37">
-        <v>1.138418888</v>
+        <v>1.1271622848</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1322575765065683</v>
+        <v>0.1333784102631354</v>
       </c>
       <c r="T37">
-        <v>1.190121083675511</v>
+        <v>1.205549782222069</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.150864531800194</v>
+        <v>2.091118294805745</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4480,22 +4480,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1061010625684067</v>
+        <v>0.1060719004075439</v>
       </c>
       <c r="C38">
-        <v>12.5620290064892</v>
+        <v>12.3754912896677</v>
       </c>
       <c r="D38">
-        <v>18.31642900648919</v>
+        <v>18.3252912896677</v>
       </c>
       <c r="E38">
-        <v>-1.605600000000001</v>
+        <v>-1.410200000000001</v>
       </c>
       <c r="F38">
-        <v>7.0344</v>
+        <v>7.2298</v>
       </c>
       <c r="G38">
         <v>1.28</v>
@@ -4516,28 +4516,28 @@
         <v>1.115</v>
       </c>
       <c r="M38">
-        <v>0.53320752</v>
+        <v>0.54801884</v>
       </c>
       <c r="N38">
-        <v>0.5817924800000002</v>
+        <v>0.5669811600000002</v>
       </c>
       <c r="O38">
-        <v>0.1396301952</v>
+        <v>0.1360754784</v>
       </c>
       <c r="P38">
-        <v>0.4421622848000001</v>
+        <v>0.4309056816000002</v>
       </c>
       <c r="Q38">
-        <v>1.1271622848</v>
+        <v>1.1159056816</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1333784102631354</v>
+        <v>0.1345348260437206</v>
       </c>
       <c r="T38">
-        <v>1.205549782222068</v>
+        <v>1.221468280722485</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.091118294805745</v>
+        <v>2.03460158413532</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4562,22 +4562,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1060719004075439</v>
+        <v>0.1101436982466812</v>
       </c>
       <c r="C39">
-        <v>12.3754912896677</v>
+        <v>11.02043022715364</v>
       </c>
       <c r="D39">
-        <v>18.3252912896677</v>
+        <v>17.16563022715363</v>
       </c>
       <c r="E39">
-        <v>-1.410200000000001</v>
+        <v>-1.214800000000001</v>
       </c>
       <c r="F39">
-        <v>7.2298</v>
+        <v>7.425199999999999</v>
       </c>
       <c r="G39">
         <v>1.28</v>
@@ -4598,45 +4598,45 @@
         <v>1.115</v>
       </c>
       <c r="M39">
-        <v>0.54801884</v>
+        <v>0.6682679999999999</v>
       </c>
       <c r="N39">
-        <v>0.5669811600000002</v>
+        <v>0.4467320000000004</v>
       </c>
       <c r="O39">
-        <v>0.1360754784</v>
+        <v>0.1072156800000001</v>
       </c>
       <c r="P39">
-        <v>0.4309056816000002</v>
+        <v>0.3395163200000003</v>
       </c>
       <c r="Q39">
-        <v>1.1159056816</v>
+        <v>1.02451632</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1345348260437206</v>
+        <v>0.1357285455591633</v>
       </c>
       <c r="T39">
-        <v>1.221468280722485</v>
+        <v>1.237900279174528</v>
       </c>
       <c r="U39">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V39">
         <v>0.24</v>
       </c>
       <c r="W39">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.03460158413532</v>
+        <v>1.668492281539742</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4644,22 +4644,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1101436982466812</v>
+        <v>0.1102224560858185</v>
       </c>
       <c r="C40">
-        <v>11.02043022715364</v>
+        <v>10.80404487474299</v>
       </c>
       <c r="D40">
-        <v>17.16563022715363</v>
+        <v>17.14464487474299</v>
       </c>
       <c r="E40">
-        <v>-1.214800000000001</v>
+        <v>-1.019400000000001</v>
       </c>
       <c r="F40">
-        <v>7.425199999999999</v>
+        <v>7.6206</v>
       </c>
       <c r="G40">
         <v>1.28</v>
@@ -4680,28 +4680,28 @@
         <v>1.115</v>
       </c>
       <c r="M40">
-        <v>0.6682679999999999</v>
+        <v>0.685854</v>
       </c>
       <c r="N40">
-        <v>0.4467320000000004</v>
+        <v>0.4291460000000002</v>
       </c>
       <c r="O40">
-        <v>0.1072156800000001</v>
+        <v>0.1029950400000001</v>
       </c>
       <c r="P40">
-        <v>0.3395163200000003</v>
+        <v>0.3261509600000002</v>
       </c>
       <c r="Q40">
-        <v>1.02451632</v>
+        <v>1.01115096</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1357285455591633</v>
+        <v>0.1369614034193746</v>
       </c>
       <c r="T40">
-        <v>1.237900279174528</v>
+        <v>1.254871031674178</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.668492281539742</v>
+        <v>1.625710428166928</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4726,22 +4726,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1102224560858185</v>
+        <v>0.1103012139249558</v>
       </c>
       <c r="C41">
-        <v>10.80404487474299</v>
+        <v>10.58771076977123</v>
       </c>
       <c r="D41">
-        <v>17.14464487474299</v>
+        <v>17.12371076977123</v>
       </c>
       <c r="E41">
-        <v>-1.019400000000001</v>
+        <v>-0.8240000000000007</v>
       </c>
       <c r="F41">
-        <v>7.6206</v>
+        <v>7.816</v>
       </c>
       <c r="G41">
         <v>1.28</v>
@@ -4762,28 +4762,28 @@
         <v>1.115</v>
       </c>
       <c r="M41">
-        <v>0.685854</v>
+        <v>0.70344</v>
       </c>
       <c r="N41">
-        <v>0.4291460000000002</v>
+        <v>0.4115600000000003</v>
       </c>
       <c r="O41">
-        <v>0.1029950400000001</v>
+        <v>0.09877440000000005</v>
       </c>
       <c r="P41">
-        <v>0.3261509600000002</v>
+        <v>0.3127856000000002</v>
       </c>
       <c r="Q41">
-        <v>1.01115096</v>
+        <v>0.9977856000000003</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1369614034193746</v>
+        <v>0.138235356541593</v>
       </c>
       <c r="T41">
-        <v>1.254871031674178</v>
+        <v>1.272407475923818</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.625710428166928</v>
+        <v>1.585067667462755</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4808,22 +4808,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1103012139249558</v>
+        <v>0.1103799717640931</v>
       </c>
       <c r="C42">
-        <v>10.58771076977123</v>
+        <v>10.37142772474351</v>
       </c>
       <c r="D42">
-        <v>17.12371076977123</v>
+        <v>17.10282772474351</v>
       </c>
       <c r="E42">
-        <v>-0.8240000000000007</v>
+        <v>-0.6286000000000005</v>
       </c>
       <c r="F42">
-        <v>7.816</v>
+        <v>8.0114</v>
       </c>
       <c r="G42">
         <v>1.28</v>
@@ -4844,28 +4844,28 @@
         <v>1.115</v>
       </c>
       <c r="M42">
-        <v>0.70344</v>
+        <v>0.7210259999999999</v>
       </c>
       <c r="N42">
-        <v>0.4115600000000003</v>
+        <v>0.3939740000000003</v>
       </c>
       <c r="O42">
-        <v>0.09877440000000005</v>
+        <v>0.09455376000000006</v>
       </c>
       <c r="P42">
-        <v>0.3127856000000002</v>
+        <v>0.2994202400000002</v>
       </c>
       <c r="Q42">
-        <v>0.9977856000000003</v>
+        <v>0.9844202400000003</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.138235356541593</v>
+        <v>0.139552494515412</v>
       </c>
       <c r="T42">
-        <v>1.272407475923818</v>
+        <v>1.290538375910733</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.585067667462755</v>
+        <v>1.546407480451468</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4890,22 +4890,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1103799717640931</v>
+        <v>0.1104587296032304</v>
       </c>
       <c r="C43">
-        <v>10.37142772474351</v>
+        <v>10.15519555307846</v>
       </c>
       <c r="D43">
-        <v>17.10282772474351</v>
+        <v>17.08199555307846</v>
       </c>
       <c r="E43">
-        <v>-0.6286000000000005</v>
+        <v>-0.4331999999999994</v>
       </c>
       <c r="F43">
-        <v>8.0114</v>
+        <v>8.206800000000001</v>
       </c>
       <c r="G43">
         <v>1.28</v>
@@ -4926,28 +4926,28 @@
         <v>1.115</v>
       </c>
       <c r="M43">
-        <v>0.7210259999999999</v>
+        <v>0.738612</v>
       </c>
       <c r="N43">
-        <v>0.3939740000000003</v>
+        <v>0.3763880000000002</v>
       </c>
       <c r="O43">
-        <v>0.09455376000000006</v>
+        <v>0.09033312000000003</v>
       </c>
       <c r="P43">
-        <v>0.2994202400000002</v>
+        <v>0.2860548800000001</v>
       </c>
       <c r="Q43">
-        <v>0.9844202400000003</v>
+        <v>0.9710548800000002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.139552494515412</v>
+        <v>0.1409150510400524</v>
       </c>
       <c r="T43">
-        <v>1.290538375910733</v>
+        <v>1.309294479345473</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.546407480451468</v>
+        <v>1.509588254726433</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1104587296032304</v>
+        <v>0.1311624849326474</v>
       </c>
       <c r="C44">
-        <v>10.15519555307846</v>
+        <v>5.816740711737193</v>
       </c>
       <c r="D44">
-        <v>17.08199555307845</v>
+        <v>12.93894071173719</v>
       </c>
       <c r="E44">
-        <v>-0.4332000000000011</v>
+        <v>-0.2378000000000018</v>
       </c>
       <c r="F44">
-        <v>8.206799999999999</v>
+        <v>8.402199999999999</v>
       </c>
       <c r="G44">
         <v>1.28</v>
@@ -5008,45 +5008,45 @@
         <v>1.115</v>
       </c>
       <c r="M44">
-        <v>0.7386119999999999</v>
+        <v>1.23344296</v>
       </c>
       <c r="N44">
-        <v>0.3763880000000003</v>
+        <v>-0.1184429599999997</v>
       </c>
       <c r="O44">
-        <v>0.09033312000000006</v>
+        <v>-0.02842631039999991</v>
       </c>
       <c r="P44">
-        <v>0.2860548800000002</v>
+        <v>-0.09001664959999973</v>
       </c>
       <c r="Q44">
-        <v>0.9710548800000003</v>
+        <v>0.5949833504000003</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1409150510400524</v>
+        <v>0.1433920518939045</v>
       </c>
       <c r="T44">
-        <v>1.309294479345472</v>
+        <v>1.343391328454211</v>
       </c>
       <c r="U44">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.24</v>
+        <v>0.2169536887218523</v>
       </c>
       <c r="W44">
-        <v>0.0684</v>
+        <v>0.1149511984956321</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y44">
-        <v>1.509588254726433</v>
+        <v>0.9039737030077177</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5054,22 +5054,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1311624849326474</v>
+        <v>0.1321724849326474</v>
       </c>
       <c r="C45">
-        <v>5.816740711737193</v>
+        <v>5.470038707064694</v>
       </c>
       <c r="D45">
-        <v>12.93894071173719</v>
+        <v>12.78763870706469</v>
       </c>
       <c r="E45">
-        <v>-0.2378000000000018</v>
+        <v>-0.04240000000000066</v>
       </c>
       <c r="F45">
-        <v>8.402199999999999</v>
+        <v>8.5976</v>
       </c>
       <c r="G45">
         <v>1.28</v>
@@ -5090,37 +5090,37 @@
         <v>1.115</v>
       </c>
       <c r="M45">
-        <v>1.23344296</v>
+        <v>1.26212768</v>
       </c>
       <c r="N45">
-        <v>-0.1184429599999997</v>
+        <v>-0.1471276799999999</v>
       </c>
       <c r="O45">
-        <v>-0.02842631039999991</v>
+        <v>-0.03531064319999997</v>
       </c>
       <c r="P45">
-        <v>-0.09001664959999973</v>
+        <v>-0.1118170367999999</v>
       </c>
       <c r="Q45">
-        <v>0.5949833504000003</v>
+        <v>0.5731829632000002</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1433920518939045</v>
+        <v>0.1451347671062957</v>
       </c>
       <c r="T45">
-        <v>1.343391328454211</v>
+        <v>1.367380459319465</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.2169536887218523</v>
+        <v>0.2120229230690829</v>
       </c>
       <c r="W45">
-        <v>0.1149511984956321</v>
+        <v>0.1156750348934587</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.9039737030077177</v>
+        <v>0.8834288461211786</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5136,22 +5136,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1321724849326474</v>
+        <v>0.1331824849326474</v>
       </c>
       <c r="C46">
-        <v>5.470038707064694</v>
+        <v>5.126834314638794</v>
       </c>
       <c r="D46">
-        <v>12.78763870706469</v>
+        <v>12.63983431463879</v>
       </c>
       <c r="E46">
-        <v>-0.04240000000000066</v>
+        <v>0.1529999999999987</v>
       </c>
       <c r="F46">
-        <v>8.5976</v>
+        <v>8.792999999999999</v>
       </c>
       <c r="G46">
         <v>1.28</v>
@@ -5172,37 +5172,37 @@
         <v>1.115</v>
       </c>
       <c r="M46">
-        <v>1.26212768</v>
+        <v>1.2908124</v>
       </c>
       <c r="N46">
-        <v>-0.1471276799999999</v>
+        <v>-0.1758123999999999</v>
       </c>
       <c r="O46">
-        <v>-0.03531064319999997</v>
+        <v>-0.04219497599999997</v>
       </c>
       <c r="P46">
-        <v>-0.1118170367999999</v>
+        <v>-0.1336174239999999</v>
       </c>
       <c r="Q46">
-        <v>0.5731829632000002</v>
+        <v>0.5513825760000002</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1451347671062957</v>
+        <v>0.1469408537809556</v>
       </c>
       <c r="T46">
-        <v>1.367380459319465</v>
+        <v>1.392241922216182</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.2120229230690829</v>
+        <v>0.2073113025564366</v>
       </c>
       <c r="W46">
-        <v>0.1156750348934587</v>
+        <v>0.1163667007847151</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8834288461211786</v>
+        <v>0.8637970939851525</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5218,22 +5218,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1331824849326474</v>
+        <v>0.1341924849326474</v>
       </c>
       <c r="C47">
-        <v>5.126834314638794</v>
+        <v>4.787007640046347</v>
       </c>
       <c r="D47">
-        <v>12.63983431463879</v>
+        <v>12.49540764004635</v>
       </c>
       <c r="E47">
-        <v>0.1529999999999987</v>
+        <v>0.3483999999999998</v>
       </c>
       <c r="F47">
-        <v>8.792999999999999</v>
+        <v>8.9884</v>
       </c>
       <c r="G47">
         <v>1.28</v>
@@ -5254,37 +5254,37 @@
         <v>1.115</v>
       </c>
       <c r="M47">
-        <v>1.2908124</v>
+        <v>1.31949712</v>
       </c>
       <c r="N47">
-        <v>-0.1758123999999999</v>
+        <v>-0.2044971199999999</v>
       </c>
       <c r="O47">
-        <v>-0.04219497599999997</v>
+        <v>-0.04907930879999996</v>
       </c>
       <c r="P47">
-        <v>-0.1336174239999999</v>
+        <v>-0.1554178111999999</v>
       </c>
       <c r="Q47">
-        <v>0.5513825760000002</v>
+        <v>0.5295821888000002</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1469408537809556</v>
+        <v>0.148813832554677</v>
       </c>
       <c r="T47">
-        <v>1.392241922216182</v>
+        <v>1.418024180035</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.2073113025564366</v>
+        <v>0.2028045351095575</v>
       </c>
       <c r="W47">
-        <v>0.1163667007847151</v>
+        <v>0.117028294245917</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8637970939851525</v>
+        <v>0.8450188962898231</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5300,22 +5300,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1341924849326474</v>
+        <v>0.1352024849326474</v>
       </c>
       <c r="C48">
-        <v>4.787007640046347</v>
+        <v>4.450444206770925</v>
       </c>
       <c r="D48">
-        <v>12.49540764004635</v>
+        <v>12.35424420677093</v>
       </c>
       <c r="E48">
-        <v>0.3483999999999998</v>
+        <v>0.5437999999999992</v>
       </c>
       <c r="F48">
-        <v>8.9884</v>
+        <v>9.1838</v>
       </c>
       <c r="G48">
         <v>1.28</v>
@@ -5336,37 +5336,37 @@
         <v>1.115</v>
       </c>
       <c r="M48">
-        <v>1.31949712</v>
+        <v>1.34818184</v>
       </c>
       <c r="N48">
-        <v>-0.2044971199999999</v>
+        <v>-0.2331818399999999</v>
       </c>
       <c r="O48">
-        <v>-0.04907930879999996</v>
+        <v>-0.05596364159999997</v>
       </c>
       <c r="P48">
-        <v>-0.1554178111999999</v>
+        <v>-0.1772181983999999</v>
       </c>
       <c r="Q48">
-        <v>0.5295821888000002</v>
+        <v>0.5077818016000002</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.148813832554677</v>
+        <v>0.1507574897726898</v>
       </c>
       <c r="T48">
-        <v>1.418024180035</v>
+        <v>1.444779353243208</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.2028045351095575</v>
+        <v>0.1984895450008435</v>
       </c>
       <c r="W48">
-        <v>0.117028294245917</v>
+        <v>0.1176617347938762</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8450188962898231</v>
+        <v>0.827039770836848</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5382,22 +5382,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1352024849326474</v>
+        <v>0.1362124849326474</v>
       </c>
       <c r="C49">
-        <v>4.450444206770925</v>
+        <v>4.117034653575546</v>
       </c>
       <c r="D49">
-        <v>12.35424420677093</v>
+        <v>12.21623465357555</v>
       </c>
       <c r="E49">
-        <v>0.5437999999999992</v>
+        <v>0.7392000000000003</v>
       </c>
       <c r="F49">
-        <v>9.1838</v>
+        <v>9.379200000000001</v>
       </c>
       <c r="G49">
         <v>1.28</v>
@@ -5418,37 +5418,37 @@
         <v>1.115</v>
       </c>
       <c r="M49">
-        <v>1.34818184</v>
+        <v>1.37686656</v>
       </c>
       <c r="N49">
-        <v>-0.2331818399999999</v>
+        <v>-0.2618665600000001</v>
       </c>
       <c r="O49">
-        <v>-0.05596364159999997</v>
+        <v>-0.06284797440000002</v>
       </c>
       <c r="P49">
-        <v>-0.1772181983999999</v>
+        <v>-0.1990185856000001</v>
       </c>
       <c r="Q49">
-        <v>0.5077818016000002</v>
+        <v>0.4859814144</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1507574897726898</v>
+        <v>0.1527759030375492</v>
       </c>
       <c r="T49">
-        <v>1.444779353243208</v>
+        <v>1.472563571574808</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.1984895450008435</v>
+        <v>0.1943543461466593</v>
       </c>
       <c r="W49">
-        <v>0.1176617347938762</v>
+        <v>0.1182687819856704</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.827039770836848</v>
+        <v>0.8098097756110803</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5464,22 +5464,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1362124849326474</v>
+        <v>0.1652216545647026</v>
       </c>
       <c r="C50">
-        <v>4.117034653575548</v>
+        <v>0.9541424962921248</v>
       </c>
       <c r="D50">
-        <v>12.21623465357555</v>
+        <v>9.248742496292126</v>
       </c>
       <c r="E50">
-        <v>0.7391999999999985</v>
+        <v>0.9345999999999997</v>
       </c>
       <c r="F50">
-        <v>9.379199999999999</v>
+        <v>9.5746</v>
       </c>
       <c r="G50">
         <v>1.28</v>
@@ -5500,45 +5500,45 @@
         <v>1.115</v>
       </c>
       <c r="M50">
-        <v>1.37686656</v>
+        <v>1.92257968</v>
       </c>
       <c r="N50">
-        <v>-0.2618665599999999</v>
+        <v>-0.8075796799999999</v>
       </c>
       <c r="O50">
-        <v>-0.06284797439999996</v>
+        <v>-0.1938191232</v>
       </c>
       <c r="P50">
-        <v>-0.1990185855999999</v>
+        <v>-0.6137605568</v>
       </c>
       <c r="Q50">
-        <v>0.4859814144000001</v>
+        <v>0.07123944320000009</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1527759030375492</v>
+        <v>0.1578914494344722</v>
       </c>
       <c r="T50">
-        <v>1.472563571574808</v>
+        <v>1.542980993245607</v>
       </c>
       <c r="U50">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1943543461466593</v>
+        <v>0.1391879893373262</v>
       </c>
       <c r="W50">
-        <v>0.1182687819856704</v>
+        <v>0.1728510517410649</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y50">
-        <v>0.8098097756110804</v>
+        <v>0.5799499555721925</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5546,22 +5546,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1652216545647026</v>
+        <v>0.1667716545647026</v>
       </c>
       <c r="C51">
-        <v>0.9541424962921248</v>
+        <v>0.6402391086941197</v>
       </c>
       <c r="D51">
-        <v>9.248742496292126</v>
+        <v>9.13023910869412</v>
       </c>
       <c r="E51">
-        <v>0.9345999999999997</v>
+        <v>1.129999999999999</v>
       </c>
       <c r="F51">
-        <v>9.5746</v>
+        <v>9.77</v>
       </c>
       <c r="G51">
         <v>1.28</v>
@@ -5582,37 +5582,37 @@
         <v>1.115</v>
       </c>
       <c r="M51">
-        <v>1.92257968</v>
+        <v>1.961816</v>
       </c>
       <c r="N51">
-        <v>-0.8075796799999999</v>
+        <v>-0.8468159999999998</v>
       </c>
       <c r="O51">
-        <v>-0.1938191232</v>
+        <v>-0.2032358399999999</v>
       </c>
       <c r="P51">
-        <v>-0.6137605568</v>
+        <v>-0.6435801599999998</v>
       </c>
       <c r="Q51">
-        <v>0.07123944320000009</v>
+        <v>0.04141984000000021</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1578914494344722</v>
+        <v>0.1601332784231617</v>
       </c>
       <c r="T51">
-        <v>1.542980993245607</v>
+        <v>1.573840613110519</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1391879893373262</v>
+        <v>0.1364042295505797</v>
       </c>
       <c r="W51">
-        <v>0.1728510517410649</v>
+        <v>0.1734100307062436</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5799499555721925</v>
+        <v>0.5683509564607487</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5628,22 +5628,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1667716545647026</v>
+        <v>0.1683216545647026</v>
       </c>
       <c r="C52">
-        <v>0.6402391086941197</v>
+        <v>0.3293340523124169</v>
       </c>
       <c r="D52">
-        <v>9.13023910869412</v>
+        <v>9.014734052312416</v>
       </c>
       <c r="E52">
-        <v>1.129999999999999</v>
+        <v>1.325399999999998</v>
       </c>
       <c r="F52">
-        <v>9.77</v>
+        <v>9.965399999999999</v>
       </c>
       <c r="G52">
         <v>1.28</v>
@@ -5664,37 +5664,37 @@
         <v>1.115</v>
       </c>
       <c r="M52">
-        <v>1.961816</v>
+        <v>2.00105232</v>
       </c>
       <c r="N52">
-        <v>-0.8468159999999998</v>
+        <v>-0.8860523199999997</v>
       </c>
       <c r="O52">
-        <v>-0.2032358399999999</v>
+        <v>-0.2126525567999999</v>
       </c>
       <c r="P52">
-        <v>-0.6435801599999998</v>
+        <v>-0.6733997631999997</v>
       </c>
       <c r="Q52">
-        <v>0.04141984000000021</v>
+        <v>0.01160023680000033</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1601332784231617</v>
+        <v>0.1624666106358792</v>
       </c>
       <c r="T52">
-        <v>1.573840613110519</v>
+        <v>1.605959809296448</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1364042295505797</v>
+        <v>0.1337296368142938</v>
       </c>
       <c r="W52">
-        <v>0.1734100307062436</v>
+        <v>0.1739470889276898</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5683509564607487</v>
+        <v>0.5572068200595577</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5710,22 +5710,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1683216545647026</v>
+        <v>0.1698716545647026</v>
       </c>
       <c r="C53">
-        <v>0.3293340523124169</v>
+        <v>0.02131495466189115</v>
       </c>
       <c r="D53">
-        <v>9.014734052312416</v>
+        <v>8.902114954661892</v>
       </c>
       <c r="E53">
-        <v>1.325399999999998</v>
+        <v>1.520799999999999</v>
       </c>
       <c r="F53">
-        <v>9.965399999999999</v>
+        <v>10.1608</v>
       </c>
       <c r="G53">
         <v>1.28</v>
@@ -5746,37 +5746,37 @@
         <v>1.115</v>
       </c>
       <c r="M53">
-        <v>2.00105232</v>
+        <v>2.04028864</v>
       </c>
       <c r="N53">
-        <v>-0.8860523199999997</v>
+        <v>-0.9252886399999998</v>
       </c>
       <c r="O53">
-        <v>-0.2126525567999999</v>
+        <v>-0.2220692736</v>
       </c>
       <c r="P53">
-        <v>-0.6733997631999997</v>
+        <v>-0.7032193663999998</v>
       </c>
       <c r="Q53">
-        <v>0.01160023680000033</v>
+        <v>-0.01821936639999977</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1624666106358792</v>
+        <v>0.1648971650241267</v>
       </c>
       <c r="T53">
-        <v>1.605959809296448</v>
+        <v>1.639417305323458</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1337296368142938</v>
+        <v>0.1311579130294036</v>
       </c>
       <c r="W53">
-        <v>0.1739470889276898</v>
+        <v>0.1744634910636958</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5572068200595577</v>
+        <v>0.5464913042891815</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5792,22 +5792,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1698716545647026</v>
+        <v>0.1714216545647027</v>
       </c>
       <c r="C54">
-        <v>0.02131495466189115</v>
+        <v>-0.2839250106493356</v>
       </c>
       <c r="D54">
-        <v>8.902114954661892</v>
+        <v>8.792274989350664</v>
       </c>
       <c r="E54">
-        <v>1.520799999999999</v>
+        <v>1.716199999999999</v>
       </c>
       <c r="F54">
-        <v>10.1608</v>
+        <v>10.3562</v>
       </c>
       <c r="G54">
         <v>1.28</v>
@@ -5828,37 +5828,37 @@
         <v>1.115</v>
       </c>
       <c r="M54">
-        <v>2.04028864</v>
+        <v>2.07952496</v>
       </c>
       <c r="N54">
-        <v>-0.9252886399999998</v>
+        <v>-0.9645249599999999</v>
       </c>
       <c r="O54">
-        <v>-0.2220692736</v>
+        <v>-0.2314859904</v>
       </c>
       <c r="P54">
-        <v>-0.7032193663999998</v>
+        <v>-0.7330389695999999</v>
       </c>
       <c r="Q54">
-        <v>-0.01821936639999977</v>
+        <v>-0.04803896959999987</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1648971650241267</v>
+        <v>0.1674311472586826</v>
       </c>
       <c r="T54">
-        <v>1.639417305323458</v>
+        <v>1.674298524585659</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1311579130294036</v>
+        <v>0.1286832354250751</v>
       </c>
       <c r="W54">
-        <v>0.1744634910636958</v>
+        <v>0.1749604063266449</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5464913042891815</v>
+        <v>0.5361801476044799</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5874,22 +5874,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1714216545647027</v>
+        <v>0.1729716545647026</v>
       </c>
       <c r="C55">
-        <v>-0.2839250106493356</v>
+        <v>-0.5864874619057989</v>
       </c>
       <c r="D55">
-        <v>8.792274989350664</v>
+        <v>8.685112538094202</v>
       </c>
       <c r="E55">
-        <v>1.716199999999999</v>
+        <v>1.9116</v>
       </c>
       <c r="F55">
-        <v>10.3562</v>
+        <v>10.5516</v>
       </c>
       <c r="G55">
         <v>1.28</v>
@@ -5910,37 +5910,37 @@
         <v>1.115</v>
       </c>
       <c r="M55">
-        <v>2.07952496</v>
+        <v>2.11876128</v>
       </c>
       <c r="N55">
-        <v>-0.9645249599999999</v>
+        <v>-1.00376128</v>
       </c>
       <c r="O55">
-        <v>-0.2314859904</v>
+        <v>-0.2409027072</v>
       </c>
       <c r="P55">
-        <v>-0.7330389695999999</v>
+        <v>-0.7628585728</v>
       </c>
       <c r="Q55">
-        <v>-0.04803896959999987</v>
+        <v>-0.07785857279999997</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1674311472586826</v>
+        <v>0.1700753026338714</v>
       </c>
       <c r="T55">
-        <v>1.674298524585659</v>
+        <v>1.710696318598391</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1286832354250751</v>
+        <v>0.126300212546833</v>
       </c>
       <c r="W55">
-        <v>0.1749604063266449</v>
+        <v>0.1754389173205959</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5361801476044799</v>
+        <v>0.5262508856118043</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5956,22 +5956,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1729716545647026</v>
+        <v>0.1745216545647026</v>
       </c>
       <c r="C56">
-        <v>-0.5864874619057989</v>
+        <v>-0.8864691228514268</v>
       </c>
       <c r="D56">
-        <v>8.685112538094202</v>
+        <v>8.580530877148574</v>
       </c>
       <c r="E56">
-        <v>1.9116</v>
+        <v>2.106999999999999</v>
       </c>
       <c r="F56">
-        <v>10.5516</v>
+        <v>10.747</v>
       </c>
       <c r="G56">
         <v>1.28</v>
@@ -5992,37 +5992,37 @@
         <v>1.115</v>
       </c>
       <c r="M56">
-        <v>2.11876128</v>
+        <v>2.1579976</v>
       </c>
       <c r="N56">
-        <v>-1.00376128</v>
+        <v>-1.0429976</v>
       </c>
       <c r="O56">
-        <v>-0.2409027072</v>
+        <v>-0.2503194239999999</v>
       </c>
       <c r="P56">
-        <v>-0.7628585728</v>
+        <v>-0.7926781759999997</v>
       </c>
       <c r="Q56">
-        <v>-0.07785857279999997</v>
+        <v>-0.1076781759999996</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1700753026338714</v>
+        <v>0.1728369760257352</v>
       </c>
       <c r="T56">
-        <v>1.710696318598391</v>
+        <v>1.748711792345022</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.126300212546833</v>
+        <v>0.1240038450459815</v>
       </c>
       <c r="W56">
-        <v>0.1754389173205959</v>
+        <v>0.1759000279147669</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5262508856118043</v>
+        <v>0.5166826876915898</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6038,22 +6038,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1745216545647026</v>
+        <v>0.1760716545647026</v>
       </c>
       <c r="C57">
-        <v>-0.8864691228514268</v>
+        <v>-1.183962113871008</v>
       </c>
       <c r="D57">
-        <v>8.580530877148574</v>
+        <v>8.478437886128994</v>
       </c>
       <c r="E57">
-        <v>2.106999999999999</v>
+        <v>2.3024</v>
       </c>
       <c r="F57">
-        <v>10.747</v>
+        <v>10.9424</v>
       </c>
       <c r="G57">
         <v>1.28</v>
@@ -6074,37 +6074,37 @@
         <v>1.115</v>
       </c>
       <c r="M57">
-        <v>2.1579976</v>
+        <v>2.19723392</v>
       </c>
       <c r="N57">
-        <v>-1.0429976</v>
+        <v>-1.08223392</v>
       </c>
       <c r="O57">
-        <v>-0.2503194239999999</v>
+        <v>-0.2597361408</v>
       </c>
       <c r="P57">
-        <v>-0.7926781759999997</v>
+        <v>-0.8224977792000001</v>
       </c>
       <c r="Q57">
-        <v>-0.1076781759999996</v>
+        <v>-0.1374977792000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1728369760257352</v>
+        <v>0.1757241800263201</v>
       </c>
       <c r="T57">
-        <v>1.748711792345022</v>
+        <v>1.788455242171045</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1240038450459815</v>
+        <v>0.1217894906701604</v>
       </c>
       <c r="W57">
-        <v>0.1759000279147669</v>
+        <v>0.1763446702734318</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5166826876915898</v>
+        <v>0.5074562111256684</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6120,22 +6120,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1760716545647026</v>
+        <v>0.1981927281023444</v>
       </c>
       <c r="C58">
-        <v>-1.183962113871008</v>
+        <v>-2.610077977409002</v>
       </c>
       <c r="D58">
-        <v>8.478437886128994</v>
+        <v>7.247722022590998</v>
       </c>
       <c r="E58">
-        <v>2.3024</v>
+        <v>2.4978</v>
       </c>
       <c r="F58">
-        <v>10.9424</v>
+        <v>11.1378</v>
       </c>
       <c r="G58">
         <v>1.28</v>
@@ -6156,45 +6156,45 @@
         <v>1.115</v>
       </c>
       <c r="M58">
-        <v>2.19723392</v>
+        <v>2.62629324</v>
       </c>
       <c r="N58">
-        <v>-1.08223392</v>
+        <v>-1.51129324</v>
       </c>
       <c r="O58">
-        <v>-0.2597361408</v>
+        <v>-0.3627103776</v>
       </c>
       <c r="P58">
-        <v>-0.8224977792000001</v>
+        <v>-1.1485828624</v>
       </c>
       <c r="Q58">
-        <v>-0.1374977792000001</v>
+        <v>-0.4635828624</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1757241800263201</v>
+        <v>0.1801900296493549</v>
       </c>
       <c r="T58">
-        <v>1.788455242171045</v>
+        <v>1.84992934320017</v>
       </c>
       <c r="U58">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.1217894906701604</v>
+        <v>0.1018926584146407</v>
       </c>
       <c r="W58">
-        <v>0.1763446702734318</v>
+        <v>0.2117737111458277</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.5074562111256684</v>
+        <v>0.4245527433943364</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6202,22 +6202,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1981927281023444</v>
+        <v>0.2000927281023444</v>
       </c>
       <c r="C59">
-        <v>-2.610077977409002</v>
+        <v>-2.894728274634863</v>
       </c>
       <c r="D59">
-        <v>7.247722022590998</v>
+        <v>7.158471725365139</v>
       </c>
       <c r="E59">
-        <v>2.4978</v>
+        <v>2.693200000000001</v>
       </c>
       <c r="F59">
-        <v>11.1378</v>
+        <v>11.3332</v>
       </c>
       <c r="G59">
         <v>1.28</v>
@@ -6238,37 +6238,37 @@
         <v>1.115</v>
       </c>
       <c r="M59">
-        <v>2.62629324</v>
+        <v>2.672368560000001</v>
       </c>
       <c r="N59">
-        <v>-1.51129324</v>
+        <v>-1.55736856</v>
       </c>
       <c r="O59">
-        <v>-0.3627103776</v>
+        <v>-0.3737684544000001</v>
       </c>
       <c r="P59">
-        <v>-1.1485828624</v>
+        <v>-1.1836001056</v>
       </c>
       <c r="Q59">
-        <v>-0.4635828624</v>
+        <v>-0.4986001056000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1801900296493549</v>
+        <v>0.1833897922600538</v>
       </c>
       <c r="T59">
-        <v>1.84992934320017</v>
+        <v>1.89397527994303</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.1018926584146407</v>
+        <v>0.1001358884419745</v>
       </c>
       <c r="W59">
-        <v>0.2117737111458277</v>
+        <v>0.2121879575053824</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4245527433943364</v>
+        <v>0.4172328685082271</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6284,22 +6284,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2000927281023444</v>
+        <v>0.2019927281023444</v>
       </c>
       <c r="C60">
-        <v>-2.894728274634856</v>
+        <v>-3.17720720874043</v>
       </c>
       <c r="D60">
-        <v>7.158471725365142</v>
+        <v>7.071392791259568</v>
       </c>
       <c r="E60">
-        <v>2.693199999999997</v>
+        <v>2.888599999999999</v>
       </c>
       <c r="F60">
-        <v>11.3332</v>
+        <v>11.5286</v>
       </c>
       <c r="G60">
         <v>1.28</v>
@@ -6320,37 +6320,37 @@
         <v>1.115</v>
       </c>
       <c r="M60">
-        <v>2.67236856</v>
+        <v>2.71844388</v>
       </c>
       <c r="N60">
-        <v>-1.55736856</v>
+        <v>-1.603443879999999</v>
       </c>
       <c r="O60">
-        <v>-0.3737684543999999</v>
+        <v>-0.3848265311999999</v>
       </c>
       <c r="P60">
-        <v>-1.1836001056</v>
+        <v>-1.2186173488</v>
       </c>
       <c r="Q60">
-        <v>-0.4986001055999996</v>
+        <v>-0.5336173487999996</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1833897922600538</v>
+        <v>0.1867456408517624</v>
       </c>
       <c r="T60">
-        <v>1.89397527994303</v>
+        <v>1.94016979896603</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.1001358884419745</v>
+        <v>0.09843866999380545</v>
       </c>
       <c r="W60">
-        <v>0.2121879575053824</v>
+        <v>0.2125881616154607</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4172328685082272</v>
+        <v>0.4101611249741894</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6366,22 +6366,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2019927281023444</v>
+        <v>0.2038927281023444</v>
       </c>
       <c r="C61">
-        <v>-3.17720720874043</v>
+        <v>-3.457593067765492</v>
       </c>
       <c r="D61">
-        <v>7.071392791259568</v>
+        <v>6.986406932234507</v>
       </c>
       <c r="E61">
-        <v>2.888599999999999</v>
+        <v>3.083999999999998</v>
       </c>
       <c r="F61">
-        <v>11.5286</v>
+        <v>11.724</v>
       </c>
       <c r="G61">
         <v>1.28</v>
@@ -6402,37 +6402,37 @@
         <v>1.115</v>
       </c>
       <c r="M61">
-        <v>2.71844388</v>
+        <v>2.7645192</v>
       </c>
       <c r="N61">
-        <v>-1.603443879999999</v>
+        <v>-1.649519199999999</v>
       </c>
       <c r="O61">
-        <v>-0.3848265311999999</v>
+        <v>-0.3958846079999999</v>
       </c>
       <c r="P61">
-        <v>-1.2186173488</v>
+        <v>-1.253634592</v>
       </c>
       <c r="Q61">
-        <v>-0.5336173487999996</v>
+        <v>-0.5686345919999996</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1867456408517624</v>
+        <v>0.1902692818730564</v>
       </c>
       <c r="T61">
-        <v>1.94016979896603</v>
+        <v>1.988674043940181</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.09843866999380545</v>
+        <v>0.0967980254939087</v>
       </c>
       <c r="W61">
-        <v>0.2125881616154607</v>
+        <v>0.2129750255885363</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4101611249741894</v>
+        <v>0.4033251062246196</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6448,22 +6448,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2038927281023444</v>
+        <v>0.2057927281023444</v>
       </c>
       <c r="C62">
-        <v>-3.457593067765492</v>
+        <v>-3.735960420898907</v>
       </c>
       <c r="D62">
-        <v>6.986406932234507</v>
+        <v>6.903439579101092</v>
       </c>
       <c r="E62">
-        <v>3.083999999999998</v>
+        <v>3.279399999999999</v>
       </c>
       <c r="F62">
-        <v>11.724</v>
+        <v>11.9194</v>
       </c>
       <c r="G62">
         <v>1.28</v>
@@ -6484,37 +6484,37 @@
         <v>1.115</v>
       </c>
       <c r="M62">
-        <v>2.7645192</v>
+        <v>2.81059452</v>
       </c>
       <c r="N62">
-        <v>-1.649519199999999</v>
+        <v>-1.69559452</v>
       </c>
       <c r="O62">
-        <v>-0.3958846079999999</v>
+        <v>-0.4069426848</v>
       </c>
       <c r="P62">
-        <v>-1.253634592</v>
+        <v>-1.2886518352</v>
       </c>
       <c r="Q62">
-        <v>-0.5686345919999996</v>
+        <v>-0.6036518351999998</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1902692818730564</v>
+        <v>0.1939736224339041</v>
       </c>
       <c r="T62">
-        <v>1.988674043940181</v>
+        <v>2.039665686092494</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.0967980254939087</v>
+        <v>0.09521117261695937</v>
       </c>
       <c r="W62">
-        <v>0.2129750255885363</v>
+        <v>0.213349205496921</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4033251062246196</v>
+        <v>0.3967132192373307</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6530,22 +6530,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2057927281023444</v>
+        <v>0.2076927281023444</v>
       </c>
       <c r="C63">
-        <v>-3.735960420898907</v>
+        <v>-4.012380336703897</v>
       </c>
       <c r="D63">
-        <v>6.903439579101092</v>
+        <v>6.822419663296102</v>
       </c>
       <c r="E63">
-        <v>3.279399999999999</v>
+        <v>3.474799999999998</v>
       </c>
       <c r="F63">
-        <v>11.9194</v>
+        <v>12.1148</v>
       </c>
       <c r="G63">
         <v>1.28</v>
@@ -6566,37 +6566,37 @@
         <v>1.115</v>
       </c>
       <c r="M63">
-        <v>2.81059452</v>
+        <v>2.85666984</v>
       </c>
       <c r="N63">
-        <v>-1.69559452</v>
+        <v>-1.74166984</v>
       </c>
       <c r="O63">
-        <v>-0.4069426848</v>
+        <v>-0.4180007615999999</v>
       </c>
       <c r="P63">
-        <v>-1.2886518352</v>
+        <v>-1.3236690784</v>
       </c>
       <c r="Q63">
-        <v>-0.6036518351999998</v>
+        <v>-0.6386690783999998</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1939736224339041</v>
+        <v>0.1978729282874279</v>
       </c>
       <c r="T63">
-        <v>2.039665686092494</v>
+        <v>2.093341098884402</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.09521117261695937</v>
+        <v>0.09367550854249228</v>
       </c>
       <c r="W63">
-        <v>0.213349205496921</v>
+        <v>0.2137113150856803</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3967132192373307</v>
+        <v>0.3903146189270512</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6612,22 +6612,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2076927281023444</v>
+        <v>0.2095927281023444</v>
       </c>
       <c r="C64">
-        <v>-4.012380336703897</v>
+        <v>-4.286920586154796</v>
       </c>
       <c r="D64">
-        <v>6.822419663296102</v>
+        <v>6.743279413845204</v>
       </c>
       <c r="E64">
-        <v>3.474799999999998</v>
+        <v>3.670199999999999</v>
       </c>
       <c r="F64">
-        <v>12.1148</v>
+        <v>12.3102</v>
       </c>
       <c r="G64">
         <v>1.28</v>
@@ -6648,37 +6648,37 @@
         <v>1.115</v>
       </c>
       <c r="M64">
-        <v>2.85666984</v>
+        <v>2.90274516</v>
       </c>
       <c r="N64">
-        <v>-1.74166984</v>
+        <v>-1.78774516</v>
       </c>
       <c r="O64">
-        <v>-0.4180007615999999</v>
+        <v>-0.4290588384</v>
       </c>
       <c r="P64">
-        <v>-1.3236690784</v>
+        <v>-1.3586863216</v>
       </c>
       <c r="Q64">
-        <v>-0.6386690783999998</v>
+        <v>-0.6736863216</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1978729282874279</v>
+        <v>0.2019830074303313</v>
       </c>
       <c r="T64">
-        <v>2.093341098884402</v>
+        <v>2.149917885340737</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.09367550854249228</v>
+        <v>0.09218859570848445</v>
       </c>
       <c r="W64">
-        <v>0.2137113150856803</v>
+        <v>0.2140619291319394</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3903146189270512</v>
+        <v>0.3841191487853519</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6694,22 +6694,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2095927281023444</v>
+        <v>0.2114927281023444</v>
       </c>
       <c r="C65">
-        <v>-4.286920586154796</v>
+        <v>-4.559645831704449</v>
       </c>
       <c r="D65">
-        <v>6.743279413845204</v>
+        <v>6.66595416829555</v>
       </c>
       <c r="E65">
-        <v>3.670199999999999</v>
+        <v>3.865599999999999</v>
       </c>
       <c r="F65">
-        <v>12.3102</v>
+        <v>12.5056</v>
       </c>
       <c r="G65">
         <v>1.28</v>
@@ -6730,37 +6730,37 @@
         <v>1.115</v>
       </c>
       <c r="M65">
-        <v>2.90274516</v>
+        <v>2.94882048</v>
       </c>
       <c r="N65">
-        <v>-1.78774516</v>
+        <v>-1.83382048</v>
       </c>
       <c r="O65">
-        <v>-0.4290588384</v>
+        <v>-0.4401169152</v>
       </c>
       <c r="P65">
-        <v>-1.3586863216</v>
+        <v>-1.3937035648</v>
       </c>
       <c r="Q65">
-        <v>-0.6736863216</v>
+        <v>-0.7087035648</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2019830074303313</v>
+        <v>0.2063214243033961</v>
       </c>
       <c r="T65">
-        <v>2.149917885340737</v>
+        <v>2.209637826600202</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.09218859570848445</v>
+        <v>0.09074814890053938</v>
       </c>
       <c r="W65">
-        <v>0.2140619291319394</v>
+        <v>0.2144015864892528</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3841191487853519</v>
+        <v>0.3781172870855808</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6776,22 +6776,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2114927281023444</v>
+        <v>0.2133927281023444</v>
       </c>
       <c r="C66">
-        <v>-4.559645831704449</v>
+        <v>-4.830617803490883</v>
       </c>
       <c r="D66">
-        <v>6.66595416829555</v>
+        <v>6.590382196509117</v>
       </c>
       <c r="E66">
-        <v>3.865599999999999</v>
+        <v>4.061</v>
       </c>
       <c r="F66">
-        <v>12.5056</v>
+        <v>12.701</v>
       </c>
       <c r="G66">
         <v>1.28</v>
@@ -6812,37 +6812,37 @@
         <v>1.115</v>
       </c>
       <c r="M66">
-        <v>2.94882048</v>
+        <v>2.9948958</v>
       </c>
       <c r="N66">
-        <v>-1.83382048</v>
+        <v>-1.8798958</v>
       </c>
       <c r="O66">
-        <v>-0.4401169152</v>
+        <v>-0.4511749919999999</v>
       </c>
       <c r="P66">
-        <v>-1.3937035648</v>
+        <v>-1.428720808</v>
       </c>
       <c r="Q66">
-        <v>-0.7087035648</v>
+        <v>-0.743720808</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2063214243033961</v>
+        <v>0.2109077507120646</v>
       </c>
       <c r="T66">
-        <v>2.209637826600202</v>
+        <v>2.272770335931637</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.09074814890053938</v>
+        <v>0.08935202353283879</v>
       </c>
       <c r="W66">
-        <v>0.2144015864892528</v>
+        <v>0.2147307928509566</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3781172870855808</v>
+        <v>0.372300098053495</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6858,22 +6858,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2133927281023444</v>
+        <v>0.2152927281023444</v>
       </c>
       <c r="C67">
-        <v>-4.830617803490883</v>
+        <v>-5.099895463692364</v>
       </c>
       <c r="D67">
-        <v>6.590382196509117</v>
+        <v>6.516504536307636</v>
       </c>
       <c r="E67">
-        <v>4.061</v>
+        <v>4.256399999999999</v>
       </c>
       <c r="F67">
-        <v>12.701</v>
+        <v>12.8964</v>
       </c>
       <c r="G67">
         <v>1.28</v>
@@ -6894,37 +6894,37 @@
         <v>1.115</v>
       </c>
       <c r="M67">
-        <v>2.9948958</v>
+        <v>3.04097112</v>
       </c>
       <c r="N67">
-        <v>-1.8798958</v>
+        <v>-1.92597112</v>
       </c>
       <c r="O67">
-        <v>-0.4511749919999999</v>
+        <v>-0.4622330687999999</v>
       </c>
       <c r="P67">
-        <v>-1.428720808</v>
+        <v>-1.4637380512</v>
       </c>
       <c r="Q67">
-        <v>-0.743720808</v>
+        <v>-0.7787380511999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2109077507120646</v>
+        <v>0.2157638610271253</v>
       </c>
       <c r="T67">
-        <v>2.272770335931637</v>
+        <v>2.339616522282567</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.08935202353283879</v>
+        <v>0.08799820499446244</v>
       </c>
       <c r="W67">
-        <v>0.2147307928509566</v>
+        <v>0.2150500232623058</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.372300098053495</v>
+        <v>0.3666591874769268</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6940,22 +6940,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2152927281023444</v>
+        <v>0.2171927281023444</v>
       </c>
       <c r="C68">
-        <v>-5.099895463692364</v>
+        <v>-5.367535159950607</v>
       </c>
       <c r="D68">
-        <v>6.516504536307636</v>
+        <v>6.444264840049394</v>
       </c>
       <c r="E68">
-        <v>4.256399999999999</v>
+        <v>4.4518</v>
       </c>
       <c r="F68">
-        <v>12.8964</v>
+        <v>13.0918</v>
       </c>
       <c r="G68">
         <v>1.28</v>
@@ -6976,37 +6976,37 @@
         <v>1.115</v>
       </c>
       <c r="M68">
-        <v>3.04097112</v>
+        <v>3.08704644</v>
       </c>
       <c r="N68">
-        <v>-1.92597112</v>
+        <v>-1.97204644</v>
       </c>
       <c r="O68">
-        <v>-0.4622330687999999</v>
+        <v>-0.4732911456</v>
       </c>
       <c r="P68">
-        <v>-1.4637380512</v>
+        <v>-1.4987552944</v>
       </c>
       <c r="Q68">
-        <v>-0.7787380511999999</v>
+        <v>-0.8137552944000002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2157638610271253</v>
+        <v>0.2209142810582503</v>
       </c>
       <c r="T68">
-        <v>2.339616522282567</v>
+        <v>2.410513992654766</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.08799820499446244</v>
+        <v>0.08668479894976897</v>
       </c>
       <c r="W68">
-        <v>0.2150500232623058</v>
+        <v>0.2153597244076445</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3666591874769268</v>
+        <v>0.3611866622907041</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7022,22 +7022,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2171927281023444</v>
+        <v>0.2190927281023444</v>
       </c>
       <c r="C69">
-        <v>-5.367535159950607</v>
+        <v>-5.633590768701036</v>
       </c>
       <c r="D69">
-        <v>6.444264840049394</v>
+        <v>6.373609231298964</v>
       </c>
       <c r="E69">
-        <v>4.4518</v>
+        <v>4.6472</v>
       </c>
       <c r="F69">
-        <v>13.0918</v>
+        <v>13.2872</v>
       </c>
       <c r="G69">
         <v>1.28</v>
@@ -7058,37 +7058,37 @@
         <v>1.115</v>
       </c>
       <c r="M69">
-        <v>3.08704644</v>
+        <v>3.13312176</v>
       </c>
       <c r="N69">
-        <v>-1.97204644</v>
+        <v>-2.01812176</v>
       </c>
       <c r="O69">
-        <v>-0.4732911456</v>
+        <v>-0.4843492224</v>
       </c>
       <c r="P69">
-        <v>-1.4987552944</v>
+        <v>-1.5337725376</v>
       </c>
       <c r="Q69">
-        <v>-0.8137552944000002</v>
+        <v>-0.8487725375999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2209142810582503</v>
+        <v>0.2263866023413206</v>
       </c>
       <c r="T69">
-        <v>2.410513992654766</v>
+        <v>2.485842554925227</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.08668479894976897</v>
+        <v>0.0854100224946253</v>
       </c>
       <c r="W69">
-        <v>0.2153597244076445</v>
+        <v>0.2156603166957674</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3611866622907041</v>
+        <v>0.3558750937276054</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7104,22 +7104,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2190927281023444</v>
+        <v>0.2209927281023444</v>
       </c>
       <c r="C70">
-        <v>-5.633590768701036</v>
+        <v>-5.898113829176432</v>
       </c>
       <c r="D70">
-        <v>6.373609231298964</v>
+        <v>6.304486170823568</v>
       </c>
       <c r="E70">
-        <v>4.6472</v>
+        <v>4.842599999999999</v>
       </c>
       <c r="F70">
-        <v>13.2872</v>
+        <v>13.4826</v>
       </c>
       <c r="G70">
         <v>1.28</v>
@@ -7140,37 +7140,37 @@
         <v>1.115</v>
       </c>
       <c r="M70">
-        <v>3.13312176</v>
+        <v>3.17919708</v>
       </c>
       <c r="N70">
-        <v>-2.01812176</v>
+        <v>-2.06419708</v>
       </c>
       <c r="O70">
-        <v>-0.4843492224</v>
+        <v>-0.4954072992</v>
       </c>
       <c r="P70">
-        <v>-1.5337725376</v>
+        <v>-1.5687897808</v>
       </c>
       <c r="Q70">
-        <v>-0.8487725375999999</v>
+        <v>-0.8837897807999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2263866023413206</v>
+        <v>0.2322119766103955</v>
       </c>
       <c r="T70">
-        <v>2.485842554925227</v>
+        <v>2.566031024438944</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0854100224946253</v>
+        <v>0.08417219608165973</v>
       </c>
       <c r="W70">
-        <v>0.2156603166957674</v>
+        <v>0.2159521961639446</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3558750937276054</v>
+        <v>0.3507174836735821</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7186,22 +7186,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2209927281023444</v>
+        <v>0.2228927281023444</v>
       </c>
       <c r="C71">
-        <v>-5.898113829176432</v>
+        <v>-6.161153668784314</v>
       </c>
       <c r="D71">
-        <v>6.304486170823568</v>
+        <v>6.236846331215687</v>
       </c>
       <c r="E71">
-        <v>4.842599999999999</v>
+        <v>5.038</v>
       </c>
       <c r="F71">
-        <v>13.4826</v>
+        <v>13.678</v>
       </c>
       <c r="G71">
         <v>1.28</v>
@@ -7222,37 +7222,37 @@
         <v>1.115</v>
       </c>
       <c r="M71">
-        <v>3.17919708</v>
+        <v>3.2252724</v>
       </c>
       <c r="N71">
-        <v>-2.06419708</v>
+        <v>-2.1102724</v>
       </c>
       <c r="O71">
-        <v>-0.4954072992</v>
+        <v>-0.506465376</v>
       </c>
       <c r="P71">
-        <v>-1.5687897808</v>
+        <v>-1.603807024</v>
       </c>
       <c r="Q71">
-        <v>-0.8837897807999999</v>
+        <v>-0.9188070239999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2322119766103955</v>
+        <v>0.2384257091640753</v>
       </c>
       <c r="T71">
-        <v>2.566031024438944</v>
+        <v>2.651565391920243</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.08417219608165973</v>
+        <v>0.08296973613763602</v>
       </c>
       <c r="W71">
-        <v>0.2159521961639446</v>
+        <v>0.2162357362187454</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3507174836735821</v>
+        <v>0.3457072339068167</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7268,22 +7268,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2228927281023444</v>
+        <v>0.2247927281023444</v>
       </c>
       <c r="C72">
-        <v>-6.161153668784314</v>
+        <v>-6.422757520499085</v>
       </c>
       <c r="D72">
-        <v>6.236846331215687</v>
+        <v>6.170642479500915</v>
       </c>
       <c r="E72">
-        <v>5.038</v>
+        <v>5.2334</v>
       </c>
       <c r="F72">
-        <v>13.678</v>
+        <v>13.8734</v>
       </c>
       <c r="G72">
         <v>1.28</v>
@@ -7304,37 +7304,37 @@
         <v>1.115</v>
       </c>
       <c r="M72">
-        <v>3.2252724</v>
+        <v>3.27134772</v>
       </c>
       <c r="N72">
-        <v>-2.1102724</v>
+        <v>-2.15634772</v>
       </c>
       <c r="O72">
-        <v>-0.506465376</v>
+        <v>-0.5175234527999999</v>
       </c>
       <c r="P72">
-        <v>-1.603807024</v>
+        <v>-1.6388242672</v>
       </c>
       <c r="Q72">
-        <v>-0.9188070239999999</v>
+        <v>-0.9538242671999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2384257091640753</v>
+        <v>0.2450679749973193</v>
       </c>
       <c r="T72">
-        <v>2.651565391920243</v>
+        <v>2.742998681296803</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.08296973613763602</v>
+        <v>0.08180114830471157</v>
       </c>
       <c r="W72">
-        <v>0.2162357362187454</v>
+        <v>0.216511289229749</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3457072339068167</v>
+        <v>0.3408381179362981</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7350,22 +7350,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2247927281023444</v>
+        <v>0.2266927281023444</v>
       </c>
       <c r="C73">
-        <v>-6.42275752049908</v>
+        <v>-6.682970632856028</v>
       </c>
       <c r="D73">
-        <v>6.170642479500918</v>
+        <v>6.105829367143971</v>
       </c>
       <c r="E73">
-        <v>5.233399999999998</v>
+        <v>5.428799999999999</v>
       </c>
       <c r="F73">
-        <v>13.8734</v>
+        <v>14.0688</v>
       </c>
       <c r="G73">
         <v>1.28</v>
@@ -7386,37 +7386,37 @@
         <v>1.115</v>
       </c>
       <c r="M73">
-        <v>3.27134772</v>
+        <v>3.31742304</v>
       </c>
       <c r="N73">
-        <v>-2.156347719999999</v>
+        <v>-2.20242304</v>
       </c>
       <c r="O73">
-        <v>-0.5175234527999999</v>
+        <v>-0.5285815295999999</v>
       </c>
       <c r="P73">
-        <v>-1.6388242672</v>
+        <v>-1.6738415104</v>
       </c>
       <c r="Q73">
-        <v>-0.9538242671999995</v>
+        <v>-0.9888415103999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2450679749973192</v>
+        <v>0.2521846883900806</v>
       </c>
       <c r="T73">
-        <v>2.742998681296802</v>
+        <v>2.840962919914545</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08180114830471158</v>
+        <v>0.0806650212449239</v>
       </c>
       <c r="W73">
-        <v>0.216511289229749</v>
+        <v>0.216779187990447</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3408381179362983</v>
+        <v>0.3361042551871829</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7432,22 +7432,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2266927281023444</v>
+        <v>0.2285927281023444</v>
       </c>
       <c r="C74">
-        <v>-6.682970632856028</v>
+        <v>-6.941836373085465</v>
       </c>
       <c r="D74">
-        <v>6.105829367143971</v>
+        <v>6.042363626914534</v>
       </c>
       <c r="E74">
-        <v>5.428799999999999</v>
+        <v>5.624199999999998</v>
       </c>
       <c r="F74">
-        <v>14.0688</v>
+        <v>14.2642</v>
       </c>
       <c r="G74">
         <v>1.28</v>
@@ -7468,37 +7468,37 @@
         <v>1.115</v>
       </c>
       <c r="M74">
-        <v>3.31742304</v>
+        <v>3.36349836</v>
       </c>
       <c r="N74">
-        <v>-2.20242304</v>
+        <v>-2.24849836</v>
       </c>
       <c r="O74">
-        <v>-0.5285815295999999</v>
+        <v>-0.5396396063999999</v>
       </c>
       <c r="P74">
-        <v>-1.6738415104</v>
+        <v>-1.7088587536</v>
       </c>
       <c r="Q74">
-        <v>-0.9888415103999999</v>
+        <v>-1.0238587536</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2521846883900806</v>
+        <v>0.2598285657378614</v>
       </c>
       <c r="T74">
-        <v>2.840962919914545</v>
+        <v>2.946183768800269</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.0806650212449239</v>
+        <v>0.07956002095389755</v>
       </c>
       <c r="W74">
-        <v>0.216779187990447</v>
+        <v>0.2170397470590709</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3361042551871829</v>
+        <v>0.3315000873079065</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7514,22 +7514,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2285927281023444</v>
+        <v>0.2304927281023444</v>
       </c>
       <c r="C75">
-        <v>-6.941836373085465</v>
+        <v>-7.199396323881015</v>
       </c>
       <c r="D75">
-        <v>6.042363626914534</v>
+        <v>5.980203676118984</v>
       </c>
       <c r="E75">
-        <v>5.624199999999998</v>
+        <v>5.819599999999999</v>
       </c>
       <c r="F75">
-        <v>14.2642</v>
+        <v>14.4596</v>
       </c>
       <c r="G75">
         <v>1.28</v>
@@ -7550,37 +7550,37 @@
         <v>1.115</v>
       </c>
       <c r="M75">
-        <v>3.36349836</v>
+        <v>3.40957368</v>
       </c>
       <c r="N75">
-        <v>-2.24849836</v>
+        <v>-2.29457368</v>
       </c>
       <c r="O75">
-        <v>-0.5396396063999999</v>
+        <v>-0.5506976832</v>
       </c>
       <c r="P75">
-        <v>-1.7088587536</v>
+        <v>-1.7438759968</v>
       </c>
       <c r="Q75">
-        <v>-1.0238587536</v>
+        <v>-1.0588759968</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2598285657378614</v>
+        <v>0.268060433650856</v>
       </c>
       <c r="T75">
-        <v>2.946183768800269</v>
+        <v>3.05949852913874</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07956002095389755</v>
+        <v>0.07848488553560164</v>
       </c>
       <c r="W75">
-        <v>0.2170397470590709</v>
+        <v>0.2172932639907051</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3315000873079065</v>
+        <v>0.3270203563983402</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7596,22 +7596,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2304927281023444</v>
+        <v>0.2323927281023444</v>
       </c>
       <c r="C76">
-        <v>-7.199396323881015</v>
+        <v>-7.455690374255765</v>
       </c>
       <c r="D76">
-        <v>5.980203676118984</v>
+        <v>5.919309625744234</v>
       </c>
       <c r="E76">
-        <v>5.819599999999999</v>
+        <v>6.014999999999999</v>
       </c>
       <c r="F76">
-        <v>14.4596</v>
+        <v>14.655</v>
       </c>
       <c r="G76">
         <v>1.28</v>
@@ -7632,37 +7632,37 @@
         <v>1.115</v>
       </c>
       <c r="M76">
-        <v>3.40957368</v>
+        <v>3.455649</v>
       </c>
       <c r="N76">
-        <v>-2.29457368</v>
+        <v>-2.340649</v>
       </c>
       <c r="O76">
-        <v>-0.5506976832</v>
+        <v>-0.5617557599999999</v>
       </c>
       <c r="P76">
-        <v>-1.7438759968</v>
+        <v>-1.77889324</v>
       </c>
       <c r="Q76">
-        <v>-1.0588759968</v>
+        <v>-1.09389324</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.268060433650856</v>
+        <v>0.2769508509968903</v>
       </c>
       <c r="T76">
-        <v>3.05949852913874</v>
+        <v>3.181878470304291</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.07848488553560164</v>
+        <v>0.07743842039512694</v>
       </c>
       <c r="W76">
-        <v>0.2172932639907051</v>
+        <v>0.2175400204708291</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3270203563983402</v>
+        <v>0.3226600849796956</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7678,22 +7678,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2323927281023444</v>
+        <v>0.2342927281023444</v>
       </c>
       <c r="C77">
-        <v>-7.455690374255765</v>
+        <v>-7.710756804903464</v>
       </c>
       <c r="D77">
-        <v>5.919309625744234</v>
+        <v>5.859643195096535</v>
       </c>
       <c r="E77">
-        <v>6.014999999999999</v>
+        <v>6.210399999999998</v>
       </c>
       <c r="F77">
-        <v>14.655</v>
+        <v>14.8504</v>
       </c>
       <c r="G77">
         <v>1.28</v>
@@ -7714,37 +7714,37 @@
         <v>1.115</v>
       </c>
       <c r="M77">
-        <v>3.455649</v>
+        <v>3.50172432</v>
       </c>
       <c r="N77">
-        <v>-2.340649</v>
+        <v>-2.386724319999999</v>
       </c>
       <c r="O77">
-        <v>-0.5617557599999999</v>
+        <v>-0.5728138367999999</v>
       </c>
       <c r="P77">
-        <v>-1.77889324</v>
+        <v>-1.813910483199999</v>
       </c>
       <c r="Q77">
-        <v>-1.09389324</v>
+        <v>-1.128910483199999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2769508509968903</v>
+        <v>0.2865821364550941</v>
       </c>
       <c r="T77">
-        <v>3.181878470304291</v>
+        <v>3.314456739900303</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.07743842039512694</v>
+        <v>0.07641949381098055</v>
       </c>
       <c r="W77">
-        <v>0.2175400204708291</v>
+        <v>0.2177802833593708</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3226600849796956</v>
+        <v>0.3184145575457523</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7760,22 +7760,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2342927281023444</v>
+        <v>0.2361927281023444</v>
       </c>
       <c r="C78">
-        <v>-7.710756804903464</v>
+        <v>-7.964632368448615</v>
       </c>
       <c r="D78">
-        <v>5.859643195096535</v>
+        <v>5.801167631551385</v>
       </c>
       <c r="E78">
-        <v>6.210399999999998</v>
+        <v>6.405799999999999</v>
       </c>
       <c r="F78">
-        <v>14.8504</v>
+        <v>15.0458</v>
       </c>
       <c r="G78">
         <v>1.28</v>
@@ -7796,37 +7796,37 @@
         <v>1.115</v>
       </c>
       <c r="M78">
-        <v>3.50172432</v>
+        <v>3.54779964</v>
       </c>
       <c r="N78">
-        <v>-2.386724319999999</v>
+        <v>-2.43279964</v>
       </c>
       <c r="O78">
-        <v>-0.5728138367999999</v>
+        <v>-0.5838719135999999</v>
       </c>
       <c r="P78">
-        <v>-1.813910483199999</v>
+        <v>-1.8489277264</v>
       </c>
       <c r="Q78">
-        <v>-1.128910483199999</v>
+        <v>-1.1639277264</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2865821364550941</v>
+        <v>0.2970509249966199</v>
       </c>
       <c r="T78">
-        <v>3.314456739900303</v>
+        <v>3.458563554678577</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07641949381098055</v>
+        <v>0.07542703285239637</v>
       </c>
       <c r="W78">
-        <v>0.2177802833593708</v>
+        <v>0.2180143056534049</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3184145575457523</v>
+        <v>0.3142793035516516</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7842,22 +7842,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2361927281023444</v>
+        <v>0.2380927281023444</v>
       </c>
       <c r="C79">
-        <v>-7.964632368448615</v>
+        <v>-8.217352364938971</v>
       </c>
       <c r="D79">
-        <v>5.801167631551385</v>
+        <v>5.743847635061027</v>
       </c>
       <c r="E79">
-        <v>6.405799999999999</v>
+        <v>6.601199999999999</v>
       </c>
       <c r="F79">
-        <v>15.0458</v>
+        <v>15.2412</v>
       </c>
       <c r="G79">
         <v>1.28</v>
@@ -7878,37 +7878,37 @@
         <v>1.115</v>
       </c>
       <c r="M79">
-        <v>3.54779964</v>
+        <v>3.59387496</v>
       </c>
       <c r="N79">
-        <v>-2.43279964</v>
+        <v>-2.47887496</v>
       </c>
       <c r="O79">
-        <v>-0.5838719135999999</v>
+        <v>-0.5949299903999999</v>
       </c>
       <c r="P79">
-        <v>-1.8489277264</v>
+        <v>-1.8839449696</v>
       </c>
       <c r="Q79">
-        <v>-1.1639277264</v>
+        <v>-1.1989449696</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2970509249966199</v>
+        <v>0.3084714215873753</v>
       </c>
       <c r="T79">
-        <v>3.458563554678577</v>
+        <v>3.615770988982148</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07542703285239637</v>
+        <v>0.07446001961069899</v>
       </c>
       <c r="W79">
-        <v>0.2180143056534049</v>
+        <v>0.2182423273757972</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3142793035516516</v>
+        <v>0.3102500817112458</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7924,22 +7924,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2380927281023444</v>
+        <v>0.2399927281023444</v>
       </c>
       <c r="C80">
-        <v>-8.217352364938971</v>
+        <v>-8.468950712906278</v>
       </c>
       <c r="D80">
-        <v>5.743847635061027</v>
+        <v>5.687649287093722</v>
       </c>
       <c r="E80">
-        <v>6.601199999999999</v>
+        <v>6.7966</v>
       </c>
       <c r="F80">
-        <v>15.2412</v>
+        <v>15.4366</v>
       </c>
       <c r="G80">
         <v>1.28</v>
@@ -7960,37 +7960,37 @@
         <v>1.115</v>
       </c>
       <c r="M80">
-        <v>3.59387496</v>
+        <v>3.63995028</v>
       </c>
       <c r="N80">
-        <v>-2.47887496</v>
+        <v>-2.52495028</v>
       </c>
       <c r="O80">
-        <v>-0.5949299903999999</v>
+        <v>-0.6059880672</v>
       </c>
       <c r="P80">
-        <v>-1.8839449696</v>
+        <v>-1.9189622128</v>
       </c>
       <c r="Q80">
-        <v>-1.1989449696</v>
+        <v>-1.2339622128</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3084714215873753</v>
+        <v>0.3209795845201076</v>
       </c>
       <c r="T80">
-        <v>3.615770988982148</v>
+        <v>3.787950559886061</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07446001961069899</v>
+        <v>0.07351748771689266</v>
       </c>
       <c r="W80">
-        <v>0.2182423273757972</v>
+        <v>0.2184645763963567</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3102500817112458</v>
+        <v>0.3063228654870528</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8006,22 +8006,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2399927281023444</v>
+        <v>0.2418927281023444</v>
       </c>
       <c r="C81">
-        <v>-8.468950712906278</v>
+        <v>-8.719460016295837</v>
       </c>
       <c r="D81">
-        <v>5.687649287093722</v>
+        <v>5.632539983704163</v>
       </c>
       <c r="E81">
-        <v>6.7966</v>
+        <v>6.991999999999999</v>
       </c>
       <c r="F81">
-        <v>15.4366</v>
+        <v>15.632</v>
       </c>
       <c r="G81">
         <v>1.28</v>
@@ -8042,37 +8042,37 @@
         <v>1.115</v>
       </c>
       <c r="M81">
-        <v>3.63995028</v>
+        <v>3.6860256</v>
       </c>
       <c r="N81">
-        <v>-2.52495028</v>
+        <v>-2.5710256</v>
       </c>
       <c r="O81">
-        <v>-0.6059880672</v>
+        <v>-0.617046144</v>
       </c>
       <c r="P81">
-        <v>-1.9189622128</v>
+        <v>-1.953979456</v>
       </c>
       <c r="Q81">
-        <v>-1.2339622128</v>
+        <v>-1.268979456</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3209795845201076</v>
+        <v>0.334738563746113</v>
       </c>
       <c r="T81">
-        <v>3.787950559886061</v>
+        <v>3.977348087880364</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07351748771689266</v>
+        <v>0.0725985191204315</v>
       </c>
       <c r="W81">
-        <v>0.2184645763963567</v>
+        <v>0.2186812691914023</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3063228654870528</v>
+        <v>0.3024938296684646</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8088,22 +8088,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2418927281023444</v>
+        <v>0.2437927281023444</v>
       </c>
       <c r="C82">
-        <v>-8.719460016295837</v>
+        <v>-8.968911627542415</v>
       </c>
       <c r="D82">
-        <v>5.632539983704163</v>
+        <v>5.578488372457585</v>
       </c>
       <c r="E82">
-        <v>6.991999999999999</v>
+        <v>7.1874</v>
       </c>
       <c r="F82">
-        <v>15.632</v>
+        <v>15.8274</v>
       </c>
       <c r="G82">
         <v>1.28</v>
@@ -8124,37 +8124,37 @@
         <v>1.115</v>
       </c>
       <c r="M82">
-        <v>3.6860256</v>
+        <v>3.73210092</v>
       </c>
       <c r="N82">
-        <v>-2.5710256</v>
+        <v>-2.61710092</v>
       </c>
       <c r="O82">
-        <v>-0.617046144</v>
+        <v>-0.6281042207999999</v>
       </c>
       <c r="P82">
-        <v>-1.953979456</v>
+        <v>-1.9889966992</v>
       </c>
       <c r="Q82">
-        <v>-1.268979456</v>
+        <v>-1.3039966992</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.334738563746113</v>
+        <v>0.3499458565748558</v>
       </c>
       <c r="T82">
-        <v>3.977348087880364</v>
+        <v>4.186682197768804</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0725985191204315</v>
+        <v>0.07170224110659902</v>
       </c>
       <c r="W82">
-        <v>0.2186812691914023</v>
+        <v>0.2188926115470639</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3024938296684646</v>
+        <v>0.2987593379441627</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8170,22 +8170,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2437927281023444</v>
+        <v>0.2456927281023444</v>
       </c>
       <c r="C83">
-        <v>-8.968911627542415</v>
+        <v>-9.217335707048917</v>
       </c>
       <c r="D83">
-        <v>5.578488372457585</v>
+        <v>5.525464292951082</v>
       </c>
       <c r="E83">
-        <v>7.1874</v>
+        <v>7.3828</v>
       </c>
       <c r="F83">
-        <v>15.8274</v>
+        <v>16.0228</v>
       </c>
       <c r="G83">
         <v>1.28</v>
@@ -8206,37 +8206,37 @@
         <v>1.115</v>
       </c>
       <c r="M83">
-        <v>3.73210092</v>
+        <v>3.77817624</v>
       </c>
       <c r="N83">
-        <v>-2.61710092</v>
+        <v>-2.66317624</v>
       </c>
       <c r="O83">
-        <v>-0.6281042207999999</v>
+        <v>-0.6391622976</v>
       </c>
       <c r="P83">
-        <v>-1.9889966992</v>
+        <v>-2.0240139424</v>
       </c>
       <c r="Q83">
-        <v>-1.3039966992</v>
+        <v>-1.3390139424</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3499458565748558</v>
+        <v>0.3668428486067923</v>
       </c>
       <c r="T83">
-        <v>4.186682197768804</v>
+        <v>4.419275653200406</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07170224110659902</v>
+        <v>0.0708278235321283</v>
       </c>
       <c r="W83">
-        <v>0.2188926115470639</v>
+        <v>0.2190987992111242</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2987593379441627</v>
+        <v>0.2951159313838679</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8252,22 +8252,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2456927281023444</v>
+        <v>0.2475927281023444</v>
       </c>
       <c r="C84">
-        <v>-9.217335707048917</v>
+        <v>-9.464761279304829</v>
       </c>
       <c r="D84">
-        <v>5.525464292951082</v>
+        <v>5.47343872069517</v>
       </c>
       <c r="E84">
-        <v>7.3828</v>
+        <v>7.578199999999999</v>
       </c>
       <c r="F84">
-        <v>16.0228</v>
+        <v>16.2182</v>
       </c>
       <c r="G84">
         <v>1.28</v>
@@ -8288,37 +8288,37 @@
         <v>1.115</v>
       </c>
       <c r="M84">
-        <v>3.77817624</v>
+        <v>3.82425156</v>
       </c>
       <c r="N84">
-        <v>-2.66317624</v>
+        <v>-2.70925156</v>
       </c>
       <c r="O84">
-        <v>-0.6391622976</v>
+        <v>-0.6502203743999999</v>
       </c>
       <c r="P84">
-        <v>-2.0240139424</v>
+        <v>-2.0590311856</v>
       </c>
       <c r="Q84">
-        <v>-1.3390139424</v>
+        <v>-1.3740311856</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3668428486067923</v>
+        <v>0.3857277220542507</v>
       </c>
       <c r="T84">
-        <v>4.419275653200406</v>
+        <v>4.679233044565136</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0708278235321283</v>
+        <v>0.06997447626065688</v>
       </c>
       <c r="W84">
-        <v>0.2190987992111242</v>
+        <v>0.2193000184977371</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2951159313838679</v>
+        <v>0.2915603177527371</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8334,22 +8334,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2475927281023444</v>
+        <v>0.2494927281023444</v>
       </c>
       <c r="C85">
-        <v>-9.464761279304829</v>
+        <v>-9.711216285864005</v>
       </c>
       <c r="D85">
-        <v>5.47343872069517</v>
+        <v>5.422383714135997</v>
       </c>
       <c r="E85">
-        <v>7.578199999999999</v>
+        <v>7.773600000000002</v>
       </c>
       <c r="F85">
-        <v>16.2182</v>
+        <v>16.4136</v>
       </c>
       <c r="G85">
         <v>1.28</v>
@@ -8370,37 +8370,37 @@
         <v>1.115</v>
       </c>
       <c r="M85">
-        <v>3.82425156</v>
+        <v>3.870326880000001</v>
       </c>
       <c r="N85">
-        <v>-2.70925156</v>
+        <v>-2.755326880000001</v>
       </c>
       <c r="O85">
-        <v>-0.6502203743999999</v>
+        <v>-0.6612784512000001</v>
       </c>
       <c r="P85">
-        <v>-2.0590311856</v>
+        <v>-2.094048428800001</v>
       </c>
       <c r="Q85">
-        <v>-1.3740311856</v>
+        <v>-1.409048428800001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3857277220542507</v>
+        <v>0.4069732046826414</v>
       </c>
       <c r="T85">
-        <v>4.679233044565136</v>
+        <v>4.971685109850457</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06997447626065688</v>
+        <v>0.06914144678136333</v>
       </c>
       <c r="W85">
-        <v>0.2193000184977371</v>
+        <v>0.2194964468489545</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2915603177527371</v>
+        <v>0.2880893615890139</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8416,22 +8416,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2494927281023444</v>
+        <v>0.2513927281023444</v>
       </c>
       <c r="C86">
-        <v>-9.711216285864005</v>
+        <v>-9.956727635384738</v>
       </c>
       <c r="D86">
-        <v>5.422383714135995</v>
+        <v>5.37227236461526</v>
       </c>
       <c r="E86">
-        <v>7.773599999999998</v>
+        <v>7.968999999999998</v>
       </c>
       <c r="F86">
-        <v>16.4136</v>
+        <v>16.609</v>
       </c>
       <c r="G86">
         <v>1.28</v>
@@ -8452,37 +8452,37 @@
         <v>1.115</v>
       </c>
       <c r="M86">
-        <v>3.87032688</v>
+        <v>3.9164022</v>
       </c>
       <c r="N86">
-        <v>-2.75532688</v>
+        <v>-2.8014022</v>
       </c>
       <c r="O86">
-        <v>-0.6612784512</v>
+        <v>-0.6723365279999999</v>
       </c>
       <c r="P86">
-        <v>-2.0940484288</v>
+        <v>-2.129065672</v>
       </c>
       <c r="Q86">
-        <v>-1.4090484288</v>
+        <v>-1.444065672</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4069732046826411</v>
+        <v>0.4310514183281505</v>
       </c>
       <c r="T86">
-        <v>4.971685109850454</v>
+        <v>5.303130783840484</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06914144678136334</v>
+        <v>0.06832801799570025</v>
       </c>
       <c r="W86">
-        <v>0.2194964468489545</v>
+        <v>0.2196882533566139</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.288089361589014</v>
+        <v>0.2847000749820844</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8498,22 +8498,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2513927281023444</v>
+        <v>0.2532927281023444</v>
       </c>
       <c r="C87">
-        <v>-9.956727635384738</v>
+        <v>-10.20132125092067</v>
       </c>
       <c r="D87">
-        <v>5.37227236461526</v>
+        <v>5.323078749079325</v>
       </c>
       <c r="E87">
-        <v>7.968999999999998</v>
+        <v>8.164399999999997</v>
       </c>
       <c r="F87">
-        <v>16.609</v>
+        <v>16.8044</v>
       </c>
       <c r="G87">
         <v>1.28</v>
@@ -8534,37 +8534,37 @@
         <v>1.115</v>
       </c>
       <c r="M87">
-        <v>3.9164022</v>
+        <v>3.96247752</v>
       </c>
       <c r="N87">
-        <v>-2.8014022</v>
+        <v>-2.84747752</v>
       </c>
       <c r="O87">
-        <v>-0.6723365279999999</v>
+        <v>-0.6833946047999999</v>
       </c>
       <c r="P87">
-        <v>-2.129065672</v>
+        <v>-2.1640829152</v>
       </c>
       <c r="Q87">
-        <v>-1.444065672</v>
+        <v>-1.4790829152</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4310514183281505</v>
+        <v>0.4585693767801613</v>
       </c>
       <c r="T87">
-        <v>5.303130783840484</v>
+        <v>5.68192583982909</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06832801799570025</v>
+        <v>0.06753350615854095</v>
       </c>
       <c r="W87">
-        <v>0.2196882533566139</v>
+        <v>0.2198755992478161</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2847000749820844</v>
+        <v>0.2813896089939206</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8580,22 +8580,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2532927281023444</v>
+        <v>0.2551927281023444</v>
       </c>
       <c r="C88">
-        <v>-10.20132125092067</v>
+        <v>-10.44502211463695</v>
       </c>
       <c r="D88">
-        <v>5.323078749079325</v>
+        <v>5.27477788536305</v>
       </c>
       <c r="E88">
-        <v>8.164399999999997</v>
+        <v>8.3598</v>
       </c>
       <c r="F88">
-        <v>16.8044</v>
+        <v>16.9998</v>
       </c>
       <c r="G88">
         <v>1.28</v>
@@ -8616,37 +8616,37 @@
         <v>1.115</v>
       </c>
       <c r="M88">
-        <v>3.96247752</v>
+        <v>4.00855284</v>
       </c>
       <c r="N88">
-        <v>-2.84747752</v>
+        <v>-2.89355284</v>
       </c>
       <c r="O88">
-        <v>-0.6833946047999999</v>
+        <v>-0.6944526816</v>
       </c>
       <c r="P88">
-        <v>-2.1640829152</v>
+        <v>-2.1991001584</v>
       </c>
       <c r="Q88">
-        <v>-1.4790829152</v>
+        <v>-1.5141001584</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4585693767801613</v>
+        <v>0.4903208673017121</v>
       </c>
       <c r="T88">
-        <v>5.68192583982909</v>
+        <v>6.118997058277481</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06753350615854095</v>
+        <v>0.06675725896131633</v>
       </c>
       <c r="W88">
-        <v>0.2198755992478161</v>
+        <v>0.2200586383369216</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2813896089939206</v>
+        <v>0.2781552456721514</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8662,22 +8662,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2551927281023444</v>
+        <v>0.2570927281023444</v>
       </c>
       <c r="C89">
-        <v>-10.44502211463695</v>
+        <v>-10.68785431011381</v>
       </c>
       <c r="D89">
-        <v>5.27477788536305</v>
+        <v>5.227345689886187</v>
       </c>
       <c r="E89">
-        <v>8.3598</v>
+        <v>8.555199999999999</v>
       </c>
       <c r="F89">
-        <v>16.9998</v>
+        <v>17.1952</v>
       </c>
       <c r="G89">
         <v>1.28</v>
@@ -8698,37 +8698,37 @@
         <v>1.115</v>
       </c>
       <c r="M89">
-        <v>4.00855284</v>
+        <v>4.05462816</v>
       </c>
       <c r="N89">
-        <v>-2.89355284</v>
+        <v>-2.93962816</v>
       </c>
       <c r="O89">
-        <v>-0.6944526816</v>
+        <v>-0.7055107583999999</v>
       </c>
       <c r="P89">
-        <v>-2.1991001584</v>
+        <v>-2.2341174016</v>
       </c>
       <c r="Q89">
-        <v>-1.5141001584</v>
+        <v>-1.5491174016</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4903208673017121</v>
+        <v>0.5273642729101883</v>
       </c>
       <c r="T89">
-        <v>6.118997058277481</v>
+        <v>6.628913479800606</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06675725896131633</v>
+        <v>0.06599865374584683</v>
       </c>
       <c r="W89">
-        <v>0.2200586383369216</v>
+        <v>0.2202375174467293</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2781552456721514</v>
+        <v>0.2749943906076951</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8744,22 +8744,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2570927281023444</v>
+        <v>0.2589927281023444</v>
       </c>
       <c r="C90">
-        <v>-10.68785431011381</v>
+        <v>-10.9298410623881</v>
       </c>
       <c r="D90">
-        <v>5.227345689886187</v>
+        <v>5.180758937611898</v>
       </c>
       <c r="E90">
-        <v>8.555199999999999</v>
+        <v>8.750599999999999</v>
       </c>
       <c r="F90">
-        <v>17.1952</v>
+        <v>17.3906</v>
       </c>
       <c r="G90">
         <v>1.28</v>
@@ -8780,37 +8780,37 @@
         <v>1.115</v>
       </c>
       <c r="M90">
-        <v>4.05462816</v>
+        <v>4.10070348</v>
       </c>
       <c r="N90">
-        <v>-2.93962816</v>
+        <v>-2.98570348</v>
       </c>
       <c r="O90">
-        <v>-0.7055107583999999</v>
+        <v>-0.7165688351999999</v>
       </c>
       <c r="P90">
-        <v>-2.2341174016</v>
+        <v>-2.2691346448</v>
       </c>
       <c r="Q90">
-        <v>-1.5491174016</v>
+        <v>-1.5841346448</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5273642729101883</v>
+        <v>0.5711428431747508</v>
       </c>
       <c r="T90">
-        <v>6.628913479800606</v>
+        <v>7.231541977964298</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06599865374584683</v>
+        <v>0.06525709583859013</v>
       </c>
       <c r="W90">
-        <v>0.2202375174467293</v>
+        <v>0.2204123768012605</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2749943906076951</v>
+        <v>0.2719045659941255</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8826,22 +8826,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2589927281023444</v>
+        <v>0.2608927281023444</v>
       </c>
       <c r="C91">
-        <v>-10.9298410623881</v>
+        <v>-11.17100477587254</v>
       </c>
       <c r="D91">
-        <v>5.180758937611898</v>
+        <v>5.134995224127457</v>
       </c>
       <c r="E91">
-        <v>8.750599999999999</v>
+        <v>8.945999999999998</v>
       </c>
       <c r="F91">
-        <v>17.3906</v>
+        <v>17.586</v>
       </c>
       <c r="G91">
         <v>1.28</v>
@@ -8862,37 +8862,37 @@
         <v>1.115</v>
       </c>
       <c r="M91">
-        <v>4.10070348</v>
+        <v>4.1467788</v>
       </c>
       <c r="N91">
-        <v>-2.98570348</v>
+        <v>-3.0317788</v>
       </c>
       <c r="O91">
-        <v>-0.7165688351999999</v>
+        <v>-0.7276269119999998</v>
       </c>
       <c r="P91">
-        <v>-2.2691346448</v>
+        <v>-2.304151888</v>
       </c>
       <c r="Q91">
-        <v>-1.5841346448</v>
+        <v>-1.619151888</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5711428431747508</v>
+        <v>0.6236771274922259</v>
       </c>
       <c r="T91">
-        <v>7.231541977964298</v>
+        <v>7.954696175760728</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06525709583859013</v>
+        <v>0.06453201699593913</v>
       </c>
       <c r="W91">
-        <v>0.2204123768012605</v>
+        <v>0.2205833503923576</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2719045659941255</v>
+        <v>0.2688834041497463</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8908,22 +8908,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2608927281023444</v>
+        <v>0.2627927281023444</v>
       </c>
       <c r="C92">
-        <v>-11.17100477587254</v>
+        <v>-11.41136707028289</v>
       </c>
       <c r="D92">
-        <v>5.134995224127457</v>
+        <v>5.090032929717109</v>
       </c>
       <c r="E92">
-        <v>8.945999999999998</v>
+        <v>9.141400000000001</v>
       </c>
       <c r="F92">
-        <v>17.586</v>
+        <v>17.7814</v>
       </c>
       <c r="G92">
         <v>1.28</v>
@@ -8944,37 +8944,37 @@
         <v>1.115</v>
       </c>
       <c r="M92">
-        <v>4.1467788</v>
+        <v>4.192854120000001</v>
       </c>
       <c r="N92">
-        <v>-3.0317788</v>
+        <v>-3.07785412</v>
       </c>
       <c r="O92">
-        <v>-0.7276269119999998</v>
+        <v>-0.7386849888000001</v>
       </c>
       <c r="P92">
-        <v>-2.304151888</v>
+        <v>-2.3391691312</v>
       </c>
       <c r="Q92">
-        <v>-1.619151888</v>
+        <v>-1.6541691312</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6236771274922259</v>
+        <v>0.6878856972135845</v>
       </c>
       <c r="T92">
-        <v>7.954696175760728</v>
+        <v>8.838551306400811</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06453201699593913</v>
+        <v>0.06382287395202769</v>
       </c>
       <c r="W92">
-        <v>0.2205833503923576</v>
+        <v>0.2207505663221119</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2688834041497463</v>
+        <v>0.2659286414667821</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8990,22 +8990,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2627927281023444</v>
+        <v>0.2646927281023445</v>
       </c>
       <c r="C93">
-        <v>-11.41136707028289</v>
+        <v>-11.65094881469398</v>
       </c>
       <c r="D93">
-        <v>5.090032929717109</v>
+        <v>5.045851185306025</v>
       </c>
       <c r="E93">
-        <v>9.141400000000001</v>
+        <v>9.3368</v>
       </c>
       <c r="F93">
-        <v>17.7814</v>
+        <v>17.9768</v>
       </c>
       <c r="G93">
         <v>1.28</v>
@@ -9026,37 +9026,37 @@
         <v>1.115</v>
       </c>
       <c r="M93">
-        <v>4.192854120000001</v>
+        <v>4.238929440000001</v>
       </c>
       <c r="N93">
-        <v>-3.07785412</v>
+        <v>-3.12392944</v>
       </c>
       <c r="O93">
-        <v>-0.7386849888000001</v>
+        <v>-0.7497430656</v>
       </c>
       <c r="P93">
-        <v>-2.3391691312</v>
+        <v>-2.3741863744</v>
       </c>
       <c r="Q93">
-        <v>-1.6541691312</v>
+        <v>-1.6891863744</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6878856972135845</v>
+        <v>0.7681464093652828</v>
       </c>
       <c r="T93">
-        <v>8.838551306400811</v>
+        <v>9.943370219700915</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06382287395202769</v>
+        <v>0.06312914706124478</v>
       </c>
       <c r="W93">
-        <v>0.2207505663221119</v>
+        <v>0.2209141471229585</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2659286414667821</v>
+        <v>0.2630381127551866</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9072,22 +9072,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2646927281023445</v>
+        <v>0.2665927281023444</v>
       </c>
       <c r="C94">
-        <v>-11.65094881469398</v>
+        <v>-11.88977015983736</v>
       </c>
       <c r="D94">
-        <v>5.045851185306025</v>
+        <v>5.002429840162642</v>
       </c>
       <c r="E94">
-        <v>9.3368</v>
+        <v>9.5322</v>
       </c>
       <c r="F94">
-        <v>17.9768</v>
+        <v>18.1722</v>
       </c>
       <c r="G94">
         <v>1.28</v>
@@ -9108,37 +9108,37 @@
         <v>1.115</v>
       </c>
       <c r="M94">
-        <v>4.238929440000001</v>
+        <v>4.285004760000001</v>
       </c>
       <c r="N94">
-        <v>-3.12392944</v>
+        <v>-3.17000476</v>
       </c>
       <c r="O94">
-        <v>-0.7497430656</v>
+        <v>-0.7608011424000001</v>
       </c>
       <c r="P94">
-        <v>-2.3741863744</v>
+        <v>-2.4092036176</v>
       </c>
       <c r="Q94">
-        <v>-1.6891863744</v>
+        <v>-1.7242036176</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7681464093652828</v>
+        <v>0.8713387535603231</v>
       </c>
       <c r="T94">
-        <v>9.943370219700915</v>
+        <v>11.36385167965819</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06312914706124478</v>
+        <v>0.06245033902832818</v>
       </c>
       <c r="W94">
-        <v>0.2209141471229585</v>
+        <v>0.2210742100571202</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2630381127551866</v>
+        <v>0.2602097459513674</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9154,22 +9154,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2665927281023444</v>
+        <v>0.2684927281023444</v>
       </c>
       <c r="C95">
-        <v>-11.88977015983736</v>
+        <v>-12.12785056874564</v>
       </c>
       <c r="D95">
-        <v>5.002429840162642</v>
+        <v>4.959749431254357</v>
       </c>
       <c r="E95">
-        <v>9.5322</v>
+        <v>9.727599999999999</v>
       </c>
       <c r="F95">
-        <v>18.1722</v>
+        <v>18.3676</v>
       </c>
       <c r="G95">
         <v>1.28</v>
@@ -9190,37 +9190,37 @@
         <v>1.115</v>
       </c>
       <c r="M95">
-        <v>4.285004760000001</v>
+        <v>4.33108008</v>
       </c>
       <c r="N95">
-        <v>-3.17000476</v>
+        <v>-3.21608008</v>
       </c>
       <c r="O95">
-        <v>-0.7608011424000001</v>
+        <v>-0.7718592192</v>
       </c>
       <c r="P95">
-        <v>-2.4092036176</v>
+        <v>-2.4442208608</v>
       </c>
       <c r="Q95">
-        <v>-1.7242036176</v>
+        <v>-1.7592208608</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8713387535603231</v>
+        <v>1.008928545820377</v>
       </c>
       <c r="T95">
-        <v>11.36385167965819</v>
+        <v>13.25782695960122</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06245033902832818</v>
+        <v>0.06178597371951617</v>
       </c>
       <c r="W95">
-        <v>0.2210742100571202</v>
+        <v>0.2212308673969381</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2602097459513674</v>
+        <v>0.2574415571646508</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9236,22 +9236,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2684927281023444</v>
+        <v>0.2703927281023444</v>
       </c>
       <c r="C96">
-        <v>-12.12785056874564</v>
+        <v>-12.36520884584128</v>
       </c>
       <c r="D96">
-        <v>4.959749431254357</v>
+        <v>4.917791154158721</v>
       </c>
       <c r="E96">
-        <v>9.727599999999999</v>
+        <v>9.922999999999998</v>
       </c>
       <c r="F96">
-        <v>18.3676</v>
+        <v>18.563</v>
       </c>
       <c r="G96">
         <v>1.28</v>
@@ -9272,37 +9272,37 @@
         <v>1.115</v>
       </c>
       <c r="M96">
-        <v>4.33108008</v>
+        <v>4.377155399999999</v>
       </c>
       <c r="N96">
-        <v>-3.21608008</v>
+        <v>-3.262155399999999</v>
       </c>
       <c r="O96">
-        <v>-0.7718592192</v>
+        <v>-0.7829172959999998</v>
       </c>
       <c r="P96">
-        <v>-2.4442208608</v>
+        <v>-2.479238103999999</v>
       </c>
       <c r="Q96">
-        <v>-1.7592208608</v>
+        <v>-1.794238103999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.008928545820377</v>
+        <v>1.201554254984453</v>
       </c>
       <c r="T96">
-        <v>13.25782695960122</v>
+        <v>15.90939235152147</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06178597371951617</v>
+        <v>0.06113559504878444</v>
       </c>
       <c r="W96">
-        <v>0.2212308673969381</v>
+        <v>0.2213842266874966</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2574415571646508</v>
+        <v>0.2547316460366018</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9318,22 +9318,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2703927281023444</v>
+        <v>0.2722927281023444</v>
       </c>
       <c r="C97">
-        <v>-12.36520884584128</v>
+        <v>-12.6018631645613</v>
       </c>
       <c r="D97">
-        <v>4.917791154158721</v>
+        <v>4.876536835438698</v>
       </c>
       <c r="E97">
-        <v>9.922999999999998</v>
+        <v>10.1184</v>
       </c>
       <c r="F97">
-        <v>18.563</v>
+        <v>18.7584</v>
       </c>
       <c r="G97">
         <v>1.28</v>
@@ -9354,37 +9354,37 @@
         <v>1.115</v>
       </c>
       <c r="M97">
-        <v>4.377155399999999</v>
+        <v>4.42323072</v>
       </c>
       <c r="N97">
-        <v>-3.262155399999999</v>
+        <v>-3.30823072</v>
       </c>
       <c r="O97">
-        <v>-0.7829172959999998</v>
+        <v>-0.7939753728</v>
       </c>
       <c r="P97">
-        <v>-2.479238103999999</v>
+        <v>-2.5142553472</v>
       </c>
       <c r="Q97">
-        <v>-1.794238103999999</v>
+        <v>-1.8292553472</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.201554254984453</v>
+        <v>1.490492818730567</v>
       </c>
       <c r="T97">
-        <v>15.90939235152147</v>
+        <v>19.88674043940185</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06113559504878444</v>
+        <v>0.06049876593369292</v>
       </c>
       <c r="W97">
-        <v>0.2213842266874966</v>
+        <v>0.2215343909928352</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2547316460366018</v>
+        <v>0.2520781913903872</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9400,22 +9400,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2722927281023443</v>
+        <v>0.2741927281023444</v>
       </c>
       <c r="C98">
-        <v>-12.6018631645613</v>
+        <v>-12.83783109360316</v>
       </c>
       <c r="D98">
-        <v>4.876536835438699</v>
+        <v>4.835968906396833</v>
       </c>
       <c r="E98">
-        <v>10.1184</v>
+        <v>10.3138</v>
       </c>
       <c r="F98">
-        <v>18.7584</v>
+        <v>18.9538</v>
       </c>
       <c r="G98">
         <v>1.28</v>
@@ -9436,37 +9436,37 @@
         <v>1.115</v>
       </c>
       <c r="M98">
-        <v>4.423230719999999</v>
+        <v>4.469306039999999</v>
       </c>
       <c r="N98">
-        <v>-3.308230719999999</v>
+        <v>-3.354306039999999</v>
       </c>
       <c r="O98">
-        <v>-0.7939753727999997</v>
+        <v>-0.8050334495999998</v>
       </c>
       <c r="P98">
-        <v>-2.514255347199999</v>
+        <v>-2.549272590399999</v>
       </c>
       <c r="Q98">
-        <v>-1.829255347199999</v>
+        <v>-1.864272590399999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.490492818730563</v>
+        <v>1.972057091640751</v>
       </c>
       <c r="T98">
-        <v>19.8867404394018</v>
+        <v>26.5156539192024</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06049876593369293</v>
+        <v>0.05987506731581982</v>
       </c>
       <c r="W98">
-        <v>0.2215343909928352</v>
+        <v>0.2216814591269297</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2520781913903872</v>
+        <v>0.2494794471492492</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9482,22 +9482,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2741927281023444</v>
+        <v>0.2760927281023444</v>
       </c>
       <c r="C99">
-        <v>-12.83783109360316</v>
+        <v>-13.07312962187137</v>
       </c>
       <c r="D99">
-        <v>4.835968906396833</v>
+        <v>4.796070378128627</v>
       </c>
       <c r="E99">
-        <v>10.3138</v>
+        <v>10.5092</v>
       </c>
       <c r="F99">
-        <v>18.9538</v>
+        <v>19.1492</v>
       </c>
       <c r="G99">
         <v>1.28</v>
@@ -9518,37 +9518,37 @@
         <v>1.115</v>
       </c>
       <c r="M99">
-        <v>4.469306039999999</v>
+        <v>4.51538136</v>
       </c>
       <c r="N99">
-        <v>-3.354306039999999</v>
+        <v>-3.40038136</v>
       </c>
       <c r="O99">
-        <v>-0.8050334495999998</v>
+        <v>-0.8160915263999999</v>
       </c>
       <c r="P99">
-        <v>-2.549272590399999</v>
+        <v>-2.5842898336</v>
       </c>
       <c r="Q99">
-        <v>-1.864272590399999</v>
+        <v>-1.8992898336</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.972057091640751</v>
+        <v>2.935185637461126</v>
       </c>
       <c r="T99">
-        <v>26.5156539192024</v>
+        <v>39.7734808788036</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05987506731581982</v>
+        <v>0.05926409724116858</v>
       </c>
       <c r="W99">
-        <v>0.2216814591269297</v>
+        <v>0.2218255258705325</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2494794471492492</v>
+        <v>0.2469337385048691</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9564,22 +9564,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2760927281023444</v>
+        <v>0.2779927281023444</v>
       </c>
       <c r="C100">
-        <v>-13.07312962187137</v>
+        <v>-13.30777518219929</v>
       </c>
       <c r="D100">
-        <v>4.796070378128627</v>
+        <v>4.75682481780071</v>
       </c>
       <c r="E100">
-        <v>10.5092</v>
+        <v>10.7046</v>
       </c>
       <c r="F100">
-        <v>19.1492</v>
+        <v>19.3446</v>
       </c>
       <c r="G100">
         <v>1.28</v>
@@ -9600,37 +9600,37 @@
         <v>1.115</v>
       </c>
       <c r="M100">
-        <v>4.51538136</v>
+        <v>4.56145668</v>
       </c>
       <c r="N100">
-        <v>-3.40038136</v>
+        <v>-3.44645668</v>
       </c>
       <c r="O100">
-        <v>-0.8160915263999999</v>
+        <v>-0.8271496032</v>
       </c>
       <c r="P100">
-        <v>-2.5842898336</v>
+        <v>-2.6193070768</v>
       </c>
       <c r="Q100">
-        <v>-1.8992898336</v>
+        <v>-1.9343070768</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.935185637461126</v>
+        <v>5.824571274922253</v>
       </c>
       <c r="T100">
-        <v>39.7734808788036</v>
+        <v>79.54696175760719</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05926409724116858</v>
+        <v>0.05866546999630829</v>
       </c>
       <c r="W100">
-        <v>0.2218255258705325</v>
+        <v>0.2219666821748705</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9638,91 +9638,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2469337385048691</v>
+        <v>0.2444394583179512</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2779927281023444</v>
-      </c>
-      <c r="C101">
-        <v>-13.30777518219929</v>
-      </c>
-      <c r="D101">
-        <v>4.75682481780071</v>
-      </c>
-      <c r="E101">
-        <v>10.7046</v>
-      </c>
-      <c r="F101">
-        <v>19.3446</v>
-      </c>
-      <c r="G101">
-        <v>1.28</v>
-      </c>
-      <c r="H101">
-        <v>10.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.8</v>
-      </c>
-      <c r="K101">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="L101">
-        <v>1.115</v>
-      </c>
-      <c r="M101">
-        <v>4.56145668</v>
-      </c>
-      <c r="N101">
-        <v>-3.44645668</v>
-      </c>
-      <c r="O101">
-        <v>-0.8271496032</v>
-      </c>
-      <c r="P101">
-        <v>-2.6193070768</v>
-      </c>
-      <c r="Q101">
-        <v>-1.9343070768</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.824571274922253</v>
-      </c>
-      <c r="T101">
-        <v>79.54696175760719</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05866546999630829</v>
-      </c>
-      <c r="W101">
-        <v>0.2219666821748705</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2444394583179512</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
